--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -494,7 +494,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="792">
   <si>
     <t>Lab website content</t>
   </si>
@@ -688,7 +688,7 @@
     <t>Homepage headline</t>
   </si>
   <si>
-    <t>How the genome folds, and what that folding does.</t>
+    <t>Epigenetic regulation and chromatin architecture</t>
   </si>
   <si>
     <t>The large sentence at the top of the homepage.</t>
@@ -697,7 +697,7 @@
     <t>Homepage introduction</t>
   </si>
   <si>
-    <t>We map the physical organization of chromosomes inside the nucleus and ask how that organization controls gene expression. The group works across two sites, in Baltimore, USA and in Berlin, Germany.</t>
+    <t>Our group is interested in understanding the interplay between gene regulation and genome architecture, towards defining rules and principles of genome function.</t>
   </si>
   <si>
     <t>Paragraph under the homepage headline.</t>
@@ -755,6 +755,9 @@
     <t>Team introduction</t>
   </si>
   <si>
+    <t>Meet the members of our research team!</t>
+  </si>
+  <si>
     <t>Text at the top of the Team page.</t>
   </si>
   <si>
@@ -854,15 +857,12 @@
     <t>Bio paragraph</t>
   </si>
   <si>
-    <t>Ana Pombo studies how chromosomes are organized within the nucleus and how that organization shapes gene regulation, cellular identity, and disease. Her group develops the experimental and computational methods needed to place regulatory sequences in physical space relative to the genes they control.</t>
+    <t>Ana Pombo studies 3D genome folding and gene expression in development and disease. After her DPhil at University of Oxford, UK, Ana received a Royal Society Dorothy Hodgkin Fellowship and started her independent lab at the MRC London Institute for Medical Sciences. In 2013, she moved to the Berlin Institute of Medical Systems Biology (BIMSB) of the Max Delbrück Center in Berlin, Germany, where she serves as Deputy Director. Ana received the Robert Feulgen Prize in 2007, and was elected member of EMBO in 2018 and the European Academy of Sciences in 2022. She has pioneered Genome Architecture Mapping (GAM) to map 3D genome structure.</t>
   </si>
   <si>
     <t>One paragraph per row. Add as many "Bio paragraph" rows as you need.</t>
   </si>
   <si>
-    <t>Her lab developed Genome Architecture Mapping (GAM), a ligation-free method that infers chromatin contacts from the DNA content of thin nuclear slices, and which resolves the multi-way interactions that pairwise methods largely miss. During her doctoral work at Oxford she described transcription factories in the mammalian nucleus.</t>
-  </si>
-  <si>
     <t>Since 2024, the group has been operating at two sites: the Johns Hopkins University in Baltimore, MD, USA, and the Max Delbrück Center in Berlin, Germany.</t>
   </si>
   <si>
@@ -926,6 +926,9 @@
     <t>Gottfried Wilhelm Leibniz Prize (2025)</t>
   </si>
   <si>
+    <t>Elected member, European Academy of Sciences (2022)</t>
+  </si>
+  <si>
     <t>Elected member, EMBO (2018)</t>
   </si>
   <si>
@@ -953,6 +956,24 @@
     <t>CV (PDF)</t>
   </si>
   <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>https://github.com/pombo-lab</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/anapombo/</t>
+  </si>
+  <si>
+    <t>X (Twitter)</t>
+  </si>
+  <si>
+    <t>https://x.com/apombo1</t>
+  </si>
+  <si>
     <t>Code</t>
   </si>
   <si>
@@ -1064,12 +1085,18 @@
     <t>Department of Biology, Krieger School of Arts &amp; Sciences</t>
   </si>
   <si>
+    <t>Jing is interested in how inherited genetic variation shapes chromatin architecture and gene regulation in response to acute drug exposure, as well as the underlying molecular mechanisms that drive these responses. She integrates genetic, genomic, and epigenomic approaches to investigate these questions.</t>
+  </si>
+  <si>
     <t>jhe109@jh.edu</t>
   </si>
   <si>
     <t>Derek Hui</t>
   </si>
   <si>
+    <t>Derek is interested in how different drugs of abuse impact gene regulatory networks and cell-cell interaction dynamics. He studies the molecular impacts of how different drugs of abuse impact the cells in the mouse ventral tegmental area.</t>
+  </si>
+  <si>
     <t>mhui3@jh.edu</t>
   </si>
   <si>
@@ -1079,7 +1106,7 @@
     <t>Human Genetics &amp; Genomics PhD Program, School of Medicine</t>
   </si>
   <si>
-    <t>Alex is interested in understanding causality of 3D genome structure in gene expression, genetic variants, and cellular states.</t>
+    <t>Alex is interested in the causal relationship between noncoding elements and gene expression in response to acute drug exposure and during mammalian neurodevelopment, where a single genome generates multiple functional states. He received his B.S. from Korea University, where he studied oxidative modifications of nucleic acids in repetitive DNA elements and CRISPR-based approaches under Dr. Sung Wook Chi.</t>
   </si>
   <si>
     <t>apark55@jhmi.edu</t>
@@ -1112,7 +1139,7 @@
     <t>sergej.herzog@mdc-berlin.de</t>
   </si>
   <si>
-    <t>Berta Jimenez-Alfaro Hacha</t>
+    <t>Berta Jiménez-Alfaro Hacha</t>
   </si>
   <si>
     <t>berta.jimenez-alfarohacha@mdc-berlin.de</t>
@@ -1124,6 +1151,9 @@
     <t>alexander.kukalev@mdc-berlin.de</t>
   </si>
   <si>
+    <t>https://scholar.google.com/citations?user=EIlLnQEAAAAJ&amp;hl=en&amp;oi=sra</t>
+  </si>
+  <si>
     <t>Ali Mamivand</t>
   </si>
   <si>
@@ -1145,9 +1175,15 @@
     <t>Christoph Thieme</t>
   </si>
   <si>
+    <t>Chris develops computational approaches to extract biological insight from complex data. He combines statistical modeling, data analysis, and algorithm development to uncover patterns in multimodal data, with a particular interest in extending GAM to new biological questions.</t>
+  </si>
+  <si>
     <t>christoph.thieme@mdc-berlin.de</t>
   </si>
   <si>
+    <t>https://scholar.google.com/citations?user=bLqpoM4AAAAJ&amp;hl=en&amp;oi=sra</t>
+  </si>
+  <si>
     <t>Years</t>
   </si>
   <si>
@@ -1587,6 +1623,21 @@
   </si>
   <si>
     <t>2002</t>
+  </si>
+  <si>
+    <t>Andrea Willemin</t>
+  </si>
+  <si>
+    <t>Luna Zea-Redondo</t>
+  </si>
+  <si>
+    <t>Dominika Vojtasova</t>
+  </si>
+  <si>
+    <t>Izabela Harabula</t>
+  </si>
+  <si>
+    <t>Ibai Irastorza-Azcarate</t>
   </si>
   <si>
     <t>Page address</t>
@@ -1785,6 +1836,27 @@
     <t>649(8097), 759–776</t>
   </si>
   <si>
+    <t>Haplotype-resolved genome architecture mapping uncovers pervasive structural heterogeneity between human homologous chromosomes</t>
+  </si>
+  <si>
+    <t>Markowski, J., Kukalev, A., Robens, C., Thieme, C. J., Streck, A., Mao, H., Parsi, K. M., Maehr, R., Pombo, A., Schwarz, R. F.</t>
+  </si>
+  <si>
+    <t>bioRxiv</t>
+  </si>
+  <si>
+    <t>10.64898/2026.06.16.732681</t>
+  </si>
+  <si>
+    <t>Specialised super-enhancer networks in stem cells and neurons</t>
+  </si>
+  <si>
+    <t>Harabula, I., Speakman, L., Musella, F., Forillo, L., Zea-Redondo, L., Kukalev, A., Beagrie, R. A., Morris, K. J., Fernandes, L., Irastorza-Azcarate, I., Fernandes, A. M., Carvalho, S., Szabó, D., Ferrai, C., Nicodemi, M., Welch, L., Pombo, A.</t>
+  </si>
+  <si>
+    <t>10.1101/2025.08.13.670083</t>
+  </si>
+  <si>
     <t>Cryosectioning-enhanced super-resolution microscopy for single-protein imaging across cells and tissues</t>
   </si>
   <si>
@@ -1809,6 +1881,9 @@
     <t>21(7), 735–775</t>
   </si>
   <si>
+    <t>10.1038/s44320-025-00107-3</t>
+  </si>
+  <si>
     <t>SRRM2 splicing factor modulates cell fate in early development</t>
   </si>
   <si>
@@ -1821,6 +1896,9 @@
     <t>13(4), bio060415</t>
   </si>
   <si>
+    <t>https://journals.biologists.com/bio/article/13/4/bio060415/347005/SRRM2-splicing-factor-modulates-cell-fate-in-early</t>
+  </si>
+  <si>
     <t>Epigenetic regulatory layers in the three-dimensional nucleus</t>
   </si>
   <si>
@@ -1833,6 +1911,15 @@
     <t>84(3), 415–428</t>
   </si>
   <si>
+    <t>A single dose of cocaine rewires the 3D genome structure of midbrain dopamine neurons</t>
+  </si>
+  <si>
+    <t>Szabó, D., Franke, V., Bianco, S., Batiuk, M. Y., Paul, E. J., Kukalev, A., Pfisterer, U. G., Irastorza-Azcarate, I., Chiariello, A. M., Demharter, S., Zea-Redondo, L., Lopez-Atalaya, J. P., Nicodemi, M., Akalin, A., Khodosevich, K., Ungless, M. A., Winick-Ng, W., Pombo, A.</t>
+  </si>
+  <si>
+    <t>10.1101/2024.05.10.593308</t>
+  </si>
+  <si>
     <t>Research briefing</t>
   </si>
   <si>
@@ -1854,6 +1941,9 @@
     <t>20(7), 1037–1047</t>
   </si>
   <si>
+    <t>10.1038/s41592-023-01903-1</t>
+  </si>
+  <si>
     <t>Mechanisms of enhancer function in neuronal systems in health and disease</t>
   </si>
   <si>
@@ -1921,6 +2011,9 @@
   </si>
   <si>
     <t>599(7886), 684–691</t>
+  </si>
+  <si>
+    <t>10.1038/s41586-021-04081-2</t>
   </si>
   <si>
     <t>Comparison of the Hi-C, GAM and SPRITE methods using polymer models of chromatin</t>
@@ -3465,7 +3558,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3480,37 +3573,37 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>125</v>
@@ -3521,16 +3614,16 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -3538,7 +3631,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>127</v>
@@ -3546,27 +3639,27 @@
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F3" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>442</v>
+      </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>127</v>
@@ -3574,27 +3667,27 @@
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F4" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>445</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>127</v>
@@ -3602,19 +3695,19 @@
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -3622,7 +3715,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>127</v>
@@ -3630,27 +3723,29 @@
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="F6" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>454</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>127</v>
@@ -3658,27 +3753,29 @@
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>459</v>
+      </c>
       <c r="K7" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>127</v>
@@ -3686,19 +3783,19 @@
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -3706,7 +3803,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>127</v>
@@ -3714,27 +3811,27 @@
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F9" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>466</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>127</v>
@@ -3742,19 +3839,19 @@
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -3762,7 +3859,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>127</v>
@@ -3770,27 +3867,29 @@
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="F11" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>474</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>127</v>
@@ -3798,19 +3897,19 @@
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -3818,7 +3917,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>127</v>
@@ -3826,19 +3925,19 @@
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -3846,7 +3945,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>127</v>
@@ -3854,19 +3953,19 @@
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>420</v>
+        <v>485</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -3874,7 +3973,7 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>127</v>
@@ -3882,19 +3981,19 @@
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>440</v>
+        <v>489</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -3902,7 +4001,7 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>127</v>
@@ -3913,16 +4012,16 @@
         <v>2021</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -3930,7 +4029,7 @@
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>127</v>
@@ -3938,27 +4037,29 @@
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F17" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>498</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>127</v>
@@ -3966,19 +4067,19 @@
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -3986,7 +4087,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>127</v>
@@ -3994,19 +4095,19 @@
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -4014,7 +4115,7 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>127</v>
@@ -4025,16 +4126,16 @@
         <v>2020</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>488</v>
+        <v>437</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -4042,7 +4143,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>127</v>
@@ -4050,19 +4151,19 @@
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -4070,7 +4171,7 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>127</v>
@@ -4078,19 +4179,19 @@
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>436</v>
+        <v>515</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -4098,7 +4199,7 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>127</v>
@@ -4106,19 +4207,19 @@
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -4126,7 +4227,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>127</v>
@@ -4134,19 +4235,19 @@
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>499</v>
+        <v>523</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -4154,7 +4255,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>127</v>
@@ -4162,19 +4263,19 @@
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>428</v>
+        <v>462</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -4182,7 +4283,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>127</v>
@@ -4190,19 +4291,19 @@
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -4210,7 +4311,7 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>127</v>
@@ -4218,19 +4319,19 @@
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>420</v>
+        <v>530</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -4238,7 +4339,7 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>127</v>
@@ -4249,16 +4350,16 @@
         <v>2017</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>516</v>
+        <v>452</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -4266,7 +4367,7 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>127</v>
@@ -4277,16 +4378,16 @@
         <v>2017</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -4294,7 +4395,7 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>127</v>
@@ -4305,16 +4406,16 @@
         <v>2017</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>524</v>
+        <v>437</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>525</v>
+        <v>544</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -4322,7 +4423,7 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>127</v>
@@ -4333,16 +4434,16 @@
         <v>2017</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -4350,7 +4451,7 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>127</v>
@@ -4361,16 +4462,16 @@
         <v>2017</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>420</v>
+        <v>551</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -4378,7 +4479,7 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>127</v>
@@ -4389,16 +4490,16 @@
         <v>2017</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>436</v>
+        <v>555</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -4406,7 +4507,7 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>127</v>
@@ -4414,19 +4515,19 @@
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>512</v>
+        <v>558</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>537</v>
+        <v>559</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>538</v>
+        <v>560</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -4434,7 +4535,7 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>127</v>
@@ -4442,19 +4543,19 @@
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>539</v>
+        <v>561</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>540</v>
+        <v>562</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -4462,7 +4563,7 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>127</v>
@@ -4470,19 +4571,19 @@
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>512</v>
+        <v>565</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>543</v>
+        <v>462</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -4490,7 +4591,7 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>127</v>
@@ -4501,16 +4602,16 @@
         <v>2016</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>545</v>
+        <v>567</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -4518,7 +4619,7 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>127</v>
@@ -4526,19 +4627,19 @@
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>551</v>
+        <v>437</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -4546,7 +4647,7 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>127</v>
@@ -4554,19 +4655,19 @@
     </row>
     <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>428</v>
+        <v>574</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -4574,7 +4675,7 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>127</v>
@@ -4582,19 +4683,19 @@
     </row>
     <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>556</v>
+        <v>576</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>557</v>
+        <v>577</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -4602,7 +4703,7 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>127</v>
@@ -4613,16 +4714,16 @@
         <v>2015</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>561</v>
+        <v>581</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -4630,7 +4731,7 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>127</v>
@@ -4641,16 +4742,16 @@
         <v>2015</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -4658,7 +4759,7 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>127</v>
@@ -4666,19 +4767,19 @@
     </row>
     <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>524</v>
+        <v>589</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -4686,7 +4787,7 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>127</v>
@@ -4694,19 +4795,19 @@
     </row>
     <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>484</v>
+        <v>593</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>572</v>
+        <v>594</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -4714,7 +4815,7 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>127</v>
@@ -4722,19 +4823,19 @@
     </row>
     <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>573</v>
+        <v>595</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>574</v>
+        <v>596</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>575</v>
+        <v>481</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -4742,7 +4843,7 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>127</v>
@@ -4753,16 +4854,16 @@
         <v>2014</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -4770,7 +4871,7 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>127</v>
@@ -4778,19 +4879,19 @@
     </row>
     <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>583</v>
+        <v>515</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -4798,7 +4899,7 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>127</v>
@@ -4806,19 +4907,19 @@
     </row>
     <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>585</v>
+        <v>604</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>587</v>
+        <v>606</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -4826,7 +4927,7 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>127</v>
@@ -4834,19 +4935,19 @@
     </row>
     <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>589</v>
+        <v>608</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -4854,7 +4955,7 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>127</v>
@@ -4865,16 +4966,16 @@
         <v>2013</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>594</v>
+        <v>613</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>595</v>
+        <v>614</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -4882,7 +4983,7 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>127</v>
@@ -4890,19 +4991,19 @@
     </row>
     <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>599</v>
+        <v>618</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -4910,7 +5011,7 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>127</v>
@@ -4918,19 +5019,19 @@
     </row>
     <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>594</v>
+        <v>621</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>424</v>
+        <v>622</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -4938,7 +5039,7 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>127</v>
@@ -4946,19 +5047,19 @@
     </row>
     <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>606</v>
+        <v>627</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -4966,7 +5067,7 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>127</v>
@@ -4977,16 +5078,16 @@
         <v>2012</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>609</v>
+        <v>630</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -4994,7 +5095,7 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>127</v>
@@ -5005,16 +5106,16 @@
         <v>2012</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>524</v>
+        <v>448</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -5022,7 +5123,7 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>127</v>
@@ -5030,19 +5131,19 @@
     </row>
     <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -5050,7 +5151,7 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>127</v>
@@ -5058,19 +5159,19 @@
     </row>
     <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>579</v>
+        <v>640</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -5078,7 +5179,7 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>127</v>
@@ -5086,19 +5187,19 @@
     </row>
     <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>623</v>
+        <v>555</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -5106,7 +5207,7 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>127</v>
@@ -5114,19 +5215,19 @@
     </row>
     <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>436</v>
+        <v>647</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -5134,7 +5235,7 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>127</v>
@@ -5142,19 +5243,19 @@
     </row>
     <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>630</v>
+        <v>610</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -5162,7 +5263,7 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>127</v>
@@ -5173,16 +5274,16 @@
         <v>2010</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>547</v>
+        <v>654</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>634</v>
+        <v>655</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -5190,7 +5291,7 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>127</v>
@@ -5201,16 +5302,16 @@
         <v>2010</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>637</v>
+        <v>658</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -5218,7 +5319,7 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>127</v>
@@ -5229,16 +5330,16 @@
         <v>2010</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>638</v>
+        <v>659</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>639</v>
+        <v>660</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>640</v>
+        <v>661</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>641</v>
+        <v>662</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -5246,7 +5347,7 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>127</v>
@@ -5257,16 +5358,16 @@
         <v>2010</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>642</v>
+        <v>663</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>644</v>
+        <v>578</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -5274,7 +5375,7 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>127</v>
@@ -5285,16 +5386,16 @@
         <v>2010</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>648</v>
+        <v>515</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>649</v>
+        <v>668</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
@@ -5302,7 +5403,7 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>127</v>
@@ -5310,19 +5411,19 @@
     </row>
     <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>651</v>
+        <v>670</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>652</v>
+        <v>671</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>653</v>
+        <v>672</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -5330,7 +5431,7 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>127</v>
@@ -5338,19 +5439,19 @@
     </row>
     <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>654</v>
+        <v>673</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>608</v>
+        <v>674</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -5358,7 +5459,7 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>127</v>
@@ -5366,19 +5467,19 @@
     </row>
     <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>537</v>
+        <v>679</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>659</v>
+        <v>680</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -5386,7 +5487,7 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>127</v>
@@ -5397,16 +5498,16 @@
         <v>2009</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>663</v>
+        <v>684</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -5414,7 +5515,7 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>127</v>
@@ -5422,19 +5523,19 @@
     </row>
     <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>664</v>
+        <v>685</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>665</v>
+        <v>639</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>473</v>
+        <v>686</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -5442,7 +5543,7 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>127</v>
@@ -5450,19 +5551,19 @@
     </row>
     <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>668</v>
+        <v>689</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>669</v>
+        <v>568</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -5470,7 +5571,7 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>127</v>
@@ -5478,19 +5579,19 @@
     </row>
     <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>671</v>
+        <v>691</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>616</v>
+        <v>693</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -5498,7 +5599,7 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>127</v>
@@ -5506,19 +5607,19 @@
     </row>
     <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>674</v>
+        <v>695</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>675</v>
+        <v>696</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>547</v>
+        <v>504</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>676</v>
+        <v>697</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -5526,7 +5627,7 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>127</v>
@@ -5534,19 +5635,19 @@
     </row>
     <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>677</v>
+        <v>698</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>678</v>
+        <v>699</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>473</v>
+        <v>700</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>679</v>
+        <v>701</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -5554,7 +5655,7 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>127</v>
@@ -5562,19 +5663,19 @@
     </row>
     <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>680</v>
+        <v>702</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>681</v>
+        <v>703</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>682</v>
+        <v>647</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>683</v>
+        <v>704</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -5582,7 +5683,7 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>127</v>
@@ -5593,16 +5694,16 @@
         <v>2007</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>685</v>
+        <v>706</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>686</v>
+        <v>578</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>687</v>
+        <v>707</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -5610,7 +5711,7 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>127</v>
@@ -5621,16 +5722,16 @@
         <v>2007</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>689</v>
+        <v>709</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>690</v>
+        <v>504</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>691</v>
+        <v>710</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -5638,7 +5739,7 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>127</v>
@@ -5646,19 +5747,19 @@
     </row>
     <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>692</v>
+        <v>711</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>689</v>
+        <v>712</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>640</v>
+        <v>713</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -5666,7 +5767,7 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>127</v>
@@ -5674,19 +5775,19 @@
     </row>
     <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>694</v>
+        <v>715</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>695</v>
+        <v>716</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>579</v>
+        <v>717</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>696</v>
+        <v>718</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -5694,7 +5795,7 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>127</v>
@@ -5702,19 +5803,19 @@
     </row>
     <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>698</v>
+        <v>720</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>682</v>
+        <v>721</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>699</v>
+        <v>722</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -5722,7 +5823,7 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>127</v>
@@ -5730,19 +5831,19 @@
     </row>
     <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>700</v>
+        <v>723</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>701</v>
+        <v>720</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>655</v>
+        <v>671</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>702</v>
+        <v>724</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -5750,7 +5851,7 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>127</v>
@@ -5758,19 +5859,19 @@
     </row>
     <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>703</v>
+        <v>725</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>704</v>
+        <v>726</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>705</v>
+        <v>610</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>706</v>
+        <v>727</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -5778,7 +5879,7 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>127</v>
@@ -5786,19 +5887,19 @@
     </row>
     <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>707</v>
+        <v>728</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>708</v>
+        <v>729</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -5806,7 +5907,7 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>127</v>
@@ -5814,19 +5915,19 @@
     </row>
     <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>714</v>
+        <v>733</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -5834,7 +5935,7 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>127</v>
@@ -5842,19 +5943,19 @@
     </row>
     <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>715</v>
+        <v>734</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>716</v>
+        <v>735</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>579</v>
+        <v>736</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -5862,7 +5963,7 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>127</v>
@@ -5870,19 +5971,19 @@
     </row>
     <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -5890,7 +5991,7 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>127</v>
@@ -5898,19 +5999,19 @@
     </row>
     <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>669</v>
+        <v>744</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -5918,7 +6019,7 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>127</v>
@@ -5926,19 +6027,19 @@
     </row>
     <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>726</v>
+        <v>747</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>727</v>
+        <v>610</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>728</v>
+        <v>748</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -5946,7 +6047,7 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>127</v>
@@ -5957,16 +6058,16 @@
         <v>2003</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>729</v>
+        <v>749</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>732</v>
+        <v>752</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -5974,7 +6075,7 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>127</v>
@@ -5985,16 +6086,16 @@
         <v>2003</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>733</v>
+        <v>753</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>681</v>
+        <v>754</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>734</v>
+        <v>700</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>735</v>
+        <v>755</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -6002,7 +6103,7 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>127</v>
@@ -6013,16 +6114,16 @@
         <v>2003</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>738</v>
+        <v>759</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -6030,9 +6131,93 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L91" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L94" s="2" t="s">
         <v>127</v>
       </c>
     </row>
@@ -6068,22 +6253,22 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>739</v>
+        <v>770</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>740</v>
+        <v>771</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>741</v>
+        <v>772</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>742</v>
+        <v>773</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>124</v>
@@ -6097,23 +6282,23 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>743</v>
+        <v>774</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>744</v>
+        <v>775</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>745</v>
+        <v>776</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>746</v>
+        <v>777</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>747</v>
+        <v>778</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6121,23 +6306,23 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>743</v>
+        <v>774</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>744</v>
+        <v>775</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>745</v>
+        <v>776</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>748</v>
+        <v>779</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>747</v>
+        <v>778</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -6167,10 +6352,10 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>749</v>
+        <v>780</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>125</v>
@@ -6178,10 +6363,10 @@
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>750</v>
+        <v>781</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>751</v>
+        <v>782</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>127</v>
@@ -6189,10 +6374,10 @@
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>752</v>
+        <v>783</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>753</v>
+        <v>784</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>127</v>
@@ -6200,10 +6385,10 @@
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>754</v>
+        <v>785</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>127</v>
@@ -6234,13 +6419,13 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>756</v>
+        <v>787</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>125</v>
@@ -6248,11 +6433,11 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>757</v>
+        <v>788</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>127</v>
@@ -6260,11 +6445,11 @@
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>758</v>
+        <v>789</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>127</v>
@@ -6272,11 +6457,11 @@
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>759</v>
+        <v>790</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>760</v>
+        <v>791</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>127</v>
@@ -6430,86 +6615,88 @@
       <c r="A12" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="C12" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -6520,7 +6707,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -6541,75 +6728,64 @@
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -6620,7 +6796,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -6647,7 +6823,7 @@
         <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
@@ -6692,7 +6868,7 @@
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>73</v>
@@ -6836,50 +7012,104 @@
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -6911,45 +7141,45 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>127</v>
@@ -6957,22 +7187,22 @@
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>127</v>
@@ -6980,21 +7210,21 @@
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -7026,28 +7256,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>125</v>
@@ -7055,20 +7285,20 @@
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -7078,20 +7308,20 @@
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -7101,20 +7331,22 @@
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="F4" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -7124,20 +7356,22 @@
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E5" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>198</v>
+      </c>
       <c r="F5" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -7147,22 +7381,22 @@
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -7172,20 +7406,20 @@
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -7195,20 +7429,20 @@
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -7218,20 +7452,20 @@
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -7241,20 +7475,20 @@
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -7264,43 +7498,45 @@
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="I11" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -7310,20 +7546,20 @@
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -7333,20 +7569,20 @@
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -7356,23 +7592,27 @@
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>225</v>
+      </c>
       <c r="F15" s="2" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="I15" s="2" t="s">
         <v>127</v>
       </c>
@@ -7395,7 +7635,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -7407,22 +7647,22 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>125</v>
@@ -7430,16 +7670,16 @@
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -7449,19 +7689,19 @@
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
@@ -7470,19 +7710,19 @@
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
@@ -7491,19 +7731,19 @@
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
@@ -7512,19 +7752,19 @@
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
@@ -7533,19 +7773,19 @@
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
@@ -7554,19 +7794,19 @@
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
@@ -7575,16 +7815,16 @@
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -7594,19 +7834,19 @@
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
@@ -7615,19 +7855,19 @@
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
@@ -7636,19 +7876,19 @@
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
@@ -7657,19 +7897,19 @@
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
@@ -7678,19 +7918,19 @@
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
@@ -7699,19 +7939,19 @@
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
@@ -7720,19 +7960,19 @@
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
@@ -7741,19 +7981,19 @@
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
@@ -7762,19 +8002,19 @@
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
@@ -7783,19 +8023,19 @@
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
@@ -7804,19 +8044,19 @@
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
@@ -7825,19 +8065,19 @@
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
@@ -7846,19 +8086,19 @@
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
@@ -7867,19 +8107,19 @@
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
@@ -7888,16 +8128,16 @@
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -7907,19 +8147,19 @@
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
@@ -7928,19 +8168,19 @@
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
@@ -7949,19 +8189,19 @@
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
@@ -7970,19 +8210,19 @@
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
@@ -7991,19 +8231,19 @@
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
@@ -8012,19 +8252,19 @@
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
@@ -8033,19 +8273,19 @@
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
@@ -8054,19 +8294,19 @@
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
@@ -8075,19 +8315,19 @@
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
@@ -8096,16 +8336,16 @@
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -8115,19 +8355,19 @@
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
@@ -8136,19 +8376,19 @@
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
@@ -8157,19 +8397,19 @@
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
@@ -8178,19 +8418,19 @@
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
@@ -8199,19 +8439,19 @@
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
@@ -8220,19 +8460,19 @@
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
@@ -8241,19 +8481,19 @@
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
@@ -8262,19 +8502,19 @@
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
@@ -8283,19 +8523,19 @@
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
@@ -8304,19 +8544,19 @@
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
@@ -8325,19 +8565,19 @@
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
@@ -8346,16 +8586,16 @@
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -8365,16 +8605,16 @@
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
@@ -8384,19 +8624,19 @@
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
@@ -8405,16 +8645,16 @@
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -8424,16 +8664,16 @@
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
@@ -8443,16 +8683,16 @@
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
@@ -8462,19 +8702,19 @@
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
@@ -8483,19 +8723,19 @@
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
@@ -8504,20 +8744,95 @@
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2" t="s">
         <v>127</v>
       </c>
     </row>
@@ -8552,34 +8867,34 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>125</v>
@@ -8587,26 +8902,26 @@
     </row>
     <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -8616,26 +8931,26 @@
     </row>
     <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -8645,26 +8960,26 @@
     </row>
     <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -8699,16 +9014,16 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>395</v>
+        <v>412</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>124</v>
@@ -8722,13 +9037,13 @@
         <v>46175</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>398</v>
+        <v>415</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
@@ -8740,13 +9055,13 @@
         <v>45799</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>399</v>
+        <v>416</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>401</v>
+        <v>418</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -8758,13 +9073,13 @@
         <v>45637</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
@@ -8776,16 +9091,16 @@
         <v>45096</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>127</v>

--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -398,46 +398,25 @@
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>Optional. Last part of the page URL, e.g. "neuroepigenetics". Made from the title if blank.</t>
+          <t>Short subtitle shown under the title.</t>
         </r>
       </text>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
         <r>
-          <t>Short subtitle shown on cards.</t>
+          <t>One or two sentences about this area.</t>
         </r>
       </text>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
         <r>
-          <t>One or two sentences shown on cards and at the top of the page.</t>
+          <t>Bullet points, one per line inside the cell.</t>
         </r>
       </text>
     </comment>
     <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <t>Main text. Put each paragraph on its own line inside the cell.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <t>Bullet points, one per line inside the cell.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <t>Optional file name of an image in public/images/research, or a web address.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
       <text>
         <r>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
@@ -494,7 +473,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="840">
   <si>
     <t>Lab website content</t>
   </si>
@@ -565,7 +544,7 @@
     <t>Photos and logos</t>
   </si>
   <si>
-    <t>Upload the image to public/images/people (or research, funders) on GitHub, then type just its file name, e.g. "jane-doe.jpg".</t>
+    <t>Upload the image to public/images/people (or public/images/funders for logos) on GitHub, then type just its file name, e.g. "jane-doe.jpg".</t>
   </si>
   <si>
     <t>Column help</t>
@@ -616,7 +595,7 @@
     <t>Research</t>
   </si>
   <si>
-    <t>Research areas. Each row gets its own page. Rows appear in this order.</t>
+    <t>Research areas, shown as sections of the Research page in this order.</t>
   </si>
   <si>
     <t>News</t>
@@ -679,7 +658,7 @@
     <t>Site description</t>
   </si>
   <si>
-    <t>Genome architecture and epigenetic regulation. A research group at Johns Hopkins University and the Max Delbrück Center.</t>
+    <t>Our group is interested in understanding the interplay between gene regulation and genome architecture, towards defining rules and principles of genome function.</t>
   </si>
   <si>
     <t>One or two sentences used by search engines and link previews.</t>
@@ -697,16 +676,10 @@
     <t>Homepage introduction</t>
   </si>
   <si>
-    <t>Our group is interested in understanding the interplay between gene regulation and genome architecture, towards defining rules and principles of genome function.</t>
-  </si>
-  <si>
     <t>Paragraph under the homepage headline.</t>
   </si>
   <si>
     <t>Footer blurb</t>
-  </si>
-  <si>
-    <t>Epigenetic regulation and chromatin architecture: measuring where genes sit in three-dimensional space, and what that position does to their activity.</t>
   </si>
   <si>
     <t>Short description in the footer of every page.</t>
@@ -732,13 +705,26 @@
     <t>Author names to show in bold in publication lists. One per line, exactly as written in the Authors column (e.g. "Pombo, A.").</t>
   </si>
   <si>
-    <t>Research introduction</t>
-  </si>
-  <si>
-    <t>The group works on the interplay between gene regulation and genome architecture, from the local action of transcription factors, through long-range contacts that connect regulatory sequences to their target genes, to the positioning of whole chromosomes within the nucleus. Method development and biological questions advance together: we build the measurement when the existing one cannot answer the question.</t>
-  </si>
-  <si>
-    <t>Introduction on the homepage and the Research page.</t>
+    <t>Lab description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We study mechanisms of gene expression at multiple levels, from the local action of transcription factors, to long-range chromatin looping events that connect regulatory DNA sequences with the genes they regulate, to how whole chromosomes are positioned within cell nuclei. Binding of transcription factors at regulatory sequences helps recruit chromatin remodelers and the transcription machinery to transcription sites.
+Upon recruitment, RNA polymerases either remain primed for subsequent activation (e.g. after environmental stress, during differentiation or disease), or directly transcribe the DNA template into RNA molecules, which code for proteins or for structural RNAs that constitute many enzymatic complexes.
+An increasingly important aspect of gene regulation is the three-dimensional folding of the genome, and the mechanisms that control physical contacts of distant regulatory DNA sequences with gene promoters to activate gene expression. To directly measure genome topologies, our group developed Genome Architecture Mapping (GAM).
+Our long-term strategy for unravelling the principles of genome function in higher eukaryotes aims to integrate multiple parameters, which is becoming increasingly possible with state-of-the-art developments in single cell genomics, molecular biology, epigenetics, nuclear imaging, and genetics.</t>
+  </si>
+  <si>
+    <t>The "About the lab" text on the homepage. One paragraph per line.</t>
+  </si>
+  <si>
+    <t>Research description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our main goal is to unravel the diverse mechanisms of mammalian gene regulation and their roles in development and disease. Gene activation is controlled locally through transcription factors, chromatin modifiers, and the transcription and RNA processing machineries. Gene expression is also intricately regulated by the three-dimensional (3D) structure of the genome, which modifies the location of genes relative to activating or repressing biochemical environments. Repressing nuclear locations include the nuclear lamina and heterochromatin. Activating 3D genome conformations can work by regulating the physical proximity between regulatory regions and their responsive genes. As many disease-associated genetic variants fall in non-coding regulatory elements scattered in the genome, our work aims to advance the functional interpretation of the linear genome sequence. We especially put effort in devising experimental and computational approaches to map 3D genome structure in different cell types, in development and in disease, to study developmental and disease mechanisms, towards novel diagnostics, prognostics and therapeutics.
+We have developed Genome Architecture Mapping (GAM), an orthogonal 3D genome folding mapping technology which yields fine maps of chromatin contacts from small cell numbers (500−1000), and is uniquely powerful to quantify different metrics of 3D genome structure, such as multiway contacts and chromatin melting. With immuno-GAM, we introduced the selection of cell types within complex tissues to enable the application of GAM in rare cells, such as dopaminergic neurons in the midbrain. GAM is an inherently suited platform for multimodal molecular phenotyping of biological samples, from genome sequence and 3D structure, to transcript and protein quantification. As a first step towards GAM multimodality, we have developed Oligo-Seq, a novel approach to detect minute amounts of specific RNA sequences within thin tissue cryosections, as used for GAM. We currently develop the application of Oligo-seq in spatial transcriptomics, especially in archival clinical samples (e.g. FFPE). By further developing multimodal integration of 3D genome topology, with the abundance of specific regulatory factors and gene expression, at the single-cell level, we aim to extract dynamic states of gene regulation and cause-effect relationships that connect 3D genome structure with gene expression. Ultimately, we seek to advance the interpretability of the linear genome sequence, to gain a deeper understanding of 3D genome regulation mechanisms in gene expression, and to advance their predictability.</t>
+  </si>
+  <si>
+    <t>Main text of the Research page. The first paragraph is also shown on the homepage.</t>
   </si>
   <si>
     <t>Research themes</t>
@@ -851,7 +837,10 @@
     <t>Email</t>
   </si>
   <si>
-    <t>Leave blank to use the lab contact email.</t>
+    <t>One address per row; add another "Email" row for each extra address. The first is the main one. Leave blank to use the lab contact email.</t>
+  </si>
+  <si>
+    <t>ana.pombo@mdc-berlin.de</t>
   </si>
   <si>
     <t>Bio paragraph</t>
@@ -893,6 +882,12 @@
     <t>Guest Group Leader, Berlin Institute for Medical Systems Biology, Max Delbrück Center for Molecular Medicine</t>
   </si>
   <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>+49 30 9406-1760 (Berlin)</t>
+  </si>
+  <si>
     <t>Education</t>
   </si>
   <si>
@@ -1016,10 +1011,11 @@
     <t>Max Delbrück Center</t>
   </si>
   <si>
-    <t>Berlin Institute for Medical Systems Biology (BIMSB)</t>
-  </si>
-  <si>
-    <t>Berlin-Buch, Germany</t>
+    <t xml:space="preserve">Berlin Institute for Medical Systems Biology (BIMSB)
+Hannoversche Straße 28, 10115 Berlin</t>
+  </si>
+  <si>
+    <t>Berlin, Germany</t>
   </si>
   <si>
     <t>#D98A1F</t>
@@ -1079,7 +1075,7 @@
     <t>Jing He</t>
   </si>
   <si>
-    <t>Postdoctoral Fellow</t>
+    <t>Postdoctoral Researcher</t>
   </si>
   <si>
     <t>Department of Biology, Krieger School of Arts &amp; Sciences</t>
@@ -1115,9 +1111,6 @@
     <t>Li Wang</t>
   </si>
   <si>
-    <t>Senior Scientist</t>
-  </si>
-  <si>
     <t>lwang258@jh.edu</t>
   </si>
   <si>
@@ -1148,6 +1141,9 @@
     <t>Alexander Kukalev</t>
   </si>
   <si>
+    <t>Senior Staff Scientist</t>
+  </si>
+  <si>
     <t>alexander.kukalev@mdc-berlin.de</t>
   </si>
   <si>
@@ -1175,6 +1171,9 @@
     <t>Christoph Thieme</t>
   </si>
   <si>
+    <t>Senior Bioinformatician</t>
+  </si>
+  <si>
     <t>Chris develops computational approaches to extract biological insight from complex data. He combines statistical modeling, data analysis, and algorithm development to uncover patterns in multimodal data, with a particular interest in extending GAM to new biological questions.</t>
   </si>
   <si>
@@ -1184,6 +1183,48 @@
     <t>https://scholar.google.com/citations?user=bLqpoM4AAAAJ&amp;hl=en&amp;oi=sra</t>
   </si>
   <si>
+    <t>Warren Winick-Ng</t>
+  </si>
+  <si>
+    <t>Leading TheraGAM</t>
+  </si>
+  <si>
+    <t>Freddy Carew</t>
+  </si>
+  <si>
+    <t>Parithi Ezhil Mathi Ela</t>
+  </si>
+  <si>
+    <t>Scientist</t>
+  </si>
+  <si>
+    <t>parithiezhilmathi.ela@mdc-berlin.de</t>
+  </si>
+  <si>
+    <t>Andréa Willemin</t>
+  </si>
+  <si>
+    <t>andrea.willemin@mdc-berlin.de</t>
+  </si>
+  <si>
+    <t>Annadha Vijayakumar Jitha</t>
+  </si>
+  <si>
+    <t>Graduate / Undergraduate Student</t>
+  </si>
+  <si>
+    <t>annadha.vijayakumarjitha@mdc-berlin.de</t>
+  </si>
+  <si>
+    <t>Zeren Erten</t>
+  </si>
+  <si>
+    <t>Trainee</t>
+  </si>
+  <si>
+    <t>zeren.erten@mdc-berlin.de</t>
+  </si>
+  <si>
     <t>Years</t>
   </si>
   <si>
@@ -1211,13 +1252,13 @@
     <t>Postdoc</t>
   </si>
   <si>
-    <t>Postdoctoral Fellow, Peter Park lab, Blavatnik Institute of Biomedical Informatics, Harvard Medical School, Boston, US (with Peter Park)</t>
+    <t>Postdoctoral fellow, Blavatnik Institute of Biomedical Informatics, Harvard Medical School, Boston, US (with Peter Park)</t>
   </si>
   <si>
     <t>Mattia Conte</t>
   </si>
   <si>
-    <t>Postdoctoral Fellow, Nicodemi lab, Naples University, Naples, IT</t>
+    <t>Postdoctoral fellow (Nicodemi lab), Naples University, Naples, IT</t>
   </si>
   <si>
     <t>Federico Billeci</t>
@@ -1253,7 +1294,7 @@
     <t>Chloe Tang</t>
   </si>
   <si>
-    <t>PhD Student, Rippe lab, DKFZ, Heidelberg, DE</t>
+    <t>PhD student, Rippe lab, DKFZ, Heidelberg, DE</t>
   </si>
   <si>
     <t>Rita Moldovan</t>
@@ -1286,7 +1327,7 @@
     <t>PhD / Postdoc</t>
   </si>
   <si>
-    <t>Postdoctoral Fellow, Inst. Biology Development, Marseille, FR (with Thomas Lecuit)</t>
+    <t>Postdoctoral fellow, Inst. Biology Development, Marseille, FR (with Thomas Lecuit)</t>
   </si>
   <si>
     <t>Cleis Battaglia</t>
@@ -1295,7 +1336,7 @@
     <t>2019–2020</t>
   </si>
   <si>
-    <t>PhD Student, Marenduzzo lab, Univ. Edinburgh, UK</t>
+    <t>PhD student, Marenduzzo lab, Univ. Edinburgh, UK</t>
   </si>
   <si>
     <t>Ana Miguel Fernandes</t>
@@ -1325,7 +1366,7 @@
     <t>Vahid Assimi</t>
   </si>
   <si>
-    <t>PhD Student, Hinsz lab, MPI Molecular Genetics, Berlin, DE</t>
+    <t>PhD student, Hinsz lab, MPI Molecular Genetics, Berlin, DE</t>
   </si>
   <si>
     <t>Konstantina Skourti-Stathaki</t>
@@ -1379,7 +1420,7 @@
     <t>2017</t>
   </si>
   <si>
-    <t>PhD Student, Kind lab, Hubrecht Institute, Utrecht, NL</t>
+    <t>PhD student, Kind lab, Hubrecht Institute, Utrecht, NL</t>
   </si>
   <si>
     <t>Daria Ivanova</t>
@@ -1391,7 +1432,7 @@
     <t>2013–2017</t>
   </si>
   <si>
-    <t>Postdoctoral Fellow, Crick Institute, London, UK (with James Briscoe)</t>
+    <t>Postdoctoral fellow, Crick Institute, London, UK (with James Briscoe)</t>
   </si>
   <si>
     <t>Joao Dias</t>
@@ -1469,6 +1510,9 @@
     <t>MRes / PhD / Postdoc</t>
   </si>
   <si>
+    <t>Career break</t>
+  </si>
+  <si>
     <t>Kedar Natarajan</t>
   </si>
   <si>
@@ -1526,7 +1570,7 @@
     <t>2007–2012</t>
   </si>
   <si>
-    <t>Senior Principal Scientist, Computational Biology, e-Therapeutics PLC, Oxford, UK</t>
+    <t>Senior Principal Scientist – Computational Biology, e-Therapeutics PLC, Oxford, UK</t>
   </si>
   <si>
     <t>Emily Brookes</t>
@@ -1562,7 +1606,7 @@
     <t>2003–2008</t>
   </si>
   <si>
-    <t>Professor; Centre Lead, Blizard Institute, Queen Mary University London, London, UK</t>
+    <t>Reader, Queen Mary University London, Blizard Institute, London UK</t>
   </si>
   <si>
     <t>Pippa Hadland (née Clarke)</t>
@@ -1625,9 +1669,6 @@
     <t>2002</t>
   </si>
   <si>
-    <t>Andrea Willemin</t>
-  </si>
-  <si>
     <t>Luna Zea-Redondo</t>
   </si>
   <si>
@@ -1640,49 +1681,22 @@
     <t>Ibai Irastorza-Azcarate</t>
   </si>
   <si>
-    <t>Page address</t>
-  </si>
-  <si>
     <t>Subtitle</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>Highlights</t>
   </si>
   <si>
-    <t>Figure image</t>
-  </si>
-  <si>
-    <t>Figure caption</t>
-  </si>
-  <si>
-    <t>Collaborators</t>
-  </si>
-  <si>
-    <t>Funding</t>
-  </si>
-  <si>
     <t>Genome Architecture Mapping</t>
   </si>
   <si>
-    <t>genome-architecture-mapping</t>
-  </si>
-  <si>
     <t>Ligation-free 3D genome mapping</t>
   </si>
   <si>
     <t>A ligation-free way to measure where every part of the genome sits relative to every other part — and, increasingly, on which allele and in which cell type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAM cryosections fixed nuclei into thin slices, sequences the DNA recovered from each slice, and infers contacts from which regions are repeatedly found together. Because it needs neither ligation nor cell dissociation, it reports multi-way contacts directly and works on tissue sections, on rare populations, and on small numbers of cells where ligation-based assays lose signal.
-Phasing. Reads that cross heterozygous SNPs can be assigned to the maternal or paternal chromosome, so the same slices yield two separate contact maps instead of an allele-averaged one. In SNP-dense hybrid genomes this resolves allele-specific compartments and domains, imprinted loci, the inactive and active X, and enhancer–promoter contacts that only one allele makes. The limit is coverage: each slice carries few informative SNPs, so we develop phasing-aware co-segregation models, phase-block imputation, and power estimates that state honestly how much of the genome is callable at a given SNP density.
-Modality. One GAM dataset carries several measurements at once. Co-segregation gives pairwise and higher-order contact frequencies; how often a locus is detected across slices gives an estimate of chromatin compaction; where a locus falls across apical and equatorial slices gives radial position relative to the nuclear periphery. immunoGAM adds an imaging modality, selecting nuclear profiles by marker expression so that contacts can be assigned to identified cell types in intact tissue. We also integrate these readouts with transcriptomic and chromatin-state data, and with polymer models that must satisfy all of them simultaneously.
-Method development runs alongside the biology: extending GAM to more cell types and tissues, raising throughput through multiplexed profile collection, and building the statistics needed to read three-way and higher-order contacts out of slice data.</t>
   </si>
   <si>
     <t xml:space="preserve">Ligation-free contact maps from cryosectioned nuclear profiles
@@ -1693,24 +1707,13 @@
 Open protocols, analysis pipelines, and published contact matrices</t>
   </si>
   <si>
-    <t>Figure 01 — from nuclear cryosections to phased, multi-modal contact maps</t>
-  </si>
-  <si>
     <t>Transcriptional regulation</t>
   </si>
   <si>
-    <t>transcriptional-regulation</t>
-  </si>
-  <si>
     <t>Chromatin state, polymerase activity, and genome folding</t>
   </si>
   <si>
     <t>How chromatin states and polymerase activity relate to the folding we measure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binding of transcription factors at regulatory sequences recruits chromatin remodellers and the transcription machinery. Polymerases may then transcribe immediately, or stay poised for later activation during differentiation, stress, or disease. We ask how these states map onto the physical organization of the genome: which contacts precede activation, which follow it, and which are maintained independently of output.
-Repression has its own architecture. Polycomb-marked genes form compact domains and contact each other over long distances, and we use phased and multi-way GAM data to ask whether these contacts are simultaneous hubs or pairwise events averaged across cells.
-The work combines genomics, imaging, and computational modelling. Models are judged by whether they reproduce contact frequency, compaction, and radial position together, and by whether they predict what happens to transcription when a contact is perturbed.</t>
   </si>
   <si>
     <t xml:space="preserve">RNA polymerase II states: poised, paused, and elongating
@@ -1719,24 +1722,13 @@
 Modelling that links contact data to regulatory outcome</t>
   </si>
   <si>
-    <t>Figure 02 — chromatin state and contact frequency</t>
-  </si>
-  <si>
     <t>Neuroepigenetics</t>
   </si>
   <si>
-    <t>neuroepigenetics</t>
-  </si>
-  <si>
     <t>Epigenetic regulation in sleep, memory, and addiction</t>
   </si>
   <si>
     <t>How neurons record a changing environment in chromatin, and what of that record persists.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neurons are post-mitotic and long-lived, so experience cannot be written into the genome by cell division. It is written into chromatin instead. Sleep pressure, learning, and drug exposure each drive an ordered transcriptional response — immediate-early genes first, then slower programmes that depend on enhancer activation and on contacts between those enhancers and their target promoters. We ask which of those changes decay with the stimulus and which outlast it.
-Cell type is the unit of analysis here. Neuronal and glial populations sit side by side in the same tissue with very different genome topologies, and bulk measurements average them away. immunoGAM lets us collect nuclear profiles from identified populations in situ, so contacts, compaction, and radial position can be compared across cell types, across developmental stages, and between control and disease models.
-Across sleep, memory, and addiction the question has the same shape: an experience changes transcription, and something in the chromatin of specific neurons keeps a trace of it. We are after the physical form of that trace.</t>
   </si>
   <si>
     <t xml:space="preserve">Cell-type-specific topologies in neurons and glia, and how they change during differentiation
@@ -1746,9 +1738,6 @@
 Durable transcriptional change in reward circuitry and addiction models</t>
   </si>
   <si>
-    <t>Figure 03 — experience-driven chromatin change in defined neuronal populations</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -1758,6 +1747,15 @@
     <t>Text</t>
   </si>
   <si>
+    <t>A single cocaine dose alters mouse brain cells</t>
+  </si>
+  <si>
+    <t>Researchers led by Ana Pombo have found that just one exposure to the drug can create changes in mouse brain cells that persist for at least two weeks. Their findings were presented at the Federation of European Neuroscience Societies Forum on July 7, 2026.</t>
+  </si>
+  <si>
+    <t>https://www.mdc-berlin.de/news/news/single-cocaine-dose-alters-mouse-brain-cells-3</t>
+  </si>
+  <si>
     <t>Lab</t>
   </si>
   <si>
@@ -1770,31 +1768,94 @@
     <t>Press</t>
   </si>
   <si>
-    <t>Named among Berlin's most important minds in science</t>
-  </si>
-  <si>
-    <t>Tagesspiegel included Ana Pombo in its 2025 list of one hundred figures in Berlin science.</t>
+    <t>Five Berlin-based leading minds honored</t>
+  </si>
+  <si>
+    <t>Five scientists from the Max Delbrück Center have been named among the 100 most important minds in Berlin science in 2025 by the newspaper Tagesspiegel: Simone Spuler, Clara Vázquez García, Thoralf Niendorf, Gabriele Schiattarella and Ana Pombo.</t>
+  </si>
+  <si>
+    <t>https://www.mdc-berlin.de/news/news/five-berlin-based-leading-minds-honored</t>
+  </si>
+  <si>
+    <t>Funding</t>
+  </si>
+  <si>
+    <t>Millions in funding for two Clusters of Excellence</t>
+  </si>
+  <si>
+    <t>The Max Delbrück Center is a partner in one newly awarded Berlin based Clusters of Excellence: ImmunoPreCept. NeuroCure has also won another round of funding. All researchers are working toward a common goal – to develop therapies that can intercept diseases on a molecular level.</t>
+  </si>
+  <si>
+    <t>https://www.mdc-berlin.de/news/press/millions-funding-two-clusters-excellence</t>
   </si>
   <si>
     <t>Award</t>
   </si>
   <si>
-    <t>Gottfried Wilhelm Leibniz Prize awarded by the DFG</t>
-  </si>
-  <si>
-    <t>The prize, announced by the German Research Foundation, carries 2.5 million euros in research funding.</t>
+    <t>Leibniz Prize awarded to Ana Pombo</t>
+  </si>
+  <si>
+    <t>The German Research Foundation (DFG) has announced that biochemist Ana Pombo from the Max Delbrück Center is among this year’s winners of the Gottfried Wilhelm Leibniz Prize. With a grant of €2.5 million, the Leibniz Prize is one of the highest endowed research prizes in Germany.</t>
+  </si>
+  <si>
+    <t>https://www.mdc-berlin.de/news/press/leibniz-prize-awarded-ana-pombo</t>
+  </si>
+  <si>
+    <t>Celebrating women in STEM</t>
+  </si>
+  <si>
+    <t>Watch our videos: Twelve women, twelve careers – one conclusion: women and girls who are passionate about science should just go for it and not let anyone stop them. Because if you keep going, no obstacle will be insurmountable.</t>
+  </si>
+  <si>
+    <t>https://www.mdc-berlin.de/news/news/celebrating-women-stem</t>
   </si>
   <si>
     <t>Paper</t>
   </si>
   <si>
-    <t>Multiplex-GAM published in Nature Methods</t>
-  </si>
-  <si>
-    <t>The scaled-up protocol shows that genome architecture mapping captures complex multi-way contacts that pairwise methods largely miss.</t>
-  </si>
-  <si>
-    <t>/publications</t>
+    <t>New tool uncovers complex genome interactions</t>
+  </si>
+  <si>
+    <t>Genome Architecture Mapping captures complex, multi-way interactions in the genome. This is different than the workhorse technique of 3D genomics, which sees mostly two-way contacts, finds a new study by a team led by Ana Pombo from the Max Delbrück Center, published in “Nature Methods”.</t>
+  </si>
+  <si>
+    <t>https://www.mdc-berlin.de/news/press/new-tool-uncovers-complex-genome-interactions</t>
+  </si>
+  <si>
+    <t>Cracking the chromatin code</t>
+  </si>
+  <si>
+    <t>Chromatin factors are involved in regulating gene expression. If they do not function properly, this can result in neurological impairments. Ana Pombo and Alexander Kukalev are now receiving almost €400,000 from the DFG for a research project that aims to shed more light on how these factors work.</t>
+  </si>
+  <si>
+    <t>https://www.mdc-berlin.de/news/news/cracking-chromatin-code</t>
+  </si>
+  <si>
+    <t>Genome folding in the mouse brain</t>
+  </si>
+  <si>
+    <t>A team led by MDC researcher Ana Pombo has deciphered the 3D structure of the genome in three cell types of the mouse brain. They not only discovered specific folding patterns but also found that very long genes almost completely lose their compact folded structure when most at work, as they report in “Nature”.</t>
+  </si>
+  <si>
+    <t>https://www.mdc-berlin.de/news/press/genome-folding-mouse-brain</t>
+  </si>
+  <si>
+    <t>MDC research funded by NIH award</t>
+  </si>
+  <si>
+    <t>A large grant under the NIH’s 4D Nucleome Program supports MDC scientist Ana Pombo’s work as a member of a multi-team consortium led by UC San Diego in the U.S. The team will investigate how DNA organizes inside cell nuclei and functions in space and time.</t>
+  </si>
+  <si>
+    <t>https://www.mdc-berlin.de/news/press/mdc-research-funded-nih-award</t>
+  </si>
+  <si>
+    <t>The art of DNA folding</t>
+  </si>
+  <si>
+    <t>Ana Pombo wants to understand the rules that govern our genome. This quest has led her to discover how important our genetic architecture is for the functioning of life. In the long term, she hopes her research will help understand diseases with complex origin such as autism and epilepsy.</t>
+  </si>
+  <si>
+    <t>https://www.mdc-berlin.de/news/news/ana-pombo-art-dna-folding</t>
   </si>
   <si>
     <t>Year</t>
@@ -1836,6 +1897,9 @@
     <t>649(8097), 759–776</t>
   </si>
   <si>
+    <t>10.1038/s41586-025-09890-3</t>
+  </si>
+  <si>
     <t>Haplotype-resolved genome architecture mapping uncovers pervasive structural heterogeneity between human homologous chromosomes</t>
   </si>
   <si>
@@ -1848,6 +1912,27 @@
     <t>10.64898/2026.06.16.732681</t>
   </si>
   <si>
+    <t>Stem cell differentiation disperses transcriptional clusters via a conserved surface-condensate trajectory</t>
+  </si>
+  <si>
+    <t>Klingberg, T., Wachter, I., Pancholi, A., Akyel, M., Gohar, Y., Kumar, P., et al., Fernandes, A. M., et al., Ferrai, C., Hilbert, L.</t>
+  </si>
+  <si>
+    <t>Advanced Science</t>
+  </si>
+  <si>
+    <t>10.1002/advs.75924</t>
+  </si>
+  <si>
+    <t>Extrachromosomal DNA micronucleation constrains tumour fitness and improves patient survival</t>
+  </si>
+  <si>
+    <t>Brückner, L., Xu, R., Tang, J., Gnanasekar, A., Herrmann, A., Wong, I. T. L., et al., Kukalev, A., et al., Herzog, S., et al., Pombo, A., et al., Henssen, A. G.</t>
+  </si>
+  <si>
+    <t>10.1101/2025.04.15.648906</t>
+  </si>
+  <si>
     <t>Specialised super-enhancer networks in stem cells and neurons</t>
   </si>
   <si>
@@ -1869,6 +1954,9 @@
     <t>122(32), e2504578122</t>
   </si>
   <si>
+    <t>10.1073/pnas.2504578122</t>
+  </si>
+  <si>
     <t>Extensive folding variability between homologous chromosomes in mammalian cells</t>
   </si>
   <si>
@@ -1884,6 +1972,18 @@
     <t>10.1038/s44320-025-00107-3</t>
   </si>
   <si>
+    <t>Loss of structural specificity in 3D genome organization upon viral infection is predicted by polymer physics</t>
+  </si>
+  <si>
+    <t>Fontana, A., Bianco, S., Tafuri, F., Esposito, A., Abraham, A., Conte, M., et al., Chiariello, A. M.</t>
+  </si>
+  <si>
+    <t>Journal of Chemical Physics</t>
+  </si>
+  <si>
+    <t>10.1063/5.0243454</t>
+  </si>
+  <si>
     <t>SRRM2 splicing factor modulates cell fate in early development</t>
   </si>
   <si>
@@ -1920,6 +2020,30 @@
     <t>10.1101/2024.05.10.593308</t>
   </si>
   <si>
+    <t>Transient stabilization of human cardiovascular progenitor cells from human pluripotent stem cells in vitro reflects stage-specific heart development in vivo</t>
+  </si>
+  <si>
+    <t>Bolesani, E., Bornhorst, D., Iyer, L. I., Zawada, D., Friese, N., Morgan, M., et al., Zweigerdt, R.</t>
+  </si>
+  <si>
+    <t>Cardiovascular Research</t>
+  </si>
+  <si>
+    <t>10.1093/cvr/cvae118</t>
+  </si>
+  <si>
+    <t>Multiscale modelling of chromatin 4D organization in SARS-CoV-2 infected cells</t>
+  </si>
+  <si>
+    <t>Chiariello, A. M., Abraham, A., Bianco, S., Esposito, A., Fontana, A., Vercellone, F., Conte, M., Nicodemi, M.</t>
+  </si>
+  <si>
+    <t>Nature Communications</t>
+  </si>
+  <si>
+    <t>10.1038/s41467-024-48370-6</t>
+  </si>
+  <si>
     <t>Research briefing</t>
   </si>
   <si>
@@ -2158,9 +2282,6 @@
   </si>
   <si>
     <t>Kar, G., Kim, J. K., Kolodziejczyk, A. A., Natarajan, K. N., Triglia, E. T., Mifsud, B., et al.</t>
-  </si>
-  <si>
-    <t>Nature Communications</t>
   </si>
   <si>
     <t>8(1), 36</t>
@@ -3558,7 +3679,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3573,40 +3694,40 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3614,27 +3735,29 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>467</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3642,27 +3765,27 @@
         <v>2026</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>440</v>
+        <v>469</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3670,55 +3793,55 @@
         <v>2026</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="F5" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>478</v>
+      </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3726,274 +3849,274 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>451</v>
+        <v>480</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>453</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>454</v>
+        <v>481</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>456</v>
+        <v>483</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F7" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>486</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2" t="s">
-        <v>459</v>
-      </c>
+      <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>460</v>
+        <v>487</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F8" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>491</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>441</v>
+        <v>494</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>466</v>
+        <v>495</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>467</v>
+        <v>496</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>468</v>
+        <v>497</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>469</v>
+        <v>498</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>500</v>
+      </c>
       <c r="K10" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>472</v>
+        <v>502</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>469</v>
+        <v>503</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>474</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>475</v>
+        <v>505</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F12" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>507</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>479</v>
+        <v>508</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>480</v>
+        <v>509</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F13" s="2"/>
+        <v>510</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>511</v>
+      </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>483</v>
+        <v>512</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>484</v>
+        <v>513</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="F14" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>515</v>
+      </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>488</v>
+        <v>517</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>489</v>
+        <v>518</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>490</v>
+        <v>519</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -4001,85 +4124,85 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>491</v>
+        <v>520</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>492</v>
+        <v>521</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>493</v>
+        <v>518</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F16" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>523</v>
+      </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>496</v>
+        <v>525</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>437</v>
+        <v>526</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>498</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>499</v>
+        <v>528</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>500</v>
+        <v>529</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>469</v>
+        <v>530</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>501</v>
+        <v>531</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -4087,27 +4210,27 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>503</v>
+        <v>533</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>505</v>
+        <v>535</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -4115,27 +4238,27 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>507</v>
+        <v>537</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>437</v>
+        <v>538</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>508</v>
+        <v>539</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -4143,27 +4266,27 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>509</v>
+        <v>540</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>510</v>
+        <v>541</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>511</v>
+        <v>542</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>512</v>
+        <v>543</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -4171,55 +4294,57 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>513</v>
+        <v>544</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>514</v>
+        <v>545</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>515</v>
+        <v>465</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F22" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>547</v>
+      </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -4227,27 +4352,27 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>522</v>
+        <v>552</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -4255,27 +4380,27 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -4283,27 +4408,27 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>531</v>
+        <v>561</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -4311,27 +4436,27 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>532</v>
+        <v>562</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>530</v>
+        <v>564</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>534</v>
+        <v>565</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -4339,27 +4464,27 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>535</v>
+        <v>566</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>452</v>
+        <v>568</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>537</v>
+        <v>569</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -4367,27 +4492,27 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>538</v>
+        <v>570</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>539</v>
+        <v>571</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>540</v>
+        <v>572</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -4395,27 +4520,27 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>543</v>
+        <v>575</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>544</v>
+        <v>576</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -4423,27 +4548,27 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>546</v>
+        <v>578</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>547</v>
+        <v>579</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>548</v>
+        <v>580</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -4451,27 +4576,27 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>551</v>
+        <v>579</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -4479,10 +4604,10 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4490,16 +4615,16 @@
         <v>2017</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>554</v>
+        <v>585</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>555</v>
+        <v>489</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -4507,10 +4632,10 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4518,16 +4643,16 @@
         <v>2017</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -4535,10 +4660,10 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4546,16 +4671,16 @@
         <v>2017</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -4563,10 +4688,10 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4574,16 +4699,16 @@
         <v>2017</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>462</v>
+        <v>514</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>566</v>
+        <v>596</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -4591,27 +4716,27 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>543</v>
+        <v>598</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -4619,27 +4744,27 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>570</v>
+        <v>601</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>571</v>
+        <v>602</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>437</v>
+        <v>603</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>572</v>
+        <v>604</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -4647,27 +4772,27 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>573</v>
+        <v>605</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>543</v>
+        <v>606</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>574</v>
+        <v>607</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>575</v>
+        <v>608</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -4675,27 +4800,27 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>576</v>
+        <v>609</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>577</v>
+        <v>610</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>578</v>
+        <v>465</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>579</v>
+        <v>611</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -4703,27 +4828,27 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>580</v>
+        <v>612</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>581</v>
+        <v>613</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>582</v>
+        <v>503</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>583</v>
+        <v>614</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -4731,27 +4856,27 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>584</v>
+        <v>615</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>452</v>
+        <v>616</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -4759,27 +4884,27 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>587</v>
+        <v>618</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>588</v>
+        <v>619</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>589</v>
+        <v>465</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>590</v>
+        <v>620</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -4787,27 +4912,27 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>592</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>593</v>
+        <v>622</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>594</v>
+        <v>623</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -4815,27 +4940,27 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>595</v>
+        <v>624</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>481</v>
+        <v>626</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>597</v>
+        <v>627</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -4843,27 +4968,27 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>598</v>
+        <v>628</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>599</v>
+        <v>629</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>555</v>
+        <v>630</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -4871,27 +4996,27 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>601</v>
+        <v>632</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>602</v>
+        <v>633</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -4899,27 +5024,27 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>604</v>
+        <v>635</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>605</v>
+        <v>636</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>607</v>
+        <v>638</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -4927,27 +5052,27 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>609</v>
+        <v>640</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>610</v>
+        <v>641</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>611</v>
+        <v>642</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -4955,27 +5080,27 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>613</v>
+        <v>644</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>614</v>
+        <v>530</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -4983,27 +5108,27 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>616</v>
+        <v>646</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>617</v>
+        <v>647</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>619</v>
+        <v>648</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -5011,27 +5136,27 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>620</v>
+        <v>649</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>621</v>
+        <v>650</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>622</v>
+        <v>564</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -5039,27 +5164,27 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>624</v>
+        <v>652</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>626</v>
+        <v>654</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -5067,27 +5192,27 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>630</v>
+        <v>658</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>631</v>
+        <v>659</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -5095,27 +5220,27 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>632</v>
+        <v>660</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>625</v>
+        <v>661</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>448</v>
+        <v>662</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>633</v>
+        <v>663</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -5123,27 +5248,27 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>634</v>
+        <v>664</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>635</v>
+        <v>665</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>636</v>
+        <v>666</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>637</v>
+        <v>667</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -5151,27 +5276,27 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>638</v>
+        <v>668</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>641</v>
+        <v>671</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -5179,27 +5304,27 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>642</v>
+        <v>672</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>643</v>
+        <v>673</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>555</v>
+        <v>674</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>644</v>
+        <v>675</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -5207,27 +5332,27 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>645</v>
+        <v>676</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>646</v>
+        <v>677</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>647</v>
+        <v>678</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>648</v>
+        <v>679</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -5235,27 +5360,27 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>650</v>
+        <v>673</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>610</v>
+        <v>484</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -5263,27 +5388,27 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>652</v>
+        <v>682</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>653</v>
+        <v>683</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>655</v>
+        <v>685</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -5291,27 +5416,27 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>656</v>
+        <v>686</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>657</v>
+        <v>687</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>462</v>
+        <v>688</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>658</v>
+        <v>689</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -5319,27 +5444,27 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>659</v>
+        <v>690</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>660</v>
+        <v>691</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>661</v>
+        <v>603</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>662</v>
+        <v>692</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -5347,27 +5472,27 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>663</v>
+        <v>693</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>664</v>
+        <v>694</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>578</v>
+        <v>695</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>665</v>
+        <v>696</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -5375,27 +5500,27 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>667</v>
+        <v>698</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>515</v>
+        <v>658</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>668</v>
+        <v>699</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
@@ -5403,10 +5528,10 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5414,16 +5539,16 @@
         <v>2010</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>669</v>
+        <v>700</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>670</v>
+        <v>701</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>671</v>
+        <v>702</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>672</v>
+        <v>703</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -5431,10 +5556,10 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5442,16 +5567,16 @@
         <v>2010</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>673</v>
+        <v>704</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>674</v>
+        <v>705</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>675</v>
+        <v>503</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>676</v>
+        <v>706</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -5459,10 +5584,10 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5470,16 +5595,16 @@
         <v>2010</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>677</v>
+        <v>707</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>678</v>
+        <v>708</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -5487,27 +5612,27 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>681</v>
+        <v>711</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>683</v>
+        <v>626</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>684</v>
+        <v>713</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -5515,27 +5640,27 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>685</v>
+        <v>714</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>639</v>
+        <v>715</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>686</v>
+        <v>564</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>687</v>
+        <v>716</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -5543,27 +5668,27 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>688</v>
+        <v>717</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>689</v>
+        <v>718</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>568</v>
+        <v>719</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -5571,27 +5696,27 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>691</v>
+        <v>721</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>692</v>
+        <v>722</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>693</v>
+        <v>723</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>694</v>
+        <v>724</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -5599,27 +5724,27 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>695</v>
+        <v>725</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>696</v>
+        <v>726</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>504</v>
+        <v>727</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>697</v>
+        <v>728</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -5627,27 +5752,27 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>698</v>
+        <v>729</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>699</v>
+        <v>730</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>701</v>
+        <v>732</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -5655,27 +5780,27 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>702</v>
+        <v>733</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>647</v>
+        <v>734</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>704</v>
+        <v>735</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -5683,27 +5808,27 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>705</v>
+        <v>736</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>706</v>
+        <v>737</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>578</v>
+        <v>616</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>707</v>
+        <v>738</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -5711,27 +5836,27 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>708</v>
+        <v>739</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>709</v>
+        <v>740</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>504</v>
+        <v>741</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>710</v>
+        <v>742</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -5739,27 +5864,27 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>711</v>
+        <v>743</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>712</v>
+        <v>744</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>713</v>
+        <v>553</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>714</v>
+        <v>745</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -5767,27 +5892,27 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>715</v>
+        <v>746</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>716</v>
+        <v>747</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>717</v>
+        <v>748</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>718</v>
+        <v>749</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -5795,27 +5920,27 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>719</v>
+        <v>750</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>720</v>
+        <v>751</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>721</v>
+        <v>695</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>722</v>
+        <v>752</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -5823,27 +5948,27 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>723</v>
+        <v>753</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>720</v>
+        <v>754</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>671</v>
+        <v>626</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>724</v>
+        <v>755</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -5851,27 +5976,27 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>725</v>
+        <v>756</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>726</v>
+        <v>757</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>610</v>
+        <v>553</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>727</v>
+        <v>758</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -5879,27 +6004,27 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>728</v>
+        <v>759</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>729</v>
+        <v>760</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>713</v>
+        <v>761</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>730</v>
+        <v>762</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -5907,27 +6032,27 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>731</v>
+        <v>763</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>732</v>
+        <v>764</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>686</v>
+        <v>765</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>733</v>
+        <v>766</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -5935,27 +6060,27 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>734</v>
+        <v>767</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>735</v>
+        <v>768</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>736</v>
+        <v>769</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>737</v>
+        <v>770</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -5963,27 +6088,27 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>738</v>
+        <v>771</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>739</v>
+        <v>768</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>740</v>
+        <v>719</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>741</v>
+        <v>772</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -5991,27 +6116,27 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>742</v>
+        <v>773</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>743</v>
+        <v>774</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>744</v>
+        <v>658</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>745</v>
+        <v>775</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -6019,27 +6144,27 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>746</v>
+        <v>776</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>747</v>
+        <v>777</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>610</v>
+        <v>761</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>748</v>
+        <v>778</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -6047,27 +6172,27 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>749</v>
+        <v>779</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>750</v>
+        <v>780</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>751</v>
+        <v>734</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>752</v>
+        <v>781</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -6075,27 +6200,27 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>753</v>
+        <v>782</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>754</v>
+        <v>783</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>700</v>
+        <v>784</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>755</v>
+        <v>785</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -6103,27 +6228,27 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>757</v>
+        <v>787</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>759</v>
+        <v>789</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -6131,27 +6256,27 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>760</v>
+        <v>790</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>761</v>
+        <v>791</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>762</v>
+        <v>792</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>763</v>
+        <v>793</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -6159,27 +6284,27 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>764</v>
+        <v>794</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>712</v>
+        <v>795</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>765</v>
+        <v>658</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>766</v>
+        <v>796</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -6187,10 +6312,10 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6198,16 +6323,16 @@
         <v>2003</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>767</v>
+        <v>797</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>768</v>
+        <v>798</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>762</v>
+        <v>799</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>769</v>
+        <v>800</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -6215,10 +6340,150 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -6253,28 +6518,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>770</v>
+        <v>818</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>771</v>
+        <v>819</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>772</v>
+        <v>820</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>773</v>
+        <v>821</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6282,23 +6547,23 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>774</v>
+        <v>822</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>775</v>
+        <v>823</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>776</v>
+        <v>824</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>777</v>
+        <v>825</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>778</v>
+        <v>826</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6306,23 +6571,23 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>774</v>
+        <v>822</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>775</v>
+        <v>823</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>776</v>
+        <v>824</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>779</v>
+        <v>827</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>778</v>
+        <v>826</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -6352,46 +6617,46 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>780</v>
+        <v>828</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>781</v>
+        <v>829</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>782</v>
+        <v>830</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>783</v>
+        <v>831</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>784</v>
+        <v>832</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>785</v>
+        <v>833</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>786</v>
+        <v>834</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -6419,52 +6684,52 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>787</v>
+        <v>835</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>789</v>
+        <v>837</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>790</v>
+        <v>838</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>791</v>
+        <v>839</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -6482,7 +6747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -6550,153 +6815,164 @@
         <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>93</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="2" t="s">
+    </row>
+    <row r="20" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="B20" s="2" t="s">
         <v>107</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -6707,7 +6983,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -6728,64 +7004,77 @@
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="C5" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>120</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -6796,7 +7085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -6806,301 +7095,297 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>153</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C24" s="2" t="s">
         <v>155</v>
       </c>
+      <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>156</v>
@@ -7109,7 +7394,35 @@
         <v>157</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -7141,90 +7454,90 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -7242,7 +7555,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -7256,365 +7569,499 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -7635,7 +8082,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -7647,1193 +8094,1180 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E34" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>342</v>
+      </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -8851,146 +9285,86 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="90" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="10" width="40" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="4" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:E1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="K2:K1000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="E2:E1000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9002,7 +9376,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" style="7" customWidth="1"/>
@@ -9014,96 +9388,240 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
-        <v>46175</v>
+        <v>46212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>413</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="E2" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>419</v>
+      </c>
       <c r="F2" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
-        <v>45799</v>
+        <v>46175</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
-        <v>45637</v>
+        <v>45938</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E4" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>426</v>
+      </c>
       <c r="F4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
+        <v>45799</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9">
+        <v>45637</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>45333</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9">
         <v>45096</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>44980</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9">
+        <v>44517</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9">
+        <v>44120</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>43766</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>127</v>
+      <c r="C12" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -11,77 +11,17 @@
     <sheet sheetId="5" name="Sites" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Members" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Alumni" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Research" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="News" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Publications" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Patents" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Join" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="Funders" state="visible" r:id="rId16"/>
+    <sheet sheetId="8" name="News" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Publications" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Patents" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Join" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Funders" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <t>Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <t>Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <t>Author list as it should appear, e.g. "Beagrie, R. A., Pombo, A.".</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <t>e.g. "21(7), 735–775".</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <t>e.g. 10.1038/s41586-021-04081-2 or the full https://doi.org/… address.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <t>"yes" to show it on the homepage and mark it as featured.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0">
-      <text>
-        <r>
-          <t>Set to "no" to hide this row on the website without deleting it.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
@@ -126,7 +66,7 @@
 </comments>
 </file>
 
-<file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
@@ -150,7 +90,7 @@
 </comments>
 </file>
 
-<file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
@@ -391,51 +331,6 @@
     <comment ref="A1" authorId="0">
       <text>
         <r>
-          <t>Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <t>Short subtitle shown under the title.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <t>One or two sentences about this area.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <t>Bullet points, one per line inside the cell.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <t>Set to "no" to hide this row on the website without deleting it.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
           <t>Date of the news item, e.g. 2026-06-02. Required.</t>
         </r>
       </text>
@@ -472,8 +367,67 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>Author list as it should appear, e.g. "Beagrie, R. A., Pombo, A.".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>e.g. "21(7), 735–775".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>e.g. 10.1038/s41586-021-04081-2 or the full https://doi.org/… address.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <t>"yes" to show it on the homepage and mark it as featured.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <t>Set to "no" to hide this row on the website without deleting it.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="821">
   <si>
     <t>Lab website content</t>
   </si>
@@ -590,12 +544,6 @@
   </si>
   <si>
     <t>Former members. The website sorts them by most recent year automatically.</t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Research areas, shown as sections of the Research page in this order.</t>
   </si>
   <si>
     <t>News</t>
@@ -724,18 +672,7 @@
 We have developed Genome Architecture Mapping (GAM), an orthogonal 3D genome folding mapping technology which yields fine maps of chromatin contacts from small cell numbers (500−1000), and is uniquely powerful to quantify different metrics of 3D genome structure, such as multiway contacts and chromatin melting. With immuno-GAM, we introduced the selection of cell types within complex tissues to enable the application of GAM in rare cells, such as dopaminergic neurons in the midbrain. GAM is an inherently suited platform for multimodal molecular phenotyping of biological samples, from genome sequence and 3D structure, to transcript and protein quantification. As a first step towards GAM multimodality, we have developed Oligo-Seq, a novel approach to detect minute amounts of specific RNA sequences within thin tissue cryosections, as used for GAM. We currently develop the application of Oligo-seq in spatial transcriptomics, especially in archival clinical samples (e.g. FFPE). By further developing multimodal integration of 3D genome topology, with the abundance of specific regulatory factors and gene expression, at the single-cell level, we aim to extract dynamic states of gene regulation and cause-effect relationships that connect 3D genome structure with gene expression. Ultimately, we seek to advance the interpretability of the linear genome sequence, to gain a deeper understanding of 3D genome regulation mechanisms in gene expression, and to advance their predictability.</t>
   </si>
   <si>
-    <t>Main text of the Research page. The first paragraph is also shown on the homepage.</t>
-  </si>
-  <si>
-    <t>Research themes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genome Architecture Mapping
-Transcription and chromatin states
-Genome folding in disease</t>
-  </si>
-  <si>
-    <t>Short theme names shown as cards on the Research page. One per line.</t>
+    <t>The Research page text. The first paragraph is also shown on the homepage.</t>
   </si>
   <si>
     <t>Team introduction</t>
@@ -1681,63 +1618,6 @@
     <t>Ibai Irastorza-Azcarate</t>
   </si>
   <si>
-    <t>Subtitle</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>Highlights</t>
-  </si>
-  <si>
-    <t>Genome Architecture Mapping</t>
-  </si>
-  <si>
-    <t>Ligation-free 3D genome mapping</t>
-  </si>
-  <si>
-    <t>A ligation-free way to measure where every part of the genome sits relative to every other part — and, increasingly, on which allele and in which cell type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ligation-free contact maps from cryosectioned nuclear profiles
-Haplotype phasing: allele-resolved domains, compartments, and enhancer–promoter contacts
-Multi-way contacts among active genes, enhancers, and super-enhancers
-One experiment, several readouts: contact frequency, chromatin compaction, radial position
-immunoGAM in tissue sections and rare cell populations
-Open protocols, analysis pipelines, and published contact matrices</t>
-  </si>
-  <si>
-    <t>Transcriptional regulation</t>
-  </si>
-  <si>
-    <t>Chromatin state, polymerase activity, and genome folding</t>
-  </si>
-  <si>
-    <t>How chromatin states and polymerase activity relate to the folding we measure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RNA polymerase II states: poised, paused, and elongating
-Polycomb domains and repressive chromatin in three dimensions
-Enhancer–promoter communication and super-enhancer hubs
-Modelling that links contact data to regulatory outcome</t>
-  </si>
-  <si>
-    <t>Neuroepigenetics</t>
-  </si>
-  <si>
-    <t>Epigenetic regulation in sleep, memory, and addiction</t>
-  </si>
-  <si>
-    <t>How neurons record a changing environment in chromatin, and what of that record persists.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cell-type-specific topologies in neurons and glia, and how they change during differentiation
-Activity-dependent transcription: immediate-early genes, enhancer activation, and induced contacts
-Sleep–wake and circadian control of chromatin state and transcription
-What persists in chromatin after learning, and for how long
-Durable transcriptional change in reward circuitry and addiction models</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -1745,6 +1625,9 @@
   </si>
   <si>
     <t>Text</t>
+  </si>
+  <si>
+    <t>Research</t>
   </si>
   <si>
     <t>A single cocaine dose alters mouse brain cells</t>
@@ -3450,7 +3333,7 @@
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3663,14 +3546,6 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3678,2831 +3553,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L99"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>2025</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>2024</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>2023</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>2018</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>2018</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>2017</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L54" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L55" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>2013</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
-        <v>2011</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>2011</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L69" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
-      <c r="K70" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L71" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>2010</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L73" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
-        <v>2009</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
-      <c r="K74" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L74" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <v>2009</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
-      <c r="K75" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L75" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>2009</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
-        <v>2009</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>741</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>2008</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
-        <v>2008</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
-        <v>2008</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
-        <v>2007</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
-        <v>2007</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L82" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>2007</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
-      <c r="K83" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
-        <v>2007</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
-        <v>2007</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>767</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
-        <v>2006</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
-        <v>2006</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L87" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
-        <v>2006</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
-        <v>2005</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
-        <v>2005</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
-        <v>2004</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L91" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
-        <v>2004</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L92" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <v>2004</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L93" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L96" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
-        <v>2003</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:L1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Featured" error="&quot;yes&quot; to show it on the homepage and mark it as featured." sqref="K2:K1000">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="L2:L1000">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -6518,28 +3568,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>819</v>
+        <v>800</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>820</v>
+        <v>801</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6547,23 +3597,23 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>822</v>
+        <v>803</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>823</v>
+        <v>804</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>824</v>
+        <v>805</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>825</v>
+        <v>806</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6571,23 +3621,23 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>822</v>
+        <v>803</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>823</v>
+        <v>804</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>824</v>
+        <v>805</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>827</v>
+        <v>808</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -6606,7 +3656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -6617,46 +3667,46 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>828</v>
+        <v>809</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>829</v>
+        <v>810</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>830</v>
+        <v>811</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>832</v>
+        <v>813</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>833</v>
+        <v>814</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>834</v>
+        <v>815</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -6672,7 +3722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -6684,52 +3734,52 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>835</v>
+        <v>816</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>836</v>
+        <v>817</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>837</v>
+        <v>818</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>838</v>
+        <v>819</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>839</v>
+        <v>820</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -6747,7 +3797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -6757,222 +3807,211 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -6993,88 +4032,88 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -7095,334 +4134,334 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -7454,90 +4493,90 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -7569,499 +4608,499 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="H1" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -8094,1180 +5133,1180 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -9285,97 +6324,6 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="4" width="70" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E1"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="E2:E1000">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -9388,22 +6336,22 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9411,19 +6359,19 @@
         <v>46212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>397</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9431,17 +6379,17 @@
         <v>46175</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9449,19 +6397,19 @@
         <v>45938</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9469,19 +6417,19 @@
         <v>45799</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9489,19 +6437,19 @@
         <v>45637</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9509,19 +6457,19 @@
         <v>45333</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9529,19 +6477,19 @@
         <v>45096</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9549,19 +6497,19 @@
         <v>44980</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9569,19 +6517,19 @@
         <v>44517</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9589,19 +6537,19 @@
         <v>44120</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9609,19 +6557,19 @@
         <v>43766</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -9635,4 +6583,2829 @@
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L99"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>2013</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>2009</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>2008</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>2006</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>2005</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>2004</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L1"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Featured" error="&quot;yes&quot; to show it on the homepage and mark it as featured." sqref="K2:K1000">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="L2:L1000">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -15,7 +15,6 @@
     <sheet sheetId="9" name="Publications" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="Patents" state="visible" r:id="rId13"/>
     <sheet sheetId="11" name="Join" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="Funders" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -80,37 +79,6 @@
       </text>
     </comment>
     <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <t>Set to "no" to hide this row on the website without deleting it.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <t>Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <t>Optional file name of a logo in public/images/funders, or a web address. The name is shown if blank.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
       <text>
         <r>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
@@ -427,7 +395,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="811">
   <si>
     <t>Lab website content</t>
   </si>
@@ -495,10 +463,10 @@
     <t>Wrap words in double stars: **like this**.</t>
   </si>
   <si>
-    <t>Photos and logos</t>
-  </si>
-  <si>
-    <t>Upload the image to public/images/people (or public/images/funders for logos) on GitHub, then type just its file name, e.g. "jane-doe.jpg".</t>
+    <t>Photos</t>
+  </si>
+  <si>
+    <t>Upload the photo to public/images/people on GitHub, then type just its file name, e.g. "jane-doe.jpg".</t>
   </si>
   <si>
     <t>Column help</t>
@@ -568,12 +536,6 @@
   </si>
   <si>
     <t>Sections of the Join page. The contact email is added at the end automatically.</t>
-  </si>
-  <si>
-    <t>Funders</t>
-  </si>
-  <si>
-    <t>Organisations shown on the Support page.</t>
   </si>
   <si>
     <t>Setting</t>
@@ -738,15 +700,6 @@
     <t>Text at the top of the Join page.</t>
   </si>
   <si>
-    <t>Support introduction</t>
-  </si>
-  <si>
-    <t>We gratefully acknowledge the support of the following organizations.</t>
-  </si>
-  <si>
-    <t>Text at the top of the Support (funders) page.</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -2882,21 +2835,6 @@
   </si>
   <si>
     <t>Undergraduates interested in a research experience in our lab should be willing to commit at least 10 hours per week to research.</t>
-  </si>
-  <si>
-    <t>Logo</t>
-  </si>
-  <si>
-    <t>https://www.jhu.edu</t>
-  </si>
-  <si>
-    <t>https://www.mdc-berlin.de</t>
-  </si>
-  <si>
-    <t>Deutsche Forschungsgemeinschaft (DFG)</t>
-  </si>
-  <si>
-    <t>https://www.dfg.de</t>
   </si>
 </sst>
 </file>
@@ -3333,7 +3271,7 @@
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3536,14 +3474,6 @@
       </c>
       <c r="B29" s="2" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3568,28 +3498,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3597,23 +3527,23 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3621,23 +3551,23 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>808</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3667,46 +3597,46 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3722,82 +3652,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:D1"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="D2:D1000">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3807,211 +3664,200 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>80</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4032,88 +3878,88 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -4134,334 +3980,334 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4493,90 +4339,90 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -4608,499 +4454,499 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="H1" s="4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -5133,1180 +4979,1180 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -6336,22 +6182,22 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6359,19 +6205,19 @@
         <v>46212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6379,17 +6225,17 @@
         <v>46175</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6397,19 +6243,19 @@
         <v>45938</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6417,19 +6263,19 @@
         <v>45799</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6437,19 +6283,19 @@
         <v>45637</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6457,19 +6303,19 @@
         <v>45333</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6477,19 +6323,19 @@
         <v>45096</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6497,19 +6343,19 @@
         <v>44980</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6517,19 +6363,19 @@
         <v>44517</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6537,19 +6383,19 @@
         <v>44120</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6557,19 +6403,19 @@
         <v>43766</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -6602,40 +6448,40 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>443</v>
-      </c>
       <c r="L1" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6643,29 +6489,29 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6673,27 +6519,27 @@
         <v>2026</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6701,27 +6547,27 @@
         <v>2026</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6729,27 +6575,27 @@
         <v>2026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6757,27 +6603,27 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6785,29 +6631,29 @@
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6815,29 +6661,29 @@
         <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6845,27 +6691,27 @@
         <v>2025</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6873,29 +6719,29 @@
         <v>2024</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6903,16 +6749,16 @@
         <v>2024</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -6920,10 +6766,10 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6931,27 +6777,27 @@
         <v>2024</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6959,27 +6805,27 @@
         <v>2024</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6987,27 +6833,27 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7015,16 +6861,16 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -7032,10 +6878,10 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7043,29 +6889,29 @@
         <v>2023</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7073,16 +6919,16 @@
         <v>2023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -7090,10 +6936,10 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7101,16 +6947,16 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -7118,10 +6964,10 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7129,16 +6975,16 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -7146,10 +6992,10 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7157,16 +7003,16 @@
         <v>2022</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -7174,10 +7020,10 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7185,16 +7031,16 @@
         <v>2021</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -7202,10 +7048,10 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7213,29 +7059,29 @@
         <v>2021</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7243,16 +7089,16 @@
         <v>2021</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -7260,10 +7106,10 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7271,16 +7117,16 @@
         <v>2021</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -7288,10 +7134,10 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7299,16 +7145,16 @@
         <v>2020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -7316,10 +7162,10 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7327,16 +7173,16 @@
         <v>2020</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -7344,10 +7190,10 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7355,16 +7201,16 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -7372,10 +7218,10 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7383,16 +7229,16 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -7400,10 +7246,10 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7411,16 +7257,16 @@
         <v>2019</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -7428,10 +7274,10 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7439,16 +7285,16 @@
         <v>2019</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -7456,10 +7302,10 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7467,16 +7313,16 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -7484,10 +7330,10 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7495,16 +7341,16 @@
         <v>2018</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -7512,10 +7358,10 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7523,16 +7369,16 @@
         <v>2017</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -7540,10 +7386,10 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7551,16 +7397,16 @@
         <v>2017</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -7568,10 +7414,10 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7579,16 +7425,16 @@
         <v>2017</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -7596,10 +7442,10 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7607,16 +7453,16 @@
         <v>2017</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -7624,10 +7470,10 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7635,16 +7481,16 @@
         <v>2017</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -7652,10 +7498,10 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7663,16 +7509,16 @@
         <v>2017</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -7680,10 +7526,10 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7691,16 +7537,16 @@
         <v>2017</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -7708,10 +7554,10 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7719,16 +7565,16 @@
         <v>2017</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -7736,10 +7582,10 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7747,16 +7593,16 @@
         <v>2017</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -7764,10 +7610,10 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7775,16 +7621,16 @@
         <v>2016</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -7792,10 +7638,10 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7803,16 +7649,16 @@
         <v>2016</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -7820,10 +7666,10 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7831,16 +7677,16 @@
         <v>2016</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -7848,10 +7694,10 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7859,16 +7705,16 @@
         <v>2016</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -7876,10 +7722,10 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7887,16 +7733,16 @@
         <v>2015</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -7904,10 +7750,10 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7915,16 +7761,16 @@
         <v>2015</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -7932,10 +7778,10 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7943,16 +7789,16 @@
         <v>2015</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -7960,10 +7806,10 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7971,16 +7817,16 @@
         <v>2015</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -7988,10 +7834,10 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7999,16 +7845,16 @@
         <v>2015</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -8016,10 +7862,10 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8027,16 +7873,16 @@
         <v>2014</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -8044,10 +7890,10 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8055,16 +7901,16 @@
         <v>2014</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -8072,10 +7918,10 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8083,16 +7929,16 @@
         <v>2014</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -8100,10 +7946,10 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8111,16 +7957,16 @@
         <v>2014</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -8128,10 +7974,10 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8139,16 +7985,16 @@
         <v>2013</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -8156,10 +8002,10 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8167,16 +8013,16 @@
         <v>2013</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -8184,10 +8030,10 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8195,16 +8041,16 @@
         <v>2013</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -8212,10 +8058,10 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8223,16 +8069,16 @@
         <v>2013</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -8240,10 +8086,10 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8251,16 +8097,16 @@
         <v>2012</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -8268,10 +8114,10 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8279,16 +8125,16 @@
         <v>2012</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -8296,10 +8142,10 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8307,16 +8153,16 @@
         <v>2012</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -8324,10 +8170,10 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8335,16 +8181,16 @@
         <v>2012</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -8352,10 +8198,10 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8363,16 +8209,16 @@
         <v>2012</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -8380,10 +8226,10 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8391,16 +8237,16 @@
         <v>2011</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -8408,10 +8254,10 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8419,16 +8265,16 @@
         <v>2011</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
@@ -8436,10 +8282,10 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8447,16 +8293,16 @@
         <v>2010</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -8464,10 +8310,10 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8475,16 +8321,16 @@
         <v>2010</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -8492,10 +8338,10 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8503,16 +8349,16 @@
         <v>2010</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -8520,10 +8366,10 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8531,16 +8377,16 @@
         <v>2010</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -8548,10 +8394,10 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8559,16 +8405,16 @@
         <v>2010</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -8576,10 +8422,10 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8587,16 +8433,16 @@
         <v>2010</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -8604,10 +8450,10 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8615,16 +8461,16 @@
         <v>2010</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -8632,10 +8478,10 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8643,16 +8489,16 @@
         <v>2010</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -8660,10 +8506,10 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8671,16 +8517,16 @@
         <v>2009</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -8688,10 +8534,10 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8699,16 +8545,16 @@
         <v>2009</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -8716,10 +8562,10 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8727,16 +8573,16 @@
         <v>2009</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -8744,10 +8590,10 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8755,16 +8601,16 @@
         <v>2009</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -8772,10 +8618,10 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8783,16 +8629,16 @@
         <v>2008</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -8800,10 +8646,10 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8811,16 +8657,16 @@
         <v>2008</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -8828,10 +8674,10 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8839,16 +8685,16 @@
         <v>2008</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -8856,10 +8702,10 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8867,16 +8713,16 @@
         <v>2007</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -8884,10 +8730,10 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8895,16 +8741,16 @@
         <v>2007</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -8912,10 +8758,10 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8923,16 +8769,16 @@
         <v>2007</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -8940,10 +8786,10 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8951,16 +8797,16 @@
         <v>2007</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -8968,10 +8814,10 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8979,16 +8825,16 @@
         <v>2007</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -8996,10 +8842,10 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9007,16 +8853,16 @@
         <v>2006</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -9024,10 +8870,10 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9035,16 +8881,16 @@
         <v>2006</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -9052,10 +8898,10 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9063,16 +8909,16 @@
         <v>2006</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -9080,10 +8926,10 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9091,16 +8937,16 @@
         <v>2005</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -9108,10 +8954,10 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9119,16 +8965,16 @@
         <v>2005</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -9136,10 +8982,10 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9147,16 +8993,16 @@
         <v>2004</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -9164,10 +9010,10 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9175,16 +9021,16 @@
         <v>2004</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -9192,10 +9038,10 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9203,16 +9049,16 @@
         <v>2004</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -9220,10 +9066,10 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9231,16 +9077,16 @@
         <v>2003</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -9248,10 +9094,10 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9259,16 +9105,16 @@
         <v>2003</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -9276,10 +9122,10 @@
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9287,16 +9133,16 @@
         <v>2003</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -9304,10 +9150,10 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9315,16 +9161,16 @@
         <v>2003</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -9332,10 +9178,10 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="98" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9343,16 +9189,16 @@
         <v>2003</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -9360,10 +9206,10 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9371,16 +9217,16 @@
         <v>2003</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -9388,10 +9234,10 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -395,7 +395,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="817">
   <si>
     <t>Lab website content</t>
   </si>
@@ -581,6 +581,24 @@
   </si>
   <si>
     <t>The large sentence at the top of the homepage.</t>
+  </si>
+  <si>
+    <t>Homepage image</t>
+  </si>
+  <si>
+    <t>oprm1-contact-map.png</t>
+  </si>
+  <si>
+    <t>Picture beside the headline: a file name in public/images/site (e.g. "oprm1-contact-map.png") or a web address. Leave blank for no picture.</t>
+  </si>
+  <si>
+    <t>Homepage image caption</t>
+  </si>
+  <si>
+    <t>3D genome structure at the Oprm1 locus in dopamine neurons, mapped by immunoGAM ([Szabó et al., 2024](https://doi.org/10.1101/2024.05.10.593308))</t>
+  </si>
+  <si>
+    <t>Short caption under the homepage picture. Links like [Szabó et al., 2024](https://doi.org/…) work.</t>
   </si>
   <si>
     <t>Homepage introduction</t>
@@ -3498,28 +3516,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3527,23 +3545,23 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3551,23 +3569,23 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3597,46 +3615,46 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>805</v>
+        <v>811</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>806</v>
+        <v>812</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>807</v>
+        <v>813</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>810</v>
+        <v>816</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3654,7 +3672,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3722,40 +3740,40 @@
         <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>71</v>
@@ -3858,6 +3876,28 @@
       </c>
       <c r="C18" s="6" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3889,77 +3929,77 @@
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -3980,334 +4020,334 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -4339,90 +4379,90 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -4454,499 +4494,499 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -4979,1180 +5019,1180 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>270</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -6182,22 +6222,22 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6205,19 +6245,19 @@
         <v>46212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6225,17 +6265,17 @@
         <v>46175</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6243,19 +6283,19 @@
         <v>45938</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6263,19 +6303,19 @@
         <v>45799</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6283,19 +6323,19 @@
         <v>45637</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6303,19 +6343,19 @@
         <v>45333</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6323,19 +6363,19 @@
         <v>45096</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6343,19 +6383,19 @@
         <v>44980</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6363,19 +6403,19 @@
         <v>44517</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6383,19 +6423,19 @@
         <v>44120</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6403,19 +6443,19 @@
         <v>43766</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -6448,40 +6488,40 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6489,29 +6529,29 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6519,27 +6559,27 @@
         <v>2026</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6547,27 +6587,27 @@
         <v>2026</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6575,27 +6615,27 @@
         <v>2026</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6603,27 +6643,27 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6631,29 +6671,29 @@
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6661,29 +6701,29 @@
         <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6691,27 +6731,27 @@
         <v>2025</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6719,29 +6759,29 @@
         <v>2024</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6749,16 +6789,16 @@
         <v>2024</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -6766,10 +6806,10 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6777,27 +6817,27 @@
         <v>2024</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6805,27 +6845,27 @@
         <v>2024</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6833,27 +6873,27 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6861,16 +6901,16 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -6878,10 +6918,10 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6889,29 +6929,29 @@
         <v>2023</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6919,16 +6959,16 @@
         <v>2023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -6936,10 +6976,10 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6947,16 +6987,16 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -6964,10 +7004,10 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6975,16 +7015,16 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -6992,10 +7032,10 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7003,16 +7043,16 @@
         <v>2022</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -7020,10 +7060,10 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7031,16 +7071,16 @@
         <v>2021</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -7048,10 +7088,10 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7059,29 +7099,29 @@
         <v>2021</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7089,16 +7129,16 @@
         <v>2021</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -7106,10 +7146,10 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7117,16 +7157,16 @@
         <v>2021</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -7134,10 +7174,10 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7145,16 +7185,16 @@
         <v>2020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -7162,10 +7202,10 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7173,16 +7213,16 @@
         <v>2020</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -7190,10 +7230,10 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7201,16 +7241,16 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -7218,10 +7258,10 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7229,16 +7269,16 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -7246,10 +7286,10 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7257,16 +7297,16 @@
         <v>2019</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -7274,10 +7314,10 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7285,16 +7325,16 @@
         <v>2019</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -7302,10 +7342,10 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7313,16 +7353,16 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -7330,10 +7370,10 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7341,16 +7381,16 @@
         <v>2018</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -7358,10 +7398,10 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7369,16 +7409,16 @@
         <v>2017</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -7386,10 +7426,10 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7397,16 +7437,16 @@
         <v>2017</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -7414,10 +7454,10 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7425,16 +7465,16 @@
         <v>2017</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -7442,10 +7482,10 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7453,16 +7493,16 @@
         <v>2017</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -7470,10 +7510,10 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7481,16 +7521,16 @@
         <v>2017</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -7498,10 +7538,10 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7509,16 +7549,16 @@
         <v>2017</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -7526,10 +7566,10 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7537,16 +7577,16 @@
         <v>2017</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -7554,10 +7594,10 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7565,16 +7605,16 @@
         <v>2017</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -7582,10 +7622,10 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7593,16 +7633,16 @@
         <v>2017</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -7610,10 +7650,10 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7621,16 +7661,16 @@
         <v>2016</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -7638,10 +7678,10 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7649,16 +7689,16 @@
         <v>2016</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -7666,10 +7706,10 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7677,16 +7717,16 @@
         <v>2016</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -7694,10 +7734,10 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7705,16 +7745,16 @@
         <v>2016</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -7722,10 +7762,10 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7733,16 +7773,16 @@
         <v>2015</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -7750,10 +7790,10 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7761,16 +7801,16 @@
         <v>2015</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -7778,10 +7818,10 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7789,16 +7829,16 @@
         <v>2015</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -7806,10 +7846,10 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7817,16 +7857,16 @@
         <v>2015</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -7834,10 +7874,10 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7845,16 +7885,16 @@
         <v>2015</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -7862,10 +7902,10 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7873,16 +7913,16 @@
         <v>2014</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -7890,10 +7930,10 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7901,16 +7941,16 @@
         <v>2014</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -7918,10 +7958,10 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7929,16 +7969,16 @@
         <v>2014</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -7946,10 +7986,10 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7957,16 +7997,16 @@
         <v>2014</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -7974,10 +8014,10 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7985,16 +8025,16 @@
         <v>2013</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -8002,10 +8042,10 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8013,16 +8053,16 @@
         <v>2013</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -8030,10 +8070,10 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8041,16 +8081,16 @@
         <v>2013</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -8058,10 +8098,10 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8069,16 +8109,16 @@
         <v>2013</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -8086,10 +8126,10 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8097,16 +8137,16 @@
         <v>2012</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -8114,10 +8154,10 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8125,16 +8165,16 @@
         <v>2012</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -8142,10 +8182,10 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8153,16 +8193,16 @@
         <v>2012</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -8170,10 +8210,10 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8181,16 +8221,16 @@
         <v>2012</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -8198,10 +8238,10 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8209,16 +8249,16 @@
         <v>2012</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -8226,10 +8266,10 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8237,16 +8277,16 @@
         <v>2011</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -8254,10 +8294,10 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8265,16 +8305,16 @@
         <v>2011</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
@@ -8282,10 +8322,10 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8293,16 +8333,16 @@
         <v>2010</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -8310,10 +8350,10 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8321,16 +8361,16 @@
         <v>2010</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -8338,10 +8378,10 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8349,16 +8389,16 @@
         <v>2010</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -8366,10 +8406,10 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8377,16 +8417,16 @@
         <v>2010</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -8394,10 +8434,10 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8405,16 +8445,16 @@
         <v>2010</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -8422,10 +8462,10 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8433,16 +8473,16 @@
         <v>2010</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -8450,10 +8490,10 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8461,16 +8501,16 @@
         <v>2010</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -8478,10 +8518,10 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8489,16 +8529,16 @@
         <v>2010</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -8506,10 +8546,10 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8517,16 +8557,16 @@
         <v>2009</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -8534,10 +8574,10 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8545,16 +8585,16 @@
         <v>2009</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -8562,10 +8602,10 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8573,16 +8613,16 @@
         <v>2009</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -8590,10 +8630,10 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8601,16 +8641,16 @@
         <v>2009</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -8618,10 +8658,10 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8629,16 +8669,16 @@
         <v>2008</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -8646,10 +8686,10 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8657,16 +8697,16 @@
         <v>2008</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -8674,10 +8714,10 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8685,16 +8725,16 @@
         <v>2008</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -8702,10 +8742,10 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8713,16 +8753,16 @@
         <v>2007</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -8730,10 +8770,10 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8741,16 +8781,16 @@
         <v>2007</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -8758,10 +8798,10 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8769,16 +8809,16 @@
         <v>2007</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -8786,10 +8826,10 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8797,16 +8837,16 @@
         <v>2007</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -8814,10 +8854,10 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8825,16 +8865,16 @@
         <v>2007</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -8842,10 +8882,10 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8853,16 +8893,16 @@
         <v>2006</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -8870,10 +8910,10 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8881,16 +8921,16 @@
         <v>2006</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -8898,10 +8938,10 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8909,16 +8949,16 @@
         <v>2006</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -8926,10 +8966,10 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8937,16 +8977,16 @@
         <v>2005</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -8954,10 +8994,10 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8965,16 +9005,16 @@
         <v>2005</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -8982,10 +9022,10 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8993,16 +9033,16 @@
         <v>2004</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -9010,10 +9050,10 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9021,16 +9061,16 @@
         <v>2004</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -9038,10 +9078,10 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9049,16 +9089,16 @@
         <v>2004</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -9066,10 +9106,10 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9077,16 +9117,16 @@
         <v>2003</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -9094,10 +9134,10 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9105,16 +9145,16 @@
         <v>2003</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -9122,10 +9162,10 @@
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9133,16 +9173,16 @@
         <v>2003</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -9150,10 +9190,10 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9161,16 +9201,16 @@
         <v>2003</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -9178,10 +9218,10 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="98" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9189,16 +9229,16 @@
         <v>2003</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -9206,10 +9246,10 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9217,16 +9257,16 @@
         <v>2003</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="C99" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>786</v>
-      </c>
       <c r="E99" s="2" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -9234,10 +9274,10 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -395,7 +395,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="811">
   <si>
     <t>Lab website content</t>
   </si>
@@ -581,24 +581,6 @@
   </si>
   <si>
     <t>The large sentence at the top of the homepage.</t>
-  </si>
-  <si>
-    <t>Homepage image</t>
-  </si>
-  <si>
-    <t>oprm1-contact-map.png</t>
-  </si>
-  <si>
-    <t>Picture beside the headline: a file name in public/images/site (e.g. "oprm1-contact-map.png") or a web address. Leave blank for no picture.</t>
-  </si>
-  <si>
-    <t>Homepage image caption</t>
-  </si>
-  <si>
-    <t>3D genome structure at the Oprm1 locus in dopamine neurons, mapped by immunoGAM ([Szabó et al., 2024](https://doi.org/10.1101/2024.05.10.593308))</t>
-  </si>
-  <si>
-    <t>Short caption under the homepage picture. Links like [Szabó et al., 2024](https://doi.org/…) work.</t>
   </si>
   <si>
     <t>Homepage introduction</t>
@@ -3516,28 +3498,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3545,23 +3527,23 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3569,23 +3551,23 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3615,46 +3597,46 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3672,7 +3654,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3740,40 +3722,40 @@
         <v>62</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>71</v>
@@ -3876,28 +3858,6 @@
       </c>
       <c r="C18" s="6" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3929,77 +3889,77 @@
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -4020,334 +3980,334 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="C25" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4379,90 +4339,90 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -4494,499 +4454,499 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -5019,1180 +4979,1180 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -6222,22 +6182,22 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6245,19 +6205,19 @@
         <v>46212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6265,17 +6225,17 @@
         <v>46175</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6283,19 +6243,19 @@
         <v>45938</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6303,19 +6263,19 @@
         <v>45799</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6323,19 +6283,19 @@
         <v>45637</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6343,19 +6303,19 @@
         <v>45333</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6363,19 +6323,19 @@
         <v>45096</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6383,19 +6343,19 @@
         <v>44980</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6403,19 +6363,19 @@
         <v>44517</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6423,19 +6383,19 @@
         <v>44120</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6443,19 +6403,19 @@
         <v>43766</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -6488,40 +6448,40 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>444</v>
-      </c>
       <c r="L1" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6529,29 +6489,29 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6559,27 +6519,27 @@
         <v>2026</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6587,27 +6547,27 @@
         <v>2026</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6615,27 +6575,27 @@
         <v>2026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6643,27 +6603,27 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6671,29 +6631,29 @@
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6701,29 +6661,29 @@
         <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6731,27 +6691,27 @@
         <v>2025</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6759,29 +6719,29 @@
         <v>2024</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6789,16 +6749,16 @@
         <v>2024</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -6806,10 +6766,10 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6817,27 +6777,27 @@
         <v>2024</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6845,27 +6805,27 @@
         <v>2024</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6873,27 +6833,27 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6901,16 +6861,16 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -6918,10 +6878,10 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6929,29 +6889,29 @@
         <v>2023</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6959,16 +6919,16 @@
         <v>2023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -6976,10 +6936,10 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6987,16 +6947,16 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -7004,10 +6964,10 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7015,16 +6975,16 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -7032,10 +6992,10 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7043,16 +7003,16 @@
         <v>2022</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -7060,10 +7020,10 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7071,16 +7031,16 @@
         <v>2021</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -7088,10 +7048,10 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7099,29 +7059,29 @@
         <v>2021</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7129,16 +7089,16 @@
         <v>2021</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -7146,10 +7106,10 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7157,16 +7117,16 @@
         <v>2021</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -7174,10 +7134,10 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7185,16 +7145,16 @@
         <v>2020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -7202,10 +7162,10 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7213,16 +7173,16 @@
         <v>2020</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -7230,10 +7190,10 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7241,16 +7201,16 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -7258,10 +7218,10 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7269,16 +7229,16 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -7286,10 +7246,10 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7297,16 +7257,16 @@
         <v>2019</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -7314,10 +7274,10 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7325,16 +7285,16 @@
         <v>2019</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -7342,10 +7302,10 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7353,16 +7313,16 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -7370,10 +7330,10 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7381,16 +7341,16 @@
         <v>2018</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -7398,10 +7358,10 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7409,16 +7369,16 @@
         <v>2017</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -7426,10 +7386,10 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7437,16 +7397,16 @@
         <v>2017</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -7454,10 +7414,10 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7465,16 +7425,16 @@
         <v>2017</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -7482,10 +7442,10 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7493,16 +7453,16 @@
         <v>2017</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -7510,10 +7470,10 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7521,16 +7481,16 @@
         <v>2017</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -7538,10 +7498,10 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7549,16 +7509,16 @@
         <v>2017</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -7566,10 +7526,10 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7577,16 +7537,16 @@
         <v>2017</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -7594,10 +7554,10 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7605,16 +7565,16 @@
         <v>2017</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -7622,10 +7582,10 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7633,16 +7593,16 @@
         <v>2017</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -7650,10 +7610,10 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7661,16 +7621,16 @@
         <v>2016</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -7678,10 +7638,10 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7689,16 +7649,16 @@
         <v>2016</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -7706,10 +7666,10 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7717,16 +7677,16 @@
         <v>2016</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -7734,10 +7694,10 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7745,16 +7705,16 @@
         <v>2016</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -7762,10 +7722,10 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7773,16 +7733,16 @@
         <v>2015</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -7790,10 +7750,10 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7801,16 +7761,16 @@
         <v>2015</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -7818,10 +7778,10 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7829,16 +7789,16 @@
         <v>2015</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -7846,10 +7806,10 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7857,16 +7817,16 @@
         <v>2015</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -7874,10 +7834,10 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7885,16 +7845,16 @@
         <v>2015</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -7902,10 +7862,10 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7913,16 +7873,16 @@
         <v>2014</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -7930,10 +7890,10 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7941,16 +7901,16 @@
         <v>2014</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -7958,10 +7918,10 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7969,16 +7929,16 @@
         <v>2014</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -7986,10 +7946,10 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7997,16 +7957,16 @@
         <v>2014</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -8014,10 +7974,10 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8025,16 +7985,16 @@
         <v>2013</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -8042,10 +8002,10 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8053,16 +8013,16 @@
         <v>2013</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -8070,10 +8030,10 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8081,16 +8041,16 @@
         <v>2013</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -8098,10 +8058,10 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8109,16 +8069,16 @@
         <v>2013</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -8126,10 +8086,10 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8137,16 +8097,16 @@
         <v>2012</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -8154,10 +8114,10 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8165,16 +8125,16 @@
         <v>2012</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -8182,10 +8142,10 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8193,16 +8153,16 @@
         <v>2012</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -8210,10 +8170,10 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8221,16 +8181,16 @@
         <v>2012</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -8238,10 +8198,10 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8249,16 +8209,16 @@
         <v>2012</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -8266,10 +8226,10 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8277,16 +8237,16 @@
         <v>2011</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -8294,10 +8254,10 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8305,16 +8265,16 @@
         <v>2011</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
@@ -8322,10 +8282,10 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8333,16 +8293,16 @@
         <v>2010</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -8350,10 +8310,10 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8361,16 +8321,16 @@
         <v>2010</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -8378,10 +8338,10 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8389,16 +8349,16 @@
         <v>2010</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -8406,10 +8366,10 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8417,16 +8377,16 @@
         <v>2010</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -8434,10 +8394,10 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8445,16 +8405,16 @@
         <v>2010</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -8462,10 +8422,10 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8473,16 +8433,16 @@
         <v>2010</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -8490,10 +8450,10 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8501,16 +8461,16 @@
         <v>2010</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -8518,10 +8478,10 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8529,16 +8489,16 @@
         <v>2010</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -8546,10 +8506,10 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8557,16 +8517,16 @@
         <v>2009</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -8574,10 +8534,10 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8585,16 +8545,16 @@
         <v>2009</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -8602,10 +8562,10 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8613,16 +8573,16 @@
         <v>2009</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -8630,10 +8590,10 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8641,16 +8601,16 @@
         <v>2009</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -8658,10 +8618,10 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8669,16 +8629,16 @@
         <v>2008</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -8686,10 +8646,10 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8697,16 +8657,16 @@
         <v>2008</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -8714,10 +8674,10 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8725,16 +8685,16 @@
         <v>2008</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -8742,10 +8702,10 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8753,16 +8713,16 @@
         <v>2007</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -8770,10 +8730,10 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8781,16 +8741,16 @@
         <v>2007</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -8798,10 +8758,10 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8809,16 +8769,16 @@
         <v>2007</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -8826,10 +8786,10 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8837,16 +8797,16 @@
         <v>2007</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -8854,10 +8814,10 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8865,16 +8825,16 @@
         <v>2007</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -8882,10 +8842,10 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8893,16 +8853,16 @@
         <v>2006</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -8910,10 +8870,10 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8921,16 +8881,16 @@
         <v>2006</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -8938,10 +8898,10 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8949,16 +8909,16 @@
         <v>2006</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -8966,10 +8926,10 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8977,16 +8937,16 @@
         <v>2005</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -8994,10 +8954,10 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9005,16 +8965,16 @@
         <v>2005</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -9022,10 +8982,10 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9033,16 +8993,16 @@
         <v>2004</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -9050,10 +9010,10 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9061,16 +9021,16 @@
         <v>2004</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -9078,10 +9038,10 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9089,16 +9049,16 @@
         <v>2004</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -9106,10 +9066,10 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9117,16 +9077,16 @@
         <v>2003</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -9134,10 +9094,10 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9145,16 +9105,16 @@
         <v>2003</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -9162,10 +9122,10 @@
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9173,16 +9133,16 @@
         <v>2003</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -9190,10 +9150,10 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9201,16 +9161,16 @@
         <v>2003</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -9218,10 +9178,10 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="98" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9229,16 +9189,16 @@
         <v>2003</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -9246,10 +9206,10 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9257,16 +9217,16 @@
         <v>2003</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -9274,10 +9234,10 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -14,7 +14,6 @@
     <sheet sheetId="8" name="News" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Publications" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="Patents" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Join" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -55,30 +54,6 @@
       </text>
     </comment>
     <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <t>Set to "no" to hide this row on the website without deleting it.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <t>Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
       <text>
         <r>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
@@ -395,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="796">
   <si>
     <t>Lab website content</t>
   </si>
@@ -530,12 +505,6 @@
   </si>
   <si>
     <t>Patents and applications, grouped by year on the website. The Patents menu item only appears once at least one row is shown.</t>
-  </si>
-  <si>
-    <t>Join</t>
-  </si>
-  <si>
-    <t>Sections of the Join page. The contact email is added at the end automatically.</t>
   </si>
   <si>
     <t>Setting</t>
@@ -682,24 +651,6 @@
     <t>Text at the top of the Patents page.</t>
   </si>
   <si>
-    <t>Join page title</t>
-  </si>
-  <si>
-    <t>Join Us!</t>
-  </si>
-  <si>
-    <t>Heading of the Join page, e.g. "Join Us!".</t>
-  </si>
-  <si>
-    <t>Join page introduction</t>
-  </si>
-  <si>
-    <t>We are recruiting at all levels. If you think our research is exciting, please reach out!</t>
-  </si>
-  <si>
-    <t>Text at the top of the Join page.</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -2814,27 +2765,6 @@
   </si>
   <si>
     <t>Granted</t>
-  </si>
-  <si>
-    <t>Heading</t>
-  </si>
-  <si>
-    <t>Postdoctoral Fellows</t>
-  </si>
-  <si>
-    <t>We are looking for highly motivated postdocs with expertise in molecular biology, genomics, cell biology, and/or microscopy. Please contact Ana if interested!</t>
-  </si>
-  <si>
-    <t>Graduate Students</t>
-  </si>
-  <si>
-    <t>We are affiliated with the CMDB (KSAS), [Human Genetics and Genomics](https://www.hopkinsmedicine.org/genetic-medicine/education-training/human-genetics-genomics-graduate-program), and BCMB (SOM) graduate programs, but are happy to hear from Students in other graduate programs as well. If you are interested in a rotation, please contact Ana.</t>
-  </si>
-  <si>
-    <t>Undergraduates</t>
-  </si>
-  <si>
-    <t>Undergraduates interested in a research experience in our lab should be willing to commit at least 10 hours per week to research.</t>
   </si>
 </sst>
 </file>
@@ -3271,7 +3201,7 @@
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3466,14 +3396,6 @@
       </c>
       <c r="B28" s="2" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -3498,28 +3420,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3527,23 +3449,23 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3551,23 +3473,23 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3586,75 +3508,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>804</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C1"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="C2:C1000">
-      <formula1>"yes,no"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3664,200 +3520,178 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3878,88 +3712,88 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3980,334 +3814,334 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -4339,90 +4173,90 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4454,499 +4288,499 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -4979,1180 +4813,1180 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -6182,22 +6016,22 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6205,19 +6039,19 @@
         <v>46212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6225,17 +6059,17 @@
         <v>46175</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6243,19 +6077,19 @@
         <v>45938</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6263,19 +6097,19 @@
         <v>45799</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6283,19 +6117,19 @@
         <v>45637</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6303,19 +6137,19 @@
         <v>45333</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6323,19 +6157,19 @@
         <v>45096</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6343,19 +6177,19 @@
         <v>44980</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6363,19 +6197,19 @@
         <v>44517</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>422</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6383,19 +6217,19 @@
         <v>44120</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6403,19 +6237,19 @@
         <v>43766</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -6448,40 +6282,40 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>438</v>
-      </c>
       <c r="L1" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6489,29 +6323,29 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6519,27 +6353,27 @@
         <v>2026</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6547,27 +6381,27 @@
         <v>2026</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6575,27 +6409,27 @@
         <v>2026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6603,27 +6437,27 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6631,29 +6465,29 @@
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6661,29 +6495,29 @@
         <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6691,27 +6525,27 @@
         <v>2025</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6719,29 +6553,29 @@
         <v>2024</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6749,16 +6583,16 @@
         <v>2024</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -6766,10 +6600,10 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6777,27 +6611,27 @@
         <v>2024</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6805,27 +6639,27 @@
         <v>2024</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6833,27 +6667,27 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6861,16 +6695,16 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -6878,10 +6712,10 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6889,29 +6723,29 @@
         <v>2023</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6919,16 +6753,16 @@
         <v>2023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -6936,10 +6770,10 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6947,16 +6781,16 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -6964,10 +6798,10 @@
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6975,16 +6809,16 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -6992,10 +6826,10 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7003,16 +6837,16 @@
         <v>2022</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -7020,10 +6854,10 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7031,16 +6865,16 @@
         <v>2021</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -7048,10 +6882,10 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7059,29 +6893,29 @@
         <v>2021</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7089,16 +6923,16 @@
         <v>2021</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -7106,10 +6940,10 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7117,16 +6951,16 @@
         <v>2021</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -7134,10 +6968,10 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7145,16 +6979,16 @@
         <v>2020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -7162,10 +6996,10 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7173,16 +7007,16 @@
         <v>2020</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -7190,10 +7024,10 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7201,16 +7035,16 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -7218,10 +7052,10 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7229,16 +7063,16 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -7246,10 +7080,10 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7257,16 +7091,16 @@
         <v>2019</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -7274,10 +7108,10 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7285,16 +7119,16 @@
         <v>2019</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -7302,10 +7136,10 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7313,16 +7147,16 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -7330,10 +7164,10 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7341,16 +7175,16 @@
         <v>2018</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -7358,10 +7192,10 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7369,16 +7203,16 @@
         <v>2017</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -7386,10 +7220,10 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7397,16 +7231,16 @@
         <v>2017</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -7414,10 +7248,10 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7425,16 +7259,16 @@
         <v>2017</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -7442,10 +7276,10 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7453,16 +7287,16 @@
         <v>2017</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -7470,10 +7304,10 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7481,16 +7315,16 @@
         <v>2017</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -7498,10 +7332,10 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7509,16 +7343,16 @@
         <v>2017</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -7526,10 +7360,10 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7537,16 +7371,16 @@
         <v>2017</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -7554,10 +7388,10 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7565,16 +7399,16 @@
         <v>2017</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -7582,10 +7416,10 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7593,16 +7427,16 @@
         <v>2017</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -7610,10 +7444,10 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7621,16 +7455,16 @@
         <v>2016</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -7638,10 +7472,10 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7649,16 +7483,16 @@
         <v>2016</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -7666,10 +7500,10 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7677,16 +7511,16 @@
         <v>2016</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -7694,10 +7528,10 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7705,16 +7539,16 @@
         <v>2016</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -7722,10 +7556,10 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7733,16 +7567,16 @@
         <v>2015</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -7750,10 +7584,10 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7761,16 +7595,16 @@
         <v>2015</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -7778,10 +7612,10 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7789,16 +7623,16 @@
         <v>2015</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -7806,10 +7640,10 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7817,16 +7651,16 @@
         <v>2015</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -7834,10 +7668,10 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7845,16 +7679,16 @@
         <v>2015</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -7862,10 +7696,10 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7873,16 +7707,16 @@
         <v>2014</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -7890,10 +7724,10 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7901,16 +7735,16 @@
         <v>2014</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -7918,10 +7752,10 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7929,16 +7763,16 @@
         <v>2014</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -7946,10 +7780,10 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7957,16 +7791,16 @@
         <v>2014</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -7974,10 +7808,10 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7985,16 +7819,16 @@
         <v>2013</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -8002,10 +7836,10 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8013,16 +7847,16 @@
         <v>2013</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -8030,10 +7864,10 @@
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8041,16 +7875,16 @@
         <v>2013</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -8058,10 +7892,10 @@
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8069,16 +7903,16 @@
         <v>2013</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -8086,10 +7920,10 @@
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8097,16 +7931,16 @@
         <v>2012</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -8114,10 +7948,10 @@
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8125,16 +7959,16 @@
         <v>2012</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -8142,10 +7976,10 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8153,16 +7987,16 @@
         <v>2012</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -8170,10 +8004,10 @@
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8181,16 +8015,16 @@
         <v>2012</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -8198,10 +8032,10 @@
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8209,16 +8043,16 @@
         <v>2012</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -8226,10 +8060,10 @@
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8237,16 +8071,16 @@
         <v>2011</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -8254,10 +8088,10 @@
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8265,16 +8099,16 @@
         <v>2011</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
@@ -8282,10 +8116,10 @@
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8293,16 +8127,16 @@
         <v>2010</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -8310,10 +8144,10 @@
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8321,16 +8155,16 @@
         <v>2010</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -8338,10 +8172,10 @@
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8349,16 +8183,16 @@
         <v>2010</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -8366,10 +8200,10 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8377,16 +8211,16 @@
         <v>2010</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -8394,10 +8228,10 @@
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8405,16 +8239,16 @@
         <v>2010</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -8422,10 +8256,10 @@
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8433,16 +8267,16 @@
         <v>2010</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -8450,10 +8284,10 @@
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8461,16 +8295,16 @@
         <v>2010</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -8478,10 +8312,10 @@
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8489,16 +8323,16 @@
         <v>2010</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -8506,10 +8340,10 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8517,16 +8351,16 @@
         <v>2009</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -8534,10 +8368,10 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8545,16 +8379,16 @@
         <v>2009</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -8562,10 +8396,10 @@
       <c r="I75" s="2"/>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8573,16 +8407,16 @@
         <v>2009</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -8590,10 +8424,10 @@
       <c r="I76" s="2"/>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8601,16 +8435,16 @@
         <v>2009</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -8618,10 +8452,10 @@
       <c r="I77" s="2"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8629,16 +8463,16 @@
         <v>2008</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -8646,10 +8480,10 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8657,16 +8491,16 @@
         <v>2008</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -8674,10 +8508,10 @@
       <c r="I79" s="2"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8685,16 +8519,16 @@
         <v>2008</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -8702,10 +8536,10 @@
       <c r="I80" s="2"/>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8713,16 +8547,16 @@
         <v>2007</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -8730,10 +8564,10 @@
       <c r="I81" s="2"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8741,16 +8575,16 @@
         <v>2007</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -8758,10 +8592,10 @@
       <c r="I82" s="2"/>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8769,16 +8603,16 @@
         <v>2007</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -8786,10 +8620,10 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8797,16 +8631,16 @@
         <v>2007</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -8814,10 +8648,10 @@
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8825,16 +8659,16 @@
         <v>2007</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -8842,10 +8676,10 @@
       <c r="I85" s="2"/>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8853,16 +8687,16 @@
         <v>2006</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -8870,10 +8704,10 @@
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8881,16 +8715,16 @@
         <v>2006</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -8898,10 +8732,10 @@
       <c r="I87" s="2"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8909,16 +8743,16 @@
         <v>2006</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -8926,10 +8760,10 @@
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8937,16 +8771,16 @@
         <v>2005</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -8954,10 +8788,10 @@
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8965,16 +8799,16 @@
         <v>2005</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -8982,10 +8816,10 @@
       <c r="I90" s="2"/>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8993,16 +8827,16 @@
         <v>2004</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -9010,10 +8844,10 @@
       <c r="I91" s="2"/>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9021,16 +8855,16 @@
         <v>2004</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -9038,10 +8872,10 @@
       <c r="I92" s="2"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9049,16 +8883,16 @@
         <v>2004</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -9066,10 +8900,10 @@
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9077,16 +8911,16 @@
         <v>2003</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -9094,10 +8928,10 @@
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9105,16 +8939,16 @@
         <v>2003</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -9122,10 +8956,10 @@
       <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9133,16 +8967,16 @@
         <v>2003</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -9150,10 +8984,10 @@
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9161,16 +8995,16 @@
         <v>2003</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -9178,10 +9012,10 @@
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9189,16 +9023,16 @@
         <v>2003</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -9206,10 +9040,10 @@
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9217,16 +9051,16 @@
         <v>2003</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -9234,10 +9068,10 @@
       <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -1,61 +1,274 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10927"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF030A50-F2B1-D043-8768-A077CF386B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19680" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="README" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Settings" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="PI" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="PI Details" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Sites" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Members" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Alumni" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="News" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Publications" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Patents" state="visible" r:id="rId13"/>
+    <sheet name="README" sheetId="1" r:id="rId1"/>
+    <sheet name="Settings" sheetId="2" r:id="rId2"/>
+    <sheet name="PI" sheetId="3" r:id="rId3"/>
+    <sheet name="PI Details" sheetId="4" r:id="rId4"/>
+    <sheet name="Sites" sheetId="5" r:id="rId5"/>
+    <sheet name="Members" sheetId="6" r:id="rId6"/>
+    <sheet name="Alumni" sheetId="7" r:id="rId7"/>
+    <sheet name="News" sheetId="8" r:id="rId8"/>
+    <sheet name="Publications" sheetId="9" r:id="rId9"/>
+    <sheet name="Patents" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Group heading, e.g. "Appointments", "Education", "Honors", "Links". Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>The text of the bullet. Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Optional web address. If filled in, the item becomes a link.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Set to "no" to hide this row on the website without deleting it.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Short code used in the Site column of the Members and Alumni tabs, e.g. "JHU". Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Label shown on badges. Defaults to the code.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Optional badge colour as a hex code, e.g. #2B5CB8.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>"yes" for an active site, "no" for a past one.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
       <text>
         <r>
-          <t>Application or publication number.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>A code from the Sites tab. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000003000000}">
       <text>
         <r>
-          <t>e.g. USPTO, EPO, WIPO.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. PhD Student, Postdoctoral Fellow, Senior Scientist. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000004000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>One or two sentences on what this person works on. Leave blank to omit.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>File name of a photo in public/images/people, or a full web address. Leave blank to show initials.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Personal page, Google Scholar, ORCID, etc.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -65,35 +278,105 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
-          <t>Group heading, e.g. "Appointments", "Education", "Honors", "Links". Required.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
       <text>
         <r>
-          <t>The text of the bullet. Required.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. "2019–2022" or "2021".</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
       <text>
         <r>
-          <t>Optional web address. If filled in, the item becomes a link.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>A code from the Sites tab. Several sites can be joined with "/", e.g. "L/MDC".</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Position in the lab, e.g. PhD, Postdoc, MSc.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Current position. Leave blank if unknown.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Optional thesis title. The column only appears on the site if at least one alumnus has one.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -103,43 +386,78 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
       <text>
         <r>
-          <t>Short code used in the Site column of the Members and Alumni tabs, e.g. "JHU". Required.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Date of the news item, e.g. 2026-06-02. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000002000000}">
       <text>
         <r>
-          <t>Label shown on badges. Defaults to the code.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. Lab, Paper, Award, Press.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000003000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000004000000}">
       <text>
         <r>
-          <t>Optional badge colour as a hex code, e.g. #2B5CB8.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Optional "Read more" link. Can be a web address or a page on this site like /publications.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000005000000}">
       <text>
         <r>
-          <t>"yes" for an active site, "no" for a past one.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
     </comment>
@@ -148,56 +466,105 @@
 </file>
 
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000002000000}">
       <text>
         <r>
-          <t>A code from the Sites tab. Required.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000003000000}">
       <text>
         <r>
-          <t>e.g. PhD Student, Postdoctoral Fellow, Senior Scientist. Required.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Author list as it should appear, e.g. "Beagrie, R. A., Pombo, A.".</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000004000000}">
       <text>
         <r>
-          <t>One or two sentences on what this person works on. Leave blank to omit.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. "21(7), 735–775".</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000005000000}">
       <text>
         <r>
-          <t>File name of a photo in public/images/people, or a full web address. Leave blank to show initials.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. 10.1038/s41586-021-04081-2 or the full https://doi.org/… address.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000006000000}">
       <text>
         <r>
-          <t>Personal page, Google Scholar, ORCID, etc.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>"yes" to show it on the homepage and mark it as featured.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000007000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -207,160 +574,77 @@
 </file>
 
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000001000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000002000000}">
       <text>
         <r>
-          <t>e.g. "2019–2022" or "2021".</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <t>A code from the Sites tab. Several sites can be joined with "/", e.g. "L/MDC".</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <t>Position in the lab, e.g. PhD, Postdoc, MSc.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <t>Current position. Leave blank if unknown.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <t>Optional thesis title. The column only appears on the site if at least one alumnus has one.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <t>Set to "no" to hide this row on the website without deleting it.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <t>Date of the news item, e.g. 2026-06-02. Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <t>e.g. Lab, Paper, Award, Press.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000003000000}">
       <text>
         <r>
-          <t>Optional "Read more" link. Can be a web address or a page on this site like /publications.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Application or publication number.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
       <text>
         <r>
-          <t>Set to "no" to hide this row on the website without deleting it.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. USPTO, EPO, WIPO.</t>
         </r>
       </text>
     </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000005000000}">
       <text>
         <r>
-          <t>Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <t>Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <t>Author list as it should appear, e.g. "Beagrie, R. A., Pombo, A.".</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <t>e.g. "21(7), 735–775".</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <t>e.g. 10.1038/s41586-021-04081-2 or the full https://doi.org/… address.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <t>"yes" to show it on the homepage and mark it as featured.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0">
-      <text>
-        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -370,7 +654,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="799">
   <si>
     <t>Lab website content</t>
   </si>
@@ -576,7 +860,7 @@
     <t>Bold author names</t>
   </si>
   <si>
-    <t xml:space="preserve">Pombo, A.
+    <t>Pombo, A.
 A. Pombo
 Pombo A</t>
   </si>
@@ -587,7 +871,7 @@
     <t>Lab description</t>
   </si>
   <si>
-    <t xml:space="preserve">We study mechanisms of gene expression at multiple levels, from the local action of transcription factors, to long-range chromatin looping events that connect regulatory DNA sequences with the genes they regulate, to how whole chromosomes are positioned within cell nuclei. Binding of transcription factors at regulatory sequences helps recruit chromatin remodelers and the transcription machinery to transcription sites.
+    <t>We study mechanisms of gene expression at multiple levels, from the local action of transcription factors, to long-range chromatin looping events that connect regulatory DNA sequences with the genes they regulate, to how whole chromosomes are positioned within cell nuclei. Binding of transcription factors at regulatory sequences helps recruit chromatin remodelers and the transcription machinery to transcription sites.
 Upon recruitment, RNA polymerases either remain primed for subsequent activation (e.g. after environmental stress, during differentiation or disease), or directly transcribe the DNA template into RNA molecules, which code for proteins or for structural RNAs that constitute many enzymatic complexes.
 An increasingly important aspect of gene regulation is the three-dimensional folding of the genome, and the mechanisms that control physical contacts of distant regulatory DNA sequences with gene promoters to activate gene expression. To directly measure genome topologies, our group developed Genome Architecture Mapping (GAM).
 Our long-term strategy for unravelling the principles of genome function in higher eukaryotes aims to integrate multiple parameters, which is becoming increasingly possible with state-of-the-art developments in single cell genomics, molecular biology, epigenetics, nuclear imaging, and genetics.</t>
@@ -599,7 +883,7 @@
     <t>Research description</t>
   </si>
   <si>
-    <t xml:space="preserve">Our main goal is to unravel the diverse mechanisms of mammalian gene regulation and their roles in development and disease. Gene activation is controlled locally through transcription factors, chromatin modifiers, and the transcription and RNA processing machineries. Gene expression is also intricately regulated by the three-dimensional (3D) structure of the genome, which modifies the location of genes relative to activating or repressing biochemical environments. Repressing nuclear locations include the nuclear lamina and heterochromatin. Activating 3D genome conformations can work by regulating the physical proximity between regulatory regions and their responsive genes. As many disease-associated genetic variants fall in non-coding regulatory elements scattered in the genome, our work aims to advance the functional interpretation of the linear genome sequence. We especially put effort in devising experimental and computational approaches to map 3D genome structure in different cell types, in development and in disease, to study developmental and disease mechanisms, towards novel diagnostics, prognostics and therapeutics.
+    <t>Our main goal is to unravel the diverse mechanisms of mammalian gene regulation and their roles in development and disease. Gene activation is controlled locally through transcription factors, chromatin modifiers, and the transcription and RNA processing machineries. Gene expression is also intricately regulated by the three-dimensional (3D) structure of the genome, which modifies the location of genes relative to activating or repressing biochemical environments. Repressing nuclear locations include the nuclear lamina and heterochromatin. Activating 3D genome conformations can work by regulating the physical proximity between regulatory regions and their responsive genes. As many disease-associated genetic variants fall in non-coding regulatory elements scattered in the genome, our work aims to advance the functional interpretation of the linear genome sequence. We especially put effort in devising experimental and computational approaches to map 3D genome structure in different cell types, in development and in disease, to study developmental and disease mechanisms, towards novel diagnostics, prognostics and therapeutics.
 We have developed Genome Architecture Mapping (GAM), an orthogonal 3D genome folding mapping technology which yields fine maps of chromatin contacts from small cell numbers (500−1000), and is uniquely powerful to quantify different metrics of 3D genome structure, such as multiway contacts and chromatin melting. With immuno-GAM, we introduced the selection of cell types within complex tissues to enable the application of GAM in rare cells, such as dopaminergic neurons in the midbrain. GAM is an inherently suited platform for multimodal molecular phenotyping of biological samples, from genome sequence and 3D structure, to transcript and protein quantification. As a first step towards GAM multimodality, we have developed Oligo-Seq, a novel approach to detect minute amounts of specific RNA sequences within thin tissue cryosections, as used for GAM. We currently develop the application of Oligo-seq in spatial transcriptomics, especially in archival clinical samples (e.g. FFPE). By further developing multimodal integration of 3D genome topology, with the abundance of specific regulatory factors and gene expression, at the single-cell level, we aim to extract dynamic states of gene regulation and cause-effect relationships that connect 3D genome structure with gene expression. Ultimately, we seek to advance the interpretability of the linear genome sequence, to gain a deeper understanding of 3D genome regulation mechanisms in gene expression, and to advance their predictability.</t>
   </si>
   <si>
@@ -852,7 +1136,7 @@
     <t>Max Delbrück Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Berlin Institute for Medical Systems Biology (BIMSB)
+    <t>Berlin Institute for Medical Systems Biology (BIMSB)
 Hannoversche Straße 28, 10115 Berlin</t>
   </si>
   <si>
@@ -2765,41 +3049,71 @@
   </si>
   <si>
     <t>Granted</t>
+  </si>
+  <si>
+    <t>Brady Bock</t>
+  </si>
+  <si>
+    <t>Undergraduate</t>
+  </si>
+  <si>
+    <t>bbock4@jh.edu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
+      <sz val="11"/>
       <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2829,10 +3143,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2859,8 +3174,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3197,36 +3516,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
+    </row>
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -3234,7 +3550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -3242,7 +3558,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -3250,7 +3566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -3258,7 +3574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -3266,13 +3582,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
@@ -3280,7 +3595,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -3288,7 +3603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
@@ -3296,7 +3611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -3304,7 +3619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -3312,7 +3627,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -3320,13 +3635,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="3"/>
-    </row>
-    <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -3334,7 +3648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
@@ -3342,7 +3656,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
@@ -3350,7 +3664,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
@@ -3358,7 +3672,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>35</v>
       </c>
@@ -3366,7 +3680,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -3374,7 +3688,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>39</v>
       </c>
@@ -3382,7 +3696,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>41</v>
       </c>
@@ -3390,7 +3704,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>43</v>
       </c>
@@ -3400,14 +3714,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -3418,7 +3732,7 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>422</v>
       </c>
@@ -3444,7 +3758,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2026</v>
       </c>
@@ -3463,12 +3777,11 @@
       <c r="F2" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2025</v>
       </c>
@@ -3487,38 +3800,37 @@
       <c r="F3" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
         <v>134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Status" error="Choose a value from the list." sqref="E2:E1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Status" error="Choose a value from the list." sqref="E2:E1000" xr:uid="{00000000-0002-0000-0900-000000000000}">
       <formula1>"Filed,Published,Granted"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="H2:H1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="H2:H1000" xr:uid="{00000000-0002-0000-0900-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>45</v>
       </c>
@@ -3529,7 +3841,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>48</v>
       </c>
@@ -3540,7 +3852,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>51</v>
       </c>
@@ -3551,7 +3863,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>54</v>
       </c>
@@ -3562,7 +3874,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>57</v>
       </c>
@@ -3573,7 +3885,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>60</v>
       </c>
@@ -3584,7 +3896,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>62</v>
       </c>
@@ -3595,7 +3907,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>64</v>
       </c>
@@ -3606,7 +3918,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>67</v>
       </c>
@@ -3617,7 +3929,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" s="2" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>70</v>
       </c>
@@ -3628,7 +3940,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" s="2" customFormat="1" ht="395" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>73</v>
       </c>
@@ -3639,7 +3951,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>76</v>
       </c>
@@ -3650,7 +3962,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>79</v>
       </c>
@@ -3661,7 +3973,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>82</v>
       </c>
@@ -3672,7 +3984,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>85</v>
       </c>
@@ -3683,7 +3995,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>88</v>
       </c>
@@ -3696,21 +4008,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>45</v>
       </c>
@@ -3721,7 +4033,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>91</v>
       </c>
@@ -3730,7 +4042,7 @@
       </c>
       <c r="C2" s="6"/>
     </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>93</v>
       </c>
@@ -3741,7 +4053,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>96</v>
       </c>
@@ -3752,7 +4064,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>99</v>
       </c>
@@ -3763,7 +4075,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>99</v>
       </c>
@@ -3774,7 +4086,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" s="2" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>102</v>
       </c>
@@ -3785,7 +4097,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>102</v>
       </c>
@@ -3798,21 +4110,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>106</v>
       </c>
@@ -3826,283 +4138,260 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>132</v>
       </c>
@@ -4116,7 +4405,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>132</v>
       </c>
@@ -4130,7 +4419,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>132</v>
       </c>
@@ -4145,22 +4434,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="D2:D1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="D2:D1000" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4171,7 +4460,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>144</v>
       </c>
@@ -4194,7 +4483,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>151</v>
       </c>
@@ -4217,7 +4506,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>156</v>
       </c>
@@ -4240,7 +4529,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>161</v>
       </c>
@@ -4250,32 +4539,30 @@
       <c r="C4" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
         <v>134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Current site" error="&quot;yes&quot; for an active site, &quot;no&quot; for a past one." sqref="G2:G1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Current site" error="&quot;yes&quot; for an active site, &quot;no&quot; for a past one." sqref="G2:G1000" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -4286,7 +4573,7 @@
     <col min="8" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>91</v>
       </c>
@@ -4315,7 +4602,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>170</v>
       </c>
@@ -4328,17 +4615,14 @@
       <c r="D2" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>174</v>
       </c>
@@ -4351,17 +4635,14 @@
       <c r="D3" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>178</v>
       </c>
@@ -4380,13 +4661,11 @@
       <c r="F4" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>183</v>
       </c>
@@ -4405,13 +4684,11 @@
       <c r="F5" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="112" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>186</v>
       </c>
@@ -4430,293 +4707,256 @@
       <c r="F6" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>190</v>
+        <v>796</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>179</v>
+        <v>797</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="F7" s="10" t="s">
+        <v>798</v>
+      </c>
       <c r="I7" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>179</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="2"/>
+        <v>180</v>
+      </c>
       <c r="F8" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+        <v>191</v>
+      </c>
       <c r="I8" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+        <v>194</v>
+      </c>
       <c r="I9" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+        <v>197</v>
+      </c>
       <c r="I10" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="I12" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+        <v>205</v>
+      </c>
       <c r="I13" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+        <v>207</v>
+      </c>
       <c r="I14" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>214</v>
+      </c>
       <c r="I16" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>219</v>
+        <v>171</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>156</v>
@@ -4727,82 +4967,105 @@
       <c r="D19" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+        <v>220</v>
+      </c>
       <c r="I19" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+        <v>222</v>
+      </c>
       <c r="I20" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" showErrorMessage="1" errorStyle="warning" errorTitle="Site" error="A code from the Sites tab." sqref="B2:B1000">
-      <formula1>Sites!$A$2:$A$50</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="I2:I1000">
+  <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="I2:I1001" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="F7" r:id="rId1" xr:uid="{72576DDF-177A-9843-88DF-1B21D72EA54A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <legacyDrawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" errorStyle="warning" showErrorMessage="1" errorTitle="Site" error="A code from the Sites tab." xr:uid="{00000000-0002-0000-0500-000000000000}">
+          <x14:formula1>
+            <xm:f>Sites!$A$2:$A$50</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1001</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G58"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4811,7 +5074,7 @@
     <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>91</v>
       </c>
@@ -4834,7 +5097,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>232</v>
       </c>
@@ -4847,13 +5110,11 @@
       <c r="D2" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>235</v>
       </c>
@@ -4869,12 +5130,11 @@
       <c r="E3" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>239</v>
       </c>
@@ -4890,12 +5150,11 @@
       <c r="E4" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>241</v>
       </c>
@@ -4911,12 +5170,11 @@
       <c r="E5" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>244</v>
       </c>
@@ -4932,12 +5190,11 @@
       <c r="E6" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>248</v>
       </c>
@@ -4953,12 +5210,11 @@
       <c r="E7" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>251</v>
       </c>
@@ -4974,12 +5230,11 @@
       <c r="E8" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>253</v>
       </c>
@@ -4992,13 +5247,11 @@
       <c r="D9" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>254</v>
       </c>
@@ -5014,12 +5267,11 @@
       <c r="E10" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>257</v>
       </c>
@@ -5035,12 +5287,11 @@
       <c r="E11" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>260</v>
       </c>
@@ -5056,12 +5307,11 @@
       <c r="E12" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>264</v>
       </c>
@@ -5077,12 +5327,11 @@
       <c r="E13" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>267</v>
       </c>
@@ -5098,12 +5347,11 @@
       <c r="E14" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>270</v>
       </c>
@@ -5119,12 +5367,11 @@
       <c r="E15" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>272</v>
       </c>
@@ -5140,12 +5387,11 @@
       <c r="E16" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>275</v>
       </c>
@@ -5161,12 +5407,11 @@
       <c r="E17" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>277</v>
       </c>
@@ -5182,12 +5427,11 @@
       <c r="E18" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>280</v>
       </c>
@@ -5203,12 +5447,11 @@
       <c r="E19" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>284</v>
       </c>
@@ -5224,12 +5467,11 @@
       <c r="E20" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>287</v>
       </c>
@@ -5245,12 +5487,11 @@
       <c r="E21" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>289</v>
       </c>
@@ -5266,12 +5507,11 @@
       <c r="E22" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>292</v>
       </c>
@@ -5287,12 +5527,11 @@
       <c r="E23" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>295</v>
       </c>
@@ -5305,13 +5544,11 @@
       <c r="D24" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>296</v>
       </c>
@@ -5327,12 +5564,11 @@
       <c r="E25" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>299</v>
       </c>
@@ -5348,12 +5584,11 @@
       <c r="E26" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>302</v>
       </c>
@@ -5369,12 +5604,11 @@
       <c r="E27" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>305</v>
       </c>
@@ -5390,12 +5624,11 @@
       <c r="E28" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>308</v>
       </c>
@@ -5411,12 +5644,11 @@
       <c r="E29" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>310</v>
       </c>
@@ -5432,12 +5664,11 @@
       <c r="E30" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>313</v>
       </c>
@@ -5453,12 +5684,11 @@
       <c r="E31" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>315</v>
       </c>
@@ -5474,12 +5704,11 @@
       <c r="E32" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>318</v>
       </c>
@@ -5495,12 +5724,11 @@
       <c r="E33" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>321</v>
       </c>
@@ -5516,12 +5744,11 @@
       <c r="E34" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>325</v>
       </c>
@@ -5537,12 +5764,11 @@
       <c r="E35" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>328</v>
       </c>
@@ -5558,12 +5784,11 @@
       <c r="E36" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>331</v>
       </c>
@@ -5579,12 +5804,11 @@
       <c r="E37" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>334</v>
       </c>
@@ -5600,12 +5824,11 @@
       <c r="E38" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>336</v>
       </c>
@@ -5621,12 +5844,11 @@
       <c r="E39" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>339</v>
       </c>
@@ -5642,12 +5864,11 @@
       <c r="E40" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>342</v>
       </c>
@@ -5663,12 +5884,11 @@
       <c r="E41" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>345</v>
       </c>
@@ -5684,12 +5904,11 @@
       <c r="E42" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>348</v>
       </c>
@@ -5705,12 +5924,11 @@
       <c r="E43" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>351</v>
       </c>
@@ -5726,12 +5944,11 @@
       <c r="E44" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>354</v>
       </c>
@@ -5747,12 +5964,11 @@
       <c r="E45" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>357</v>
       </c>
@@ -5765,13 +5981,11 @@
       <c r="D46" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>360</v>
       </c>
@@ -5784,13 +5998,11 @@
       <c r="D47" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>361</v>
       </c>
@@ -5806,12 +6018,11 @@
       <c r="E48" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>364</v>
       </c>
@@ -5824,13 +6035,11 @@
       <c r="D49" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>366</v>
       </c>
@@ -5843,13 +6052,11 @@
       <c r="D50" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>368</v>
       </c>
@@ -5862,13 +6069,11 @@
       <c r="D51" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>369</v>
       </c>
@@ -5884,12 +6089,11 @@
       <c r="E52" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>372</v>
       </c>
@@ -5905,12 +6109,11 @@
       <c r="E53" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>375</v>
       </c>
@@ -5923,89 +6126,71 @@
       <c r="D54" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="G2:G1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="G2:G1000" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" style="7" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6014,7 +6199,7 @@
     <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>381</v>
       </c>
@@ -6034,7 +6219,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>46212</v>
       </c>
@@ -6054,7 +6239,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>46175</v>
       </c>
@@ -6067,12 +6252,11 @@
       <c r="D3" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>45938</v>
       </c>
@@ -6092,7 +6276,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>45799</v>
       </c>
@@ -6112,7 +6296,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>45637</v>
       </c>
@@ -6132,7 +6316,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>45333</v>
       </c>
@@ -6152,7 +6336,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>45096</v>
       </c>
@@ -6172,7 +6356,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>44980</v>
       </c>
@@ -6192,7 +6376,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>44517</v>
       </c>
@@ -6212,7 +6396,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>44120</v>
       </c>
@@ -6232,7 +6416,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>43766</v>
       </c>
@@ -6253,22 +6437,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="F2:F1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="F2:F1000" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:L99"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
@@ -6280,7 +6464,7 @@
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>422</v>
       </c>
@@ -6318,7 +6502,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2026</v>
       </c>
@@ -6337,10 +6521,6 @@
       <c r="F2" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
         <v>134</v>
       </c>
@@ -6348,7 +6528,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2026</v>
       </c>
@@ -6361,14 +6541,9 @@
       <c r="D3" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
         <v>134</v>
       </c>
@@ -6376,7 +6551,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2026</v>
       </c>
@@ -6389,14 +6564,9 @@
       <c r="D4" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
         <v>134</v>
       </c>
@@ -6404,7 +6574,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2026</v>
       </c>
@@ -6417,14 +6587,9 @@
       <c r="D5" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
         <v>134</v>
       </c>
@@ -6432,7 +6597,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2025</v>
       </c>
@@ -6445,14 +6610,9 @@
       <c r="D6" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
         <v>134</v>
       </c>
@@ -6460,7 +6620,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2025</v>
       </c>
@@ -6479,10 +6639,6 @@
       <c r="F7" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
         <v>134</v>
       </c>
@@ -6490,7 +6646,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2025</v>
       </c>
@@ -6509,10 +6665,6 @@
       <c r="F8" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
         <v>111</v>
       </c>
@@ -6520,7 +6672,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2025</v>
       </c>
@@ -6533,14 +6685,9 @@
       <c r="D9" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
         <v>134</v>
       </c>
@@ -6548,7 +6695,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="2" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2024</v>
       </c>
@@ -6564,10 +6711,6 @@
       <c r="E10" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
         <v>468</v>
       </c>
@@ -6578,7 +6721,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -6594,11 +6737,6 @@
       <c r="E11" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
         <v>134</v>
       </c>
@@ -6606,7 +6744,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" s="2" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2024</v>
       </c>
@@ -6619,14 +6757,9 @@
       <c r="D12" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
         <v>134</v>
       </c>
@@ -6634,7 +6767,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2024</v>
       </c>
@@ -6647,14 +6780,9 @@
       <c r="D13" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
         <v>134</v>
       </c>
@@ -6662,7 +6790,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2024</v>
       </c>
@@ -6675,14 +6803,9 @@
       <c r="D14" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
         <v>134</v>
       </c>
@@ -6690,7 +6813,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2023</v>
       </c>
@@ -6706,11 +6829,6 @@
       <c r="E15" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
         <v>134</v>
       </c>
@@ -6718,7 +6836,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2023</v>
       </c>
@@ -6737,10 +6855,6 @@
       <c r="F16" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
         <v>111</v>
       </c>
@@ -6748,7 +6862,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2023</v>
       </c>
@@ -6764,11 +6878,6 @@
       <c r="E17" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
         <v>134</v>
       </c>
@@ -6776,7 +6885,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2022</v>
       </c>
@@ -6792,11 +6901,6 @@
       <c r="E18" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
         <v>134</v>
       </c>
@@ -6804,7 +6908,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2022</v>
       </c>
@@ -6820,11 +6924,6 @@
       <c r="E19" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
         <v>134</v>
       </c>
@@ -6832,7 +6931,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2022</v>
       </c>
@@ -6848,11 +6947,6 @@
       <c r="E20" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
         <v>134</v>
       </c>
@@ -6860,7 +6954,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2021</v>
       </c>
@@ -6876,11 +6970,6 @@
       <c r="E21" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
         <v>134</v>
       </c>
@@ -6888,7 +6977,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2021</v>
       </c>
@@ -6907,10 +6996,6 @@
       <c r="F22" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
         <v>134</v>
       </c>
@@ -6918,7 +7003,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2021</v>
       </c>
@@ -6934,11 +7019,6 @@
       <c r="E23" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
         <v>134</v>
       </c>
@@ -6946,7 +7026,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2021</v>
       </c>
@@ -6962,11 +7042,6 @@
       <c r="E24" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
         <v>134</v>
       </c>
@@ -6974,7 +7049,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2020</v>
       </c>
@@ -6990,11 +7065,6 @@
       <c r="E25" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
         <v>134</v>
       </c>
@@ -7002,7 +7072,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2020</v>
       </c>
@@ -7018,11 +7088,6 @@
       <c r="E26" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
         <v>134</v>
       </c>
@@ -7030,7 +7095,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2020</v>
       </c>
@@ -7046,11 +7111,6 @@
       <c r="E27" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
         <v>134</v>
       </c>
@@ -7058,7 +7118,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>2020</v>
       </c>
@@ -7074,11 +7134,6 @@
       <c r="E28" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
         <v>134</v>
       </c>
@@ -7086,7 +7141,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>2019</v>
       </c>
@@ -7102,11 +7157,6 @@
       <c r="E29" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
         <v>134</v>
       </c>
@@ -7114,7 +7164,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>2019</v>
       </c>
@@ -7130,11 +7180,6 @@
       <c r="E30" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
         <v>134</v>
       </c>
@@ -7142,7 +7187,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>2018</v>
       </c>
@@ -7158,11 +7203,6 @@
       <c r="E31" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
         <v>134</v>
       </c>
@@ -7170,7 +7210,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>2018</v>
       </c>
@@ -7186,11 +7226,6 @@
       <c r="E32" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
         <v>134</v>
       </c>
@@ -7198,7 +7233,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>2017</v>
       </c>
@@ -7214,11 +7249,6 @@
       <c r="E33" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
         <v>134</v>
       </c>
@@ -7226,7 +7256,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>2017</v>
       </c>
@@ -7242,11 +7272,6 @@
       <c r="E34" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
         <v>134</v>
       </c>
@@ -7254,7 +7279,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>2017</v>
       </c>
@@ -7270,11 +7295,6 @@
       <c r="E35" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
         <v>134</v>
       </c>
@@ -7282,7 +7302,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>2017</v>
       </c>
@@ -7298,11 +7318,6 @@
       <c r="E36" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
         <v>134</v>
       </c>
@@ -7310,7 +7325,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>2017</v>
       </c>
@@ -7326,11 +7341,6 @@
       <c r="E37" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
         <v>134</v>
       </c>
@@ -7338,7 +7348,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>2017</v>
       </c>
@@ -7354,11 +7364,6 @@
       <c r="E38" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
         <v>134</v>
       </c>
@@ -7366,7 +7371,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>2017</v>
       </c>
@@ -7382,11 +7387,6 @@
       <c r="E39" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
         <v>134</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>2017</v>
       </c>
@@ -7410,11 +7410,6 @@
       <c r="E40" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
         <v>111</v>
       </c>
@@ -7422,7 +7417,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>2017</v>
       </c>
@@ -7438,11 +7433,6 @@
       <c r="E41" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
         <v>134</v>
       </c>
@@ -7450,7 +7440,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>2016</v>
       </c>
@@ -7466,11 +7456,6 @@
       <c r="E42" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
         <v>134</v>
       </c>
@@ -7478,7 +7463,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>2016</v>
       </c>
@@ -7494,11 +7479,6 @@
       <c r="E43" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
         <v>134</v>
       </c>
@@ -7506,7 +7486,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>2016</v>
       </c>
@@ -7522,11 +7502,6 @@
       <c r="E44" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
         <v>134</v>
       </c>
@@ -7534,7 +7509,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>2016</v>
       </c>
@@ -7550,11 +7525,6 @@
       <c r="E45" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
         <v>134</v>
       </c>
@@ -7562,7 +7532,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>2015</v>
       </c>
@@ -7578,11 +7548,6 @@
       <c r="E46" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
         <v>134</v>
       </c>
@@ -7590,7 +7555,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>2015</v>
       </c>
@@ -7606,11 +7571,6 @@
       <c r="E47" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
         <v>134</v>
       </c>
@@ -7618,7 +7578,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>2015</v>
       </c>
@@ -7634,11 +7594,6 @@
       <c r="E48" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
         <v>134</v>
       </c>
@@ -7646,7 +7601,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>2015</v>
       </c>
@@ -7662,11 +7617,6 @@
       <c r="E49" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
         <v>134</v>
       </c>
@@ -7674,7 +7624,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>2015</v>
       </c>
@@ -7690,11 +7640,6 @@
       <c r="E50" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
         <v>134</v>
       </c>
@@ -7702,7 +7647,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>2014</v>
       </c>
@@ -7718,11 +7663,6 @@
       <c r="E51" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
         <v>134</v>
       </c>
@@ -7730,7 +7670,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>2014</v>
       </c>
@@ -7746,11 +7686,6 @@
       <c r="E52" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
         <v>134</v>
       </c>
@@ -7758,7 +7693,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>2014</v>
       </c>
@@ -7774,11 +7709,6 @@
       <c r="E53" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
         <v>134</v>
       </c>
@@ -7786,7 +7716,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>2014</v>
       </c>
@@ -7802,11 +7732,6 @@
       <c r="E54" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
         <v>134</v>
       </c>
@@ -7814,7 +7739,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>2013</v>
       </c>
@@ -7830,11 +7755,6 @@
       <c r="E55" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
         <v>134</v>
       </c>
@@ -7842,7 +7762,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>2013</v>
       </c>
@@ -7858,11 +7778,6 @@
       <c r="E56" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
         <v>134</v>
       </c>
@@ -7870,7 +7785,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>2013</v>
       </c>
@@ -7886,11 +7801,6 @@
       <c r="E57" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
         <v>134</v>
       </c>
@@ -7898,7 +7808,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>2013</v>
       </c>
@@ -7914,11 +7824,6 @@
       <c r="E58" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
         <v>134</v>
       </c>
@@ -7926,7 +7831,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>2012</v>
       </c>
@@ -7942,11 +7847,6 @@
       <c r="E59" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
         <v>134</v>
       </c>
@@ -7954,7 +7854,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>2012</v>
       </c>
@@ -7970,11 +7870,6 @@
       <c r="E60" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
         <v>134</v>
       </c>
@@ -7982,7 +7877,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>2012</v>
       </c>
@@ -7998,11 +7893,6 @@
       <c r="E61" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
         <v>134</v>
       </c>
@@ -8010,7 +7900,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>2012</v>
       </c>
@@ -8026,11 +7916,6 @@
       <c r="E62" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
         <v>134</v>
       </c>
@@ -8038,7 +7923,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>2012</v>
       </c>
@@ -8054,11 +7939,6 @@
       <c r="E63" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
         <v>134</v>
       </c>
@@ -8066,7 +7946,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>2011</v>
       </c>
@@ -8082,11 +7962,6 @@
       <c r="E64" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
         <v>134</v>
       </c>
@@ -8094,7 +7969,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>2011</v>
       </c>
@@ -8110,11 +7985,6 @@
       <c r="E65" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
         <v>134</v>
       </c>
@@ -8122,7 +7992,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>2010</v>
       </c>
@@ -8138,11 +8008,6 @@
       <c r="E66" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
         <v>134</v>
       </c>
@@ -8150,7 +8015,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>2010</v>
       </c>
@@ -8166,11 +8031,6 @@
       <c r="E67" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
         <v>134</v>
       </c>
@@ -8178,7 +8038,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>2010</v>
       </c>
@@ -8194,11 +8054,6 @@
       <c r="E68" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
         <v>134</v>
       </c>
@@ -8206,7 +8061,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>2010</v>
       </c>
@@ -8222,11 +8077,6 @@
       <c r="E69" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
         <v>134</v>
       </c>
@@ -8234,7 +8084,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>2010</v>
       </c>
@@ -8250,11 +8100,6 @@
       <c r="E70" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
         <v>134</v>
       </c>
@@ -8262,7 +8107,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>2010</v>
       </c>
@@ -8278,11 +8123,6 @@
       <c r="E71" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
         <v>134</v>
       </c>
@@ -8290,7 +8130,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>2010</v>
       </c>
@@ -8306,11 +8146,6 @@
       <c r="E72" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
         <v>134</v>
       </c>
@@ -8318,7 +8153,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>2010</v>
       </c>
@@ -8334,11 +8169,6 @@
       <c r="E73" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
         <v>134</v>
       </c>
@@ -8346,7 +8176,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>2009</v>
       </c>
@@ -8362,11 +8192,6 @@
       <c r="E74" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
         <v>134</v>
       </c>
@@ -8374,7 +8199,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>2009</v>
       </c>
@@ -8390,11 +8215,6 @@
       <c r="E75" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
         <v>134</v>
       </c>
@@ -8402,7 +8222,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>2009</v>
       </c>
@@ -8418,11 +8238,6 @@
       <c r="E76" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
         <v>134</v>
       </c>
@@ -8430,7 +8245,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>2009</v>
       </c>
@@ -8446,11 +8261,6 @@
       <c r="E77" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
         <v>134</v>
       </c>
@@ -8458,7 +8268,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>2008</v>
       </c>
@@ -8474,11 +8284,6 @@
       <c r="E78" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
         <v>134</v>
       </c>
@@ -8486,7 +8291,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>2008</v>
       </c>
@@ -8502,11 +8307,6 @@
       <c r="E79" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
         <v>134</v>
       </c>
@@ -8514,7 +8314,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>2008</v>
       </c>
@@ -8530,11 +8330,6 @@
       <c r="E80" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
         <v>134</v>
       </c>
@@ -8542,7 +8337,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>2007</v>
       </c>
@@ -8558,11 +8353,6 @@
       <c r="E81" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
         <v>134</v>
       </c>
@@ -8570,7 +8360,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>2007</v>
       </c>
@@ -8586,11 +8376,6 @@
       <c r="E82" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
         <v>134</v>
       </c>
@@ -8598,7 +8383,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>2007</v>
       </c>
@@ -8614,11 +8399,6 @@
       <c r="E83" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
         <v>134</v>
       </c>
@@ -8626,7 +8406,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>2007</v>
       </c>
@@ -8642,11 +8422,6 @@
       <c r="E84" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
         <v>134</v>
       </c>
@@ -8654,7 +8429,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>2007</v>
       </c>
@@ -8670,11 +8445,6 @@
       <c r="E85" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
         <v>134</v>
       </c>
@@ -8682,7 +8452,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>2006</v>
       </c>
@@ -8698,11 +8468,6 @@
       <c r="E86" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
         <v>134</v>
       </c>
@@ -8710,7 +8475,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>2006</v>
       </c>
@@ -8726,11 +8491,6 @@
       <c r="E87" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
         <v>134</v>
       </c>
@@ -8738,7 +8498,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>2006</v>
       </c>
@@ -8754,11 +8514,6 @@
       <c r="E88" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
         <v>134</v>
       </c>
@@ -8766,7 +8521,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>2005</v>
       </c>
@@ -8782,11 +8537,6 @@
       <c r="E89" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
         <v>134</v>
       </c>
@@ -8794,7 +8544,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>2005</v>
       </c>
@@ -8810,11 +8560,6 @@
       <c r="E90" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
         <v>134</v>
       </c>
@@ -8822,7 +8567,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>2004</v>
       </c>
@@ -8838,11 +8583,6 @@
       <c r="E91" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
         <v>134</v>
       </c>
@@ -8850,7 +8590,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>2004</v>
       </c>
@@ -8866,11 +8606,6 @@
       <c r="E92" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
         <v>134</v>
       </c>
@@ -8878,7 +8613,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>2004</v>
       </c>
@@ -8894,11 +8629,6 @@
       <c r="E93" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
         <v>134</v>
       </c>
@@ -8906,7 +8636,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>2003</v>
       </c>
@@ -8922,11 +8652,6 @@
       <c r="E94" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
         <v>134</v>
       </c>
@@ -8934,7 +8659,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>2003</v>
       </c>
@@ -8950,11 +8675,6 @@
       <c r="E95" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
         <v>134</v>
       </c>
@@ -8962,7 +8682,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>2003</v>
       </c>
@@ -8978,11 +8698,6 @@
       <c r="E96" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
         <v>134</v>
       </c>
@@ -8990,7 +8705,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>2003</v>
       </c>
@@ -9006,11 +8721,6 @@
       <c r="E97" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
         <v>134</v>
       </c>
@@ -9018,7 +8728,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="98" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>2003</v>
       </c>
@@ -9034,11 +8744,6 @@
       <c r="E98" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
         <v>134</v>
       </c>
@@ -9046,7 +8751,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>2003</v>
       </c>
@@ -9062,11 +8767,6 @@
       <c r="E99" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
         <v>134</v>
       </c>
@@ -9075,17 +8775,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Featured" error="&quot;yes&quot; to show it on the homepage and mark it as featured." sqref="K2:K1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Featured" error="&quot;yes&quot; to show it on the homepage and mark it as featured." sqref="K2:K1000" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="L2:L1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="L2:L1000" xr:uid="{00000000-0002-0000-0800-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -1,61 +1,273 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10917"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31EB33B-A869-7449-8327-8BD8AC39B95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="README" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Settings" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="PI" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="PI Details" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Sites" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Members" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Alumni" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="News" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Publications" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Patents" state="visible" r:id="rId13"/>
+    <sheet name="README" sheetId="1" r:id="rId1"/>
+    <sheet name="Settings" sheetId="2" r:id="rId2"/>
+    <sheet name="PI" sheetId="3" r:id="rId3"/>
+    <sheet name="PI Details" sheetId="4" r:id="rId4"/>
+    <sheet name="Sites" sheetId="5" r:id="rId5"/>
+    <sheet name="Members" sheetId="6" r:id="rId6"/>
+    <sheet name="Alumni" sheetId="7" r:id="rId7"/>
+    <sheet name="News" sheetId="8" r:id="rId8"/>
+    <sheet name="Publications" sheetId="9" r:id="rId9"/>
+    <sheet name="Patents" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Group heading, e.g. "Appointments", "Education", "Honors", "Links". Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>The text of the bullet. Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Optional web address. If filled in, the item becomes a link.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Set to "no" to hide this row on the website without deleting it.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Short code used in the Site column of the Members and Alumni tabs, e.g. "JHU". Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Label shown on badges. Defaults to the code.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Optional badge colour as a hex code, e.g. #2B5CB8.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>"yes" for an active site, "no" for a past one.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
       <text>
         <r>
-          <t>Application or publication number.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>A code from the Sites tab. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000003000000}">
       <text>
         <r>
-          <t>e.g. USPTO, EPO, WIPO.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. PhD Student, Postdoctoral Fellow, Senior Scientist. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000004000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>One or two sentences on what this person works on. Leave blank to omit.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>File name of a photo in public/images/people, or a full web address. Leave blank to show initials.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Personal page, Google Scholar, ORCID, etc.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -65,35 +277,105 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
-          <t>Group heading, e.g. "Appointments", "Education", "Honors", "Links". Required.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
       <text>
         <r>
-          <t>The text of the bullet. Required.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. "2019–2022" or "2021".</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
       <text>
         <r>
-          <t>Optional web address. If filled in, the item becomes a link.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>A code from the Sites tab. Several sites can be joined with "/", e.g. "L/MDC".</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Position in the lab, e.g. PhD, Postdoc, MSc.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Current position. Leave blank if unknown.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Optional thesis title. The column only appears on the site if at least one alumnus has one.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -103,43 +385,78 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
       <text>
         <r>
-          <t>Short code used in the Site column of the Members and Alumni tabs, e.g. "JHU". Required.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Date of the news item, e.g. 2026-06-02. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000002000000}">
       <text>
         <r>
-          <t>Label shown on badges. Defaults to the code.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. Lab, Paper, Award, Press.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000003000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000004000000}">
       <text>
         <r>
-          <t>Optional badge colour as a hex code, e.g. #2B5CB8.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Optional "Read more" link. Can be a web address or a page on this site like /publications.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000005000000}">
       <text>
         <r>
-          <t>"yes" for an active site, "no" for a past one.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
     </comment>
@@ -148,56 +465,105 @@
 </file>
 
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000002000000}">
       <text>
         <r>
-          <t>A code from the Sites tab. Required.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000003000000}">
       <text>
         <r>
-          <t>e.g. PhD Student, Postdoctoral Fellow, Senior Scientist. Required.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Author list as it should appear, e.g. "Beagrie, R. A., Pombo, A.".</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000004000000}">
       <text>
         <r>
-          <t>One or two sentences on what this person works on. Leave blank to omit.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. "21(7), 735–775".</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000005000000}">
       <text>
         <r>
-          <t>File name of a photo in public/images/people, or a full web address. Leave blank to show initials.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. 10.1038/s41586-021-04081-2 or the full https://doi.org/… address.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000006000000}">
       <text>
         <r>
-          <t>Personal page, Google Scholar, ORCID, etc.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>"yes" to show it on the homepage and mark it as featured.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000007000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -207,160 +573,77 @@
 </file>
 
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000001000000}">
       <text>
         <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000002000000}">
       <text>
         <r>
-          <t>e.g. "2019–2022" or "2021".</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <t>A code from the Sites tab. Several sites can be joined with "/", e.g. "L/MDC".</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <t>Position in the lab, e.g. PhD, Postdoc, MSc.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <t>Current position. Leave blank if unknown.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <t>Optional thesis title. The column only appears on the site if at least one alumnus has one.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <t>Set to "no" to hide this row on the website without deleting it.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <t>Date of the news item, e.g. 2026-06-02. Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <t>e.g. Lab, Paper, Award, Press.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000003000000}">
       <text>
         <r>
-          <t>Optional "Read more" link. Can be a web address or a page on this site like /publications.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Application or publication number.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
       <text>
         <r>
-          <t>Set to "no" to hide this row on the website without deleting it.</t>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>e.g. USPTO, EPO, WIPO.</t>
         </r>
       </text>
     </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000005000000}">
       <text>
         <r>
-          <t>Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <t>Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <t>Author list as it should appear, e.g. "Beagrie, R. A., Pombo, A.".</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <t>e.g. "21(7), 735–775".</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <t>e.g. 10.1038/s41586-021-04081-2 or the full https://doi.org/… address.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <t>"yes" to show it on the homepage and mark it as featured.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0">
-      <text>
-        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -370,7 +653,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="797">
   <si>
     <t>Lab website content</t>
   </si>
@@ -576,7 +859,7 @@
     <t>Bold author names</t>
   </si>
   <si>
-    <t xml:space="preserve">Pombo, A.
+    <t>Pombo, A.
 A. Pombo
 Pombo A</t>
   </si>
@@ -587,7 +870,7 @@
     <t>Lab description</t>
   </si>
   <si>
-    <t xml:space="preserve">We study mechanisms of gene expression at multiple levels, from the local action of transcription factors, to long-range chromatin looping events that connect regulatory DNA sequences with the genes they regulate, to how whole chromosomes are positioned within cell nuclei. Binding of transcription factors at regulatory sequences helps recruit chromatin remodelers and the transcription machinery to transcription sites.
+    <t>We study mechanisms of gene expression at multiple levels, from the local action of transcription factors, to long-range chromatin looping events that connect regulatory DNA sequences with the genes they regulate, to how whole chromosomes are positioned within cell nuclei. Binding of transcription factors at regulatory sequences helps recruit chromatin remodelers and the transcription machinery to transcription sites.
 Upon recruitment, RNA polymerases either remain primed for subsequent activation (e.g. after environmental stress, during differentiation or disease), or directly transcribe the DNA template into RNA molecules, which code for proteins or for structural RNAs that constitute many enzymatic complexes.
 An increasingly important aspect of gene regulation is the three-dimensional folding of the genome, and the mechanisms that control physical contacts of distant regulatory DNA sequences with gene promoters to activate gene expression. To directly measure genome topologies, our group developed Genome Architecture Mapping (GAM).
 Our long-term strategy for unravelling the principles of genome function in higher eukaryotes aims to integrate multiple parameters, which is becoming increasingly possible with state-of-the-art developments in single cell genomics, molecular biology, epigenetics, nuclear imaging, and genetics.</t>
@@ -599,7 +882,7 @@
     <t>Research description</t>
   </si>
   <si>
-    <t xml:space="preserve">Our main goal is to unravel the diverse mechanisms of mammalian gene regulation and their roles in development and disease. Gene activation is controlled locally through transcription factors, chromatin modifiers, and the transcription and RNA processing machineries. Gene expression is also intricately regulated by the three-dimensional (3D) structure of the genome, which modifies the location of genes relative to activating or repressing biochemical environments. Repressing nuclear locations include the nuclear lamina and heterochromatin. Activating 3D genome conformations can work by regulating the physical proximity between regulatory regions and their responsive genes. As many disease-associated genetic variants fall in non-coding regulatory elements scattered in the genome, our work aims to advance the functional interpretation of the linear genome sequence. We especially put effort in devising experimental and computational approaches to map 3D genome structure in different cell types, in development and in disease, to study developmental and disease mechanisms, towards novel diagnostics, prognostics and therapeutics.
+    <t>Our main goal is to unravel the diverse mechanisms of mammalian gene regulation and their roles in development and disease. Gene activation is controlled locally through transcription factors, chromatin modifiers, and the transcription and RNA processing machineries. Gene expression is also intricately regulated by the three-dimensional (3D) structure of the genome, which modifies the location of genes relative to activating or repressing biochemical environments. Repressing nuclear locations include the nuclear lamina and heterochromatin. Activating 3D genome conformations can work by regulating the physical proximity between regulatory regions and their responsive genes. As many disease-associated genetic variants fall in non-coding regulatory elements scattered in the genome, our work aims to advance the functional interpretation of the linear genome sequence. We especially put effort in devising experimental and computational approaches to map 3D genome structure in different cell types, in development and in disease, to study developmental and disease mechanisms, towards novel diagnostics, prognostics and therapeutics.
 We have developed Genome Architecture Mapping (GAM), an orthogonal 3D genome folding mapping technology which yields fine maps of chromatin contacts from small cell numbers (500−1000), and is uniquely powerful to quantify different metrics of 3D genome structure, such as multiway contacts and chromatin melting. With immuno-GAM, we introduced the selection of cell types within complex tissues to enable the application of GAM in rare cells, such as dopaminergic neurons in the midbrain. GAM is an inherently suited platform for multimodal molecular phenotyping of biological samples, from genome sequence and 3D structure, to transcript and protein quantification. As a first step towards GAM multimodality, we have developed Oligo-Seq, a novel approach to detect minute amounts of specific RNA sequences within thin tissue cryosections, as used for GAM. We currently develop the application of Oligo-seq in spatial transcriptomics, especially in archival clinical samples (e.g. FFPE). By further developing multimodal integration of 3D genome topology, with the abundance of specific regulatory factors and gene expression, at the single-cell level, we aim to extract dynamic states of gene regulation and cause-effect relationships that connect 3D genome structure with gene expression. Ultimately, we seek to advance the interpretability of the linear genome sequence, to gain a deeper understanding of 3D genome regulation mechanisms in gene expression, and to advance their predictability.</t>
   </si>
   <si>
@@ -852,7 +1135,7 @@
     <t>Max Delbrück Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Berlin Institute for Medical Systems Biology (BIMSB)
+    <t>Berlin Institute for Medical Systems Biology (BIMSB)
 Hannoversche Straße 28, 10115 Berlin</t>
   </si>
   <si>
@@ -2765,41 +3048,63 @@
   </si>
   <si>
     <t>Granted</t>
+  </si>
+  <si>
+    <t>akukalev.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
+      <sz val="11"/>
       <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3197,36 +3502,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="22" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
+    </row>
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -3234,7 +3536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -3242,7 +3544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -3250,7 +3552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -3258,7 +3560,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -3266,13 +3568,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
@@ -3280,7 +3581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -3288,7 +3589,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
@@ -3296,7 +3597,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -3304,7 +3605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -3312,7 +3613,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -3320,13 +3621,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="3"/>
-    </row>
-    <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -3334,7 +3634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
@@ -3342,7 +3642,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
@@ -3350,7 +3650,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
@@ -3358,7 +3658,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>35</v>
       </c>
@@ -3366,7 +3666,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -3374,7 +3674,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>39</v>
       </c>
@@ -3382,7 +3682,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>41</v>
       </c>
@@ -3390,7 +3690,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>43</v>
       </c>
@@ -3400,14 +3700,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -3418,7 +3718,7 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>422</v>
       </c>
@@ -3444,7 +3744,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2026</v>
       </c>
@@ -3463,12 +3763,11 @@
       <c r="F2" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2025</v>
       </c>
@@ -3487,38 +3786,37 @@
       <c r="F3" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
         <v>134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Status" error="Choose a value from the list." sqref="E2:E1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Status" error="Choose a value from the list." sqref="E2:E1000" xr:uid="{00000000-0002-0000-0900-000000000000}">
       <formula1>"Filed,Published,Granted"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="H2:H1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="H2:H1000" xr:uid="{00000000-0002-0000-0900-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>45</v>
       </c>
@@ -3529,7 +3827,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>48</v>
       </c>
@@ -3540,7 +3838,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>51</v>
       </c>
@@ -3551,7 +3849,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>54</v>
       </c>
@@ -3562,7 +3860,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>57</v>
       </c>
@@ -3573,7 +3871,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>60</v>
       </c>
@@ -3584,7 +3882,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>62</v>
       </c>
@@ -3595,7 +3893,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>64</v>
       </c>
@@ -3606,7 +3904,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>67</v>
       </c>
@@ -3617,7 +3915,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" s="2" customFormat="1" ht="224" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>70</v>
       </c>
@@ -3628,7 +3926,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" s="2" customFormat="1" ht="395" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>73</v>
       </c>
@@ -3639,7 +3937,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>76</v>
       </c>
@@ -3650,7 +3948,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>79</v>
       </c>
@@ -3661,7 +3959,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>82</v>
       </c>
@@ -3672,7 +3970,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>85</v>
       </c>
@@ -3683,7 +3981,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>88</v>
       </c>
@@ -3696,21 +3994,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>45</v>
       </c>
@@ -3721,7 +4019,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>91</v>
       </c>
@@ -3730,7 +4028,7 @@
       </c>
       <c r="C2" s="6"/>
     </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>93</v>
       </c>
@@ -3741,7 +4039,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>96</v>
       </c>
@@ -3752,7 +4050,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>99</v>
       </c>
@@ -3763,7 +4061,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>99</v>
       </c>
@@ -3774,7 +4072,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" s="2" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>102</v>
       </c>
@@ -3785,7 +4083,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>102</v>
       </c>
@@ -3798,21 +4096,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>106</v>
       </c>
@@ -3826,283 +4124,260 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>132</v>
       </c>
@@ -4116,7 +4391,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>132</v>
       </c>
@@ -4130,7 +4405,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>132</v>
       </c>
@@ -4145,22 +4420,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="D2:D1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="D2:D1000" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4171,7 +4446,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>144</v>
       </c>
@@ -4194,7 +4469,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>151</v>
       </c>
@@ -4217,7 +4492,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>156</v>
       </c>
@@ -4240,7 +4515,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>161</v>
       </c>
@@ -4250,32 +4525,30 @@
       <c r="C4" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
         <v>134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Current site" error="&quot;yes&quot; for an active site, &quot;no&quot; for a past one." sqref="G2:G1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Current site" error="&quot;yes&quot; for an active site, &quot;no&quot; for a past one." sqref="G2:G1000" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -4286,7 +4559,7 @@
     <col min="8" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>91</v>
       </c>
@@ -4315,7 +4588,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>170</v>
       </c>
@@ -4328,17 +4601,14 @@
       <c r="D2" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>174</v>
       </c>
@@ -4351,17 +4621,14 @@
       <c r="D3" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="2" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>178</v>
       </c>
@@ -4380,13 +4647,11 @@
       <c r="F4" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>183</v>
       </c>
@@ -4405,13 +4670,11 @@
       <c r="F5" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" s="2" customFormat="1" ht="112" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>186</v>
       </c>
@@ -4430,13 +4693,11 @@
       <c r="F6" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>190</v>
       </c>
@@ -4449,17 +4710,14 @@
       <c r="D7" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>192</v>
       </c>
@@ -4472,17 +4730,14 @@
       <c r="D8" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>195</v>
       </c>
@@ -4495,17 +4750,14 @@
       <c r="D9" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>198</v>
       </c>
@@ -4518,17 +4770,14 @@
       <c r="D10" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>200</v>
       </c>
@@ -4541,11 +4790,12 @@
       <c r="D11" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="G11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>796</v>
+      </c>
       <c r="H11" s="2" t="s">
         <v>203</v>
       </c>
@@ -4553,7 +4803,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>204</v>
       </c>
@@ -4566,17 +4816,14 @@
       <c r="D12" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>206</v>
       </c>
@@ -4589,17 +4836,14 @@
       <c r="D13" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>208</v>
       </c>
@@ -4612,17 +4856,14 @@
       <c r="D14" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="2" customFormat="1" ht="80" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>210</v>
       </c>
@@ -4641,7 +4882,6 @@
       <c r="F15" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
         <v>214</v>
       </c>
@@ -4649,7 +4889,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>215</v>
       </c>
@@ -4662,15 +4902,11 @@
       <c r="D16" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>217</v>
       </c>
@@ -4683,15 +4919,11 @@
       <c r="D17" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>218</v>
       </c>
@@ -4704,17 +4936,14 @@
       <c r="D18" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>221</v>
       </c>
@@ -4727,17 +4956,14 @@
       <c r="D19" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>223</v>
       </c>
@@ -4750,17 +4976,14 @@
       <c r="D20" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>226</v>
       </c>
@@ -4773,36 +4996,42 @@
       <c r="D21" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" showErrorMessage="1" errorStyle="warning" errorTitle="Site" error="A code from the Sites tab." sqref="B2:B1000">
-      <formula1>Sites!$A$2:$A$50</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="I2:I1000">
+  <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="I2:I1000" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" errorStyle="warning" showErrorMessage="1" errorTitle="Site" error="A code from the Sites tab." xr:uid="{00000000-0002-0000-0500-000000000000}">
+          <x14:formula1>
+            <xm:f>Sites!$A$2:$A$50</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B1000</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G58"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4811,7 +5040,7 @@
     <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>91</v>
       </c>
@@ -4834,7 +5063,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>232</v>
       </c>
@@ -4847,13 +5076,11 @@
       <c r="D2" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>235</v>
       </c>
@@ -4869,12 +5096,11 @@
       <c r="E3" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>239</v>
       </c>
@@ -4890,12 +5116,11 @@
       <c r="E4" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>241</v>
       </c>
@@ -4911,12 +5136,11 @@
       <c r="E5" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>244</v>
       </c>
@@ -4932,12 +5156,11 @@
       <c r="E6" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>248</v>
       </c>
@@ -4953,12 +5176,11 @@
       <c r="E7" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>251</v>
       </c>
@@ -4974,12 +5196,11 @@
       <c r="E8" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>253</v>
       </c>
@@ -4992,13 +5213,11 @@
       <c r="D9" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>254</v>
       </c>
@@ -5014,12 +5233,11 @@
       <c r="E10" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>257</v>
       </c>
@@ -5035,12 +5253,11 @@
       <c r="E11" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>260</v>
       </c>
@@ -5056,12 +5273,11 @@
       <c r="E12" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>264</v>
       </c>
@@ -5077,12 +5293,11 @@
       <c r="E13" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>267</v>
       </c>
@@ -5098,12 +5313,11 @@
       <c r="E14" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>270</v>
       </c>
@@ -5119,12 +5333,11 @@
       <c r="E15" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>272</v>
       </c>
@@ -5140,12 +5353,11 @@
       <c r="E16" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>275</v>
       </c>
@@ -5161,12 +5373,11 @@
       <c r="E17" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>277</v>
       </c>
@@ -5182,12 +5393,11 @@
       <c r="E18" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>280</v>
       </c>
@@ -5203,12 +5413,11 @@
       <c r="E19" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>284</v>
       </c>
@@ -5224,12 +5433,11 @@
       <c r="E20" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>287</v>
       </c>
@@ -5245,12 +5453,11 @@
       <c r="E21" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>289</v>
       </c>
@@ -5266,12 +5473,11 @@
       <c r="E22" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>292</v>
       </c>
@@ -5287,12 +5493,11 @@
       <c r="E23" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>295</v>
       </c>
@@ -5305,13 +5510,11 @@
       <c r="D24" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>296</v>
       </c>
@@ -5327,12 +5530,11 @@
       <c r="E25" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>299</v>
       </c>
@@ -5348,12 +5550,11 @@
       <c r="E26" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>302</v>
       </c>
@@ -5369,12 +5570,11 @@
       <c r="E27" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>305</v>
       </c>
@@ -5390,12 +5590,11 @@
       <c r="E28" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>308</v>
       </c>
@@ -5411,12 +5610,11 @@
       <c r="E29" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>310</v>
       </c>
@@ -5432,12 +5630,11 @@
       <c r="E30" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>313</v>
       </c>
@@ -5453,12 +5650,11 @@
       <c r="E31" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>315</v>
       </c>
@@ -5474,12 +5670,11 @@
       <c r="E32" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>318</v>
       </c>
@@ -5495,12 +5690,11 @@
       <c r="E33" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>321</v>
       </c>
@@ -5516,12 +5710,11 @@
       <c r="E34" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>325</v>
       </c>
@@ -5537,12 +5730,11 @@
       <c r="E35" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>328</v>
       </c>
@@ -5558,12 +5750,11 @@
       <c r="E36" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>331</v>
       </c>
@@ -5579,12 +5770,11 @@
       <c r="E37" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>334</v>
       </c>
@@ -5600,12 +5790,11 @@
       <c r="E38" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>336</v>
       </c>
@@ -5621,12 +5810,11 @@
       <c r="E39" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>339</v>
       </c>
@@ -5642,12 +5830,11 @@
       <c r="E40" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>342</v>
       </c>
@@ -5663,12 +5850,11 @@
       <c r="E41" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>345</v>
       </c>
@@ -5684,12 +5870,11 @@
       <c r="E42" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>348</v>
       </c>
@@ -5705,12 +5890,11 @@
       <c r="E43" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>351</v>
       </c>
@@ -5726,12 +5910,11 @@
       <c r="E44" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>354</v>
       </c>
@@ -5747,12 +5930,11 @@
       <c r="E45" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>357</v>
       </c>
@@ -5765,13 +5947,11 @@
       <c r="D46" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>360</v>
       </c>
@@ -5784,13 +5964,11 @@
       <c r="D47" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>361</v>
       </c>
@@ -5806,12 +5984,11 @@
       <c r="E48" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>364</v>
       </c>
@@ -5824,13 +6001,11 @@
       <c r="D49" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>366</v>
       </c>
@@ -5843,13 +6018,11 @@
       <c r="D50" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>368</v>
       </c>
@@ -5862,13 +6035,11 @@
       <c r="D51" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>369</v>
       </c>
@@ -5884,12 +6055,11 @@
       <c r="E52" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>372</v>
       </c>
@@ -5905,12 +6075,11 @@
       <c r="E53" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>375</v>
       </c>
@@ -5923,89 +6092,71 @@
       <c r="D54" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="G2:G1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="G2:G1000" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" style="7" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6014,7 +6165,7 @@
     <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>381</v>
       </c>
@@ -6034,7 +6185,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>46212</v>
       </c>
@@ -6054,7 +6205,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>46175</v>
       </c>
@@ -6067,12 +6218,11 @@
       <c r="D3" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>45938</v>
       </c>
@@ -6092,7 +6242,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>45799</v>
       </c>
@@ -6112,7 +6262,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>45637</v>
       </c>
@@ -6132,7 +6282,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>45333</v>
       </c>
@@ -6152,7 +6302,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>45096</v>
       </c>
@@ -6172,7 +6322,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>44980</v>
       </c>
@@ -6192,7 +6342,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>44517</v>
       </c>
@@ -6212,7 +6362,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>44120</v>
       </c>
@@ -6232,7 +6382,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>43766</v>
       </c>
@@ -6253,22 +6403,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="F2:F1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="F2:F1000" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:L99"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
@@ -6280,7 +6430,7 @@
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>422</v>
       </c>
@@ -6318,7 +6468,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>2026</v>
       </c>
@@ -6337,10 +6487,6 @@
       <c r="F2" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
         <v>134</v>
       </c>
@@ -6348,7 +6494,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2026</v>
       </c>
@@ -6361,14 +6507,9 @@
       <c r="D3" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
         <v>134</v>
       </c>
@@ -6376,7 +6517,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2026</v>
       </c>
@@ -6389,14 +6530,9 @@
       <c r="D4" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
         <v>134</v>
       </c>
@@ -6404,7 +6540,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2026</v>
       </c>
@@ -6417,14 +6553,9 @@
       <c r="D5" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
         <v>134</v>
       </c>
@@ -6432,7 +6563,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2025</v>
       </c>
@@ -6445,14 +6576,9 @@
       <c r="D6" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
         <v>134</v>
       </c>
@@ -6460,7 +6586,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2025</v>
       </c>
@@ -6479,10 +6605,6 @@
       <c r="F7" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
         <v>134</v>
       </c>
@@ -6490,7 +6612,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2025</v>
       </c>
@@ -6509,10 +6631,6 @@
       <c r="F8" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
         <v>111</v>
       </c>
@@ -6520,7 +6638,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2025</v>
       </c>
@@ -6533,14 +6651,9 @@
       <c r="D9" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
         <v>134</v>
       </c>
@@ -6548,7 +6661,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="2" customFormat="1" ht="96" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2024</v>
       </c>
@@ -6564,10 +6677,6 @@
       <c r="E10" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
         <v>468</v>
       </c>
@@ -6578,7 +6687,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -6594,11 +6703,6 @@
       <c r="E11" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
         <v>134</v>
       </c>
@@ -6606,7 +6710,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" s="2" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2024</v>
       </c>
@@ -6619,14 +6723,9 @@
       <c r="D12" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
         <v>134</v>
       </c>
@@ -6634,7 +6733,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2024</v>
       </c>
@@ -6647,14 +6746,9 @@
       <c r="D13" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
         <v>134</v>
       </c>
@@ -6662,7 +6756,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2024</v>
       </c>
@@ -6675,14 +6769,9 @@
       <c r="D14" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
         <v>134</v>
       </c>
@@ -6690,7 +6779,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2023</v>
       </c>
@@ -6706,11 +6795,6 @@
       <c r="E15" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
         <v>134</v>
       </c>
@@ -6718,7 +6802,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2023</v>
       </c>
@@ -6737,10 +6821,6 @@
       <c r="F16" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
         <v>111</v>
       </c>
@@ -6748,7 +6828,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2023</v>
       </c>
@@ -6764,11 +6844,6 @@
       <c r="E17" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
         <v>134</v>
       </c>
@@ -6776,7 +6851,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2022</v>
       </c>
@@ -6792,11 +6867,6 @@
       <c r="E18" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
         <v>134</v>
       </c>
@@ -6804,7 +6874,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2022</v>
       </c>
@@ -6820,11 +6890,6 @@
       <c r="E19" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
         <v>134</v>
       </c>
@@ -6832,7 +6897,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2022</v>
       </c>
@@ -6848,11 +6913,6 @@
       <c r="E20" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
         <v>134</v>
       </c>
@@ -6860,7 +6920,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2021</v>
       </c>
@@ -6876,11 +6936,6 @@
       <c r="E21" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
         <v>134</v>
       </c>
@@ -6888,7 +6943,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2021</v>
       </c>
@@ -6907,10 +6962,6 @@
       <c r="F22" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
         <v>134</v>
       </c>
@@ -6918,7 +6969,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2021</v>
       </c>
@@ -6934,11 +6985,6 @@
       <c r="E23" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
         <v>134</v>
       </c>
@@ -6946,7 +6992,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2021</v>
       </c>
@@ -6962,11 +7008,6 @@
       <c r="E24" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
         <v>134</v>
       </c>
@@ -6974,7 +7015,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2020</v>
       </c>
@@ -6990,11 +7031,6 @@
       <c r="E25" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
         <v>134</v>
       </c>
@@ -7002,7 +7038,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2020</v>
       </c>
@@ -7018,11 +7054,6 @@
       <c r="E26" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
         <v>134</v>
       </c>
@@ -7030,7 +7061,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2020</v>
       </c>
@@ -7046,11 +7077,6 @@
       <c r="E27" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
         <v>134</v>
       </c>
@@ -7058,7 +7084,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>2020</v>
       </c>
@@ -7074,11 +7100,6 @@
       <c r="E28" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
         <v>134</v>
       </c>
@@ -7086,7 +7107,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>2019</v>
       </c>
@@ -7102,11 +7123,6 @@
       <c r="E29" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
         <v>134</v>
       </c>
@@ -7114,7 +7130,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>2019</v>
       </c>
@@ -7130,11 +7146,6 @@
       <c r="E30" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
         <v>134</v>
       </c>
@@ -7142,7 +7153,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>2018</v>
       </c>
@@ -7158,11 +7169,6 @@
       <c r="E31" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
         <v>134</v>
       </c>
@@ -7170,7 +7176,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>2018</v>
       </c>
@@ -7186,11 +7192,6 @@
       <c r="E32" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
         <v>134</v>
       </c>
@@ -7198,7 +7199,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>2017</v>
       </c>
@@ -7214,11 +7215,6 @@
       <c r="E33" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
         <v>134</v>
       </c>
@@ -7226,7 +7222,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>2017</v>
       </c>
@@ -7242,11 +7238,6 @@
       <c r="E34" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
         <v>134</v>
       </c>
@@ -7254,7 +7245,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>2017</v>
       </c>
@@ -7270,11 +7261,6 @@
       <c r="E35" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
         <v>134</v>
       </c>
@@ -7282,7 +7268,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>2017</v>
       </c>
@@ -7298,11 +7284,6 @@
       <c r="E36" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
         <v>134</v>
       </c>
@@ -7310,7 +7291,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>2017</v>
       </c>
@@ -7326,11 +7307,6 @@
       <c r="E37" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
         <v>134</v>
       </c>
@@ -7338,7 +7314,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>2017</v>
       </c>
@@ -7354,11 +7330,6 @@
       <c r="E38" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
         <v>134</v>
       </c>
@@ -7366,7 +7337,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>2017</v>
       </c>
@@ -7382,11 +7353,6 @@
       <c r="E39" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
         <v>134</v>
       </c>
@@ -7394,7 +7360,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>2017</v>
       </c>
@@ -7410,11 +7376,6 @@
       <c r="E40" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
         <v>111</v>
       </c>
@@ -7422,7 +7383,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>2017</v>
       </c>
@@ -7438,11 +7399,6 @@
       <c r="E41" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
         <v>134</v>
       </c>
@@ -7450,7 +7406,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>2016</v>
       </c>
@@ -7466,11 +7422,6 @@
       <c r="E42" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
         <v>134</v>
       </c>
@@ -7478,7 +7429,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>2016</v>
       </c>
@@ -7494,11 +7445,6 @@
       <c r="E43" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
         <v>134</v>
       </c>
@@ -7506,7 +7452,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>2016</v>
       </c>
@@ -7522,11 +7468,6 @@
       <c r="E44" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
         <v>134</v>
       </c>
@@ -7534,7 +7475,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>2016</v>
       </c>
@@ -7550,11 +7491,6 @@
       <c r="E45" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
         <v>134</v>
       </c>
@@ -7562,7 +7498,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>2015</v>
       </c>
@@ -7578,11 +7514,6 @@
       <c r="E46" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
         <v>134</v>
       </c>
@@ -7590,7 +7521,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>2015</v>
       </c>
@@ -7606,11 +7537,6 @@
       <c r="E47" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
         <v>134</v>
       </c>
@@ -7618,7 +7544,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>2015</v>
       </c>
@@ -7634,11 +7560,6 @@
       <c r="E48" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
         <v>134</v>
       </c>
@@ -7646,7 +7567,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>2015</v>
       </c>
@@ -7662,11 +7583,6 @@
       <c r="E49" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
         <v>134</v>
       </c>
@@ -7674,7 +7590,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>2015</v>
       </c>
@@ -7690,11 +7606,6 @@
       <c r="E50" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
         <v>134</v>
       </c>
@@ -7702,7 +7613,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>2014</v>
       </c>
@@ -7718,11 +7629,6 @@
       <c r="E51" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
         <v>134</v>
       </c>
@@ -7730,7 +7636,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>2014</v>
       </c>
@@ -7746,11 +7652,6 @@
       <c r="E52" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
         <v>134</v>
       </c>
@@ -7758,7 +7659,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>2014</v>
       </c>
@@ -7774,11 +7675,6 @@
       <c r="E53" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
         <v>134</v>
       </c>
@@ -7786,7 +7682,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>2014</v>
       </c>
@@ -7802,11 +7698,6 @@
       <c r="E54" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
         <v>134</v>
       </c>
@@ -7814,7 +7705,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>2013</v>
       </c>
@@ -7830,11 +7721,6 @@
       <c r="E55" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
         <v>134</v>
       </c>
@@ -7842,7 +7728,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>2013</v>
       </c>
@@ -7858,11 +7744,6 @@
       <c r="E56" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
         <v>134</v>
       </c>
@@ -7870,7 +7751,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>2013</v>
       </c>
@@ -7886,11 +7767,6 @@
       <c r="E57" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
         <v>134</v>
       </c>
@@ -7898,7 +7774,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>2013</v>
       </c>
@@ -7914,11 +7790,6 @@
       <c r="E58" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
         <v>134</v>
       </c>
@@ -7926,7 +7797,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>2012</v>
       </c>
@@ -7942,11 +7813,6 @@
       <c r="E59" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
         <v>134</v>
       </c>
@@ -7954,7 +7820,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>2012</v>
       </c>
@@ -7970,11 +7836,6 @@
       <c r="E60" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
         <v>134</v>
       </c>
@@ -7982,7 +7843,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>2012</v>
       </c>
@@ -7998,11 +7859,6 @@
       <c r="E61" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
         <v>134</v>
       </c>
@@ -8010,7 +7866,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>2012</v>
       </c>
@@ -8026,11 +7882,6 @@
       <c r="E62" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
         <v>134</v>
       </c>
@@ -8038,7 +7889,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>2012</v>
       </c>
@@ -8054,11 +7905,6 @@
       <c r="E63" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
         <v>134</v>
       </c>
@@ -8066,7 +7912,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>2011</v>
       </c>
@@ -8082,11 +7928,6 @@
       <c r="E64" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
         <v>134</v>
       </c>
@@ -8094,7 +7935,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>2011</v>
       </c>
@@ -8110,11 +7951,6 @@
       <c r="E65" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
         <v>134</v>
       </c>
@@ -8122,7 +7958,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>2010</v>
       </c>
@@ -8138,11 +7974,6 @@
       <c r="E66" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
         <v>134</v>
       </c>
@@ -8150,7 +7981,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>2010</v>
       </c>
@@ -8166,11 +7997,6 @@
       <c r="E67" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
         <v>134</v>
       </c>
@@ -8178,7 +8004,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>2010</v>
       </c>
@@ -8194,11 +8020,6 @@
       <c r="E68" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
         <v>134</v>
       </c>
@@ -8206,7 +8027,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>2010</v>
       </c>
@@ -8222,11 +8043,6 @@
       <c r="E69" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
         <v>134</v>
       </c>
@@ -8234,7 +8050,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>2010</v>
       </c>
@@ -8250,11 +8066,6 @@
       <c r="E70" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
         <v>134</v>
       </c>
@@ -8262,7 +8073,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>2010</v>
       </c>
@@ -8278,11 +8089,6 @@
       <c r="E71" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
         <v>134</v>
       </c>
@@ -8290,7 +8096,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>2010</v>
       </c>
@@ -8306,11 +8112,6 @@
       <c r="E72" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
         <v>134</v>
       </c>
@@ -8318,7 +8119,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>2010</v>
       </c>
@@ -8334,11 +8135,6 @@
       <c r="E73" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
         <v>134</v>
       </c>
@@ -8346,7 +8142,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>2009</v>
       </c>
@@ -8362,11 +8158,6 @@
       <c r="E74" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
         <v>134</v>
       </c>
@@ -8374,7 +8165,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>2009</v>
       </c>
@@ -8390,11 +8181,6 @@
       <c r="E75" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
         <v>134</v>
       </c>
@@ -8402,7 +8188,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>2009</v>
       </c>
@@ -8418,11 +8204,6 @@
       <c r="E76" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
         <v>134</v>
       </c>
@@ -8430,7 +8211,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>2009</v>
       </c>
@@ -8446,11 +8227,6 @@
       <c r="E77" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
         <v>134</v>
       </c>
@@ -8458,7 +8234,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>2008</v>
       </c>
@@ -8474,11 +8250,6 @@
       <c r="E78" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
         <v>134</v>
       </c>
@@ -8486,7 +8257,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>2008</v>
       </c>
@@ -8502,11 +8273,6 @@
       <c r="E79" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
         <v>134</v>
       </c>
@@ -8514,7 +8280,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>2008</v>
       </c>
@@ -8530,11 +8296,6 @@
       <c r="E80" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
         <v>134</v>
       </c>
@@ -8542,7 +8303,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>2007</v>
       </c>
@@ -8558,11 +8319,6 @@
       <c r="E81" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
         <v>134</v>
       </c>
@@ -8570,7 +8326,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>2007</v>
       </c>
@@ -8586,11 +8342,6 @@
       <c r="E82" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
         <v>134</v>
       </c>
@@ -8598,7 +8349,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>2007</v>
       </c>
@@ -8614,11 +8365,6 @@
       <c r="E83" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
         <v>134</v>
       </c>
@@ -8626,7 +8372,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>2007</v>
       </c>
@@ -8642,11 +8388,6 @@
       <c r="E84" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
         <v>134</v>
       </c>
@@ -8654,7 +8395,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>2007</v>
       </c>
@@ -8670,11 +8411,6 @@
       <c r="E85" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
         <v>134</v>
       </c>
@@ -8682,7 +8418,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>2006</v>
       </c>
@@ -8698,11 +8434,6 @@
       <c r="E86" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
         <v>134</v>
       </c>
@@ -8710,7 +8441,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>2006</v>
       </c>
@@ -8726,11 +8457,6 @@
       <c r="E87" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
         <v>134</v>
       </c>
@@ -8738,7 +8464,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>2006</v>
       </c>
@@ -8754,11 +8480,6 @@
       <c r="E88" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
         <v>134</v>
       </c>
@@ -8766,7 +8487,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>2005</v>
       </c>
@@ -8782,11 +8503,6 @@
       <c r="E89" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
         <v>134</v>
       </c>
@@ -8794,7 +8510,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>2005</v>
       </c>
@@ -8810,11 +8526,6 @@
       <c r="E90" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
         <v>134</v>
       </c>
@@ -8822,7 +8533,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>2004</v>
       </c>
@@ -8838,11 +8549,6 @@
       <c r="E91" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
         <v>134</v>
       </c>
@@ -8850,7 +8556,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>2004</v>
       </c>
@@ -8866,11 +8572,6 @@
       <c r="E92" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
         <v>134</v>
       </c>
@@ -8878,7 +8579,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>2004</v>
       </c>
@@ -8894,11 +8595,6 @@
       <c r="E93" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
         <v>134</v>
       </c>
@@ -8906,7 +8602,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>2003</v>
       </c>
@@ -8922,11 +8618,6 @@
       <c r="E94" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
         <v>134</v>
       </c>
@@ -8934,7 +8625,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>2003</v>
       </c>
@@ -8950,11 +8641,6 @@
       <c r="E95" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
         <v>134</v>
       </c>
@@ -8962,7 +8648,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>2003</v>
       </c>
@@ -8978,11 +8664,6 @@
       <c r="E96" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
         <v>134</v>
       </c>
@@ -8990,7 +8671,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>2003</v>
       </c>
@@ -9006,11 +8687,6 @@
       <c r="E97" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
         <v>134</v>
       </c>
@@ -9018,7 +8694,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="98" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>2003</v>
       </c>
@@ -9034,11 +8710,6 @@
       <c r="E98" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
         <v>134</v>
       </c>
@@ -9046,7 +8717,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>2003</v>
       </c>
@@ -9062,11 +8733,6 @@
       <c r="E99" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
         <v>134</v>
       </c>
@@ -9075,17 +8741,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Featured" error="&quot;yes&quot; to show it on the homepage and mark it as featured." sqref="K2:K1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Featured" error="&quot;yes&quot; to show it on the homepage and mark it as featured." sqref="K2:K1000" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="L2:L1000">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="L2:L1000" xr:uid="{00000000-0002-0000-0800-000001000000}">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -1,274 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10927"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF030A50-F2B1-D043-8768-A077CF386B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19680" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="Settings" sheetId="2" r:id="rId2"/>
-    <sheet name="PI" sheetId="3" r:id="rId3"/>
-    <sheet name="PI Details" sheetId="4" r:id="rId4"/>
-    <sheet name="Sites" sheetId="5" r:id="rId5"/>
-    <sheet name="Members" sheetId="6" r:id="rId6"/>
-    <sheet name="Alumni" sheetId="7" r:id="rId7"/>
-    <sheet name="News" sheetId="8" r:id="rId8"/>
-    <sheet name="Publications" sheetId="9" r:id="rId9"/>
-    <sheet name="Patents" sheetId="10" r:id="rId10"/>
+    <sheet sheetId="1" name="README" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Settings" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="PI" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="PI Details" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Sites" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Members" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Alumni" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="News" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Publications" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Patents" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Group heading, e.g. "Appointments", "Education", "Honors", "Links". Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The text of the bullet. Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Optional web address. If filled in, the item becomes a link.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Set to "no" to hide this row on the website without deleting it.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Short code used in the Site column of the Members and Alumni tabs, e.g. "JHU". Required.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Label shown on badges. Defaults to the code.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Optional badge colour as a hex code, e.g. #2B5CB8.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>"yes" for an active site, "no" for a past one.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>A code from the Sites tab. Required.</t>
+          <t>Application or publication number.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000003000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>e.g. PhD Student, Postdoctoral Fellow, Senior Scientist. Required.</t>
+          <t>e.g. USPTO, EPO, WIPO.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000004000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>One or two sentences on what this person works on. Leave blank to omit.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>File name of a photo in public/images/people, or a full web address. Leave blank to show initials.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Personal page, Google Scholar, ORCID, etc.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -278,105 +65,35 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Required.</t>
+          <t>Group heading, e.g. "Appointments", "Education", "Honors", "Links". Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>e.g. "2019–2022" or "2021".</t>
+          <t>The text of the bullet. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>A code from the Sites tab. Several sites can be joined with "/", e.g. "L/MDC".</t>
+          <t>Optional web address. If filled in, the item becomes a link.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Position in the lab, e.g. PhD, Postdoc, MSc.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Current position. Leave blank if unknown.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Optional thesis title. The column only appears on the site if at least one alumnus has one.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -386,78 +103,43 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Date of the news item, e.g. 2026-06-02. Required.</t>
+          <t>Short code used in the Site column of the Members and Alumni tabs, e.g. "JHU". Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000002000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>e.g. Lab, Paper, Award, Press.</t>
+          <t>Label shown on badges. Defaults to the code.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000003000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000004000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Optional "Read more" link. Can be a web address or a page on this site like /publications.</t>
+          <t>Optional badge colour as a hex code, e.g. #2B5CB8.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000005000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Set to "no" to hide this row on the website without deleting it.</t>
+          <t>"yes" for an active site, "no" for a past one.</t>
         </r>
       </text>
     </comment>
@@ -466,105 +148,56 @@
 </file>
 
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000002000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Required.</t>
+          <t>A code from the Sites tab. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000003000000}">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Author list as it should appear, e.g. "Beagrie, R. A., Pombo, A.".</t>
+          <t>e.g. PhD Student, Postdoctoral Fellow, Senior Scientist. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000004000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>e.g. "21(7), 735–775".</t>
+          <t>One or two sentences on what this person works on. Leave blank to omit.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000005000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>e.g. 10.1038/s41586-021-04081-2 or the full https://doi.org/… address.</t>
+          <t>File name of a photo in public/images/people, or a full web address. Leave blank to show initials.</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000006000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>"yes" to show it on the homepage and mark it as featured.</t>
+          <t>Personal page, Google Scholar, ORCID, etc.</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000007000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -574,77 +207,160 @@
 </file>
 
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000002000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+          <t>e.g. "2019–2022" or "2021".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>A code from the Sites tab. Several sites can be joined with "/", e.g. "L/MDC".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>Position in the lab, e.g. PhD, Postdoc, MSc.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>Current position. Leave blank if unknown.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>Optional thesis title. The column only appears on the site if at least one alumnus has one.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <t>Set to "no" to hide this row on the website without deleting it.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <t>Date of the news item, e.g. 2026-06-02. Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>e.g. Lab, Paper, Award, Press.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
           <t>Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000003000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Application or publication number.</t>
+          <t>Optional "Read more" link. Can be a web address or a page on this site like /publications.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>e.g. USPTO, EPO, WIPO.</t>
+          <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000005000000}">
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
       <text>
         <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
+          <t>Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <t>Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <t>Author list as it should appear, e.g. "Beagrie, R. A., Pombo, A.".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <t>e.g. "21(7), 735–775".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <t>e.g. 10.1038/s41586-021-04081-2 or the full https://doi.org/… address.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <t>"yes" to show it on the homepage and mark it as featured.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
           <t>Set to "no" to hide this row on the website without deleting it.</t>
         </r>
       </text>
@@ -654,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="796">
   <si>
     <t>Lab website content</t>
   </si>
@@ -857,21 +573,10 @@
     <t>Main lab contact address.</t>
   </si>
   <si>
-    <t>Bold author names</t>
-  </si>
-  <si>
-    <t>Pombo, A.
-A. Pombo
-Pombo A</t>
-  </si>
-  <si>
-    <t>Author names to show in bold in publication lists. One per line, exactly as written in the Authors column (e.g. "Pombo, A.").</t>
-  </si>
-  <si>
     <t>Lab description</t>
   </si>
   <si>
-    <t>We study mechanisms of gene expression at multiple levels, from the local action of transcription factors, to long-range chromatin looping events that connect regulatory DNA sequences with the genes they regulate, to how whole chromosomes are positioned within cell nuclei. Binding of transcription factors at regulatory sequences helps recruit chromatin remodelers and the transcription machinery to transcription sites.
+    <t xml:space="preserve">We study mechanisms of gene expression at multiple levels, from the local action of transcription factors, to long-range chromatin looping events that connect regulatory DNA sequences with the genes they regulate, to how whole chromosomes are positioned within cell nuclei. Binding of transcription factors at regulatory sequences helps recruit chromatin remodelers and the transcription machinery to transcription sites.
 Upon recruitment, RNA polymerases either remain primed for subsequent activation (e.g. after environmental stress, during differentiation or disease), or directly transcribe the DNA template into RNA molecules, which code for proteins or for structural RNAs that constitute many enzymatic complexes.
 An increasingly important aspect of gene regulation is the three-dimensional folding of the genome, and the mechanisms that control physical contacts of distant regulatory DNA sequences with gene promoters to activate gene expression. To directly measure genome topologies, our group developed Genome Architecture Mapping (GAM).
 Our long-term strategy for unravelling the principles of genome function in higher eukaryotes aims to integrate multiple parameters, which is becoming increasingly possible with state-of-the-art developments in single cell genomics, molecular biology, epigenetics, nuclear imaging, and genetics.</t>
@@ -883,7 +588,7 @@
     <t>Research description</t>
   </si>
   <si>
-    <t>Our main goal is to unravel the diverse mechanisms of mammalian gene regulation and their roles in development and disease. Gene activation is controlled locally through transcription factors, chromatin modifiers, and the transcription and RNA processing machineries. Gene expression is also intricately regulated by the three-dimensional (3D) structure of the genome, which modifies the location of genes relative to activating or repressing biochemical environments. Repressing nuclear locations include the nuclear lamina and heterochromatin. Activating 3D genome conformations can work by regulating the physical proximity between regulatory regions and their responsive genes. As many disease-associated genetic variants fall in non-coding regulatory elements scattered in the genome, our work aims to advance the functional interpretation of the linear genome sequence. We especially put effort in devising experimental and computational approaches to map 3D genome structure in different cell types, in development and in disease, to study developmental and disease mechanisms, towards novel diagnostics, prognostics and therapeutics.
+    <t xml:space="preserve">Our main goal is to unravel the diverse mechanisms of mammalian gene regulation and their roles in development and disease. Gene activation is controlled locally through transcription factors, chromatin modifiers, and the transcription and RNA processing machineries. Gene expression is also intricately regulated by the three-dimensional (3D) structure of the genome, which modifies the location of genes relative to activating or repressing biochemical environments. Repressing nuclear locations include the nuclear lamina and heterochromatin. Activating 3D genome conformations can work by regulating the physical proximity between regulatory regions and their responsive genes. As many disease-associated genetic variants fall in non-coding regulatory elements scattered in the genome, our work aims to advance the functional interpretation of the linear genome sequence. We especially put effort in devising experimental and computational approaches to map 3D genome structure in different cell types, in development and in disease, to study developmental and disease mechanisms, towards novel diagnostics, prognostics and therapeutics.
 We have developed Genome Architecture Mapping (GAM), an orthogonal 3D genome folding mapping technology which yields fine maps of chromatin contacts from small cell numbers (500−1000), and is uniquely powerful to quantify different metrics of 3D genome structure, such as multiway contacts and chromatin melting. With immuno-GAM, we introduced the selection of cell types within complex tissues to enable the application of GAM in rare cells, such as dopaminergic neurons in the midbrain. GAM is an inherently suited platform for multimodal molecular phenotyping of biological samples, from genome sequence and 3D structure, to transcript and protein quantification. As a first step towards GAM multimodality, we have developed Oligo-Seq, a novel approach to detect minute amounts of specific RNA sequences within thin tissue cryosections, as used for GAM. We currently develop the application of Oligo-seq in spatial transcriptomics, especially in archival clinical samples (e.g. FFPE). By further developing multimodal integration of 3D genome topology, with the abundance of specific regulatory factors and gene expression, at the single-cell level, we aim to extract dynamic states of gene regulation and cause-effect relationships that connect 3D genome structure with gene expression. Ultimately, we seek to advance the interpretability of the linear genome sequence, to gain a deeper understanding of 3D genome regulation mechanisms in gene expression, and to advance their predictability.</t>
   </si>
   <si>
@@ -920,7 +625,7 @@
     <t>Publications introduction</t>
   </si>
   <si>
-    <t>Selected papers, newest first. Group authors are shown in bold.</t>
+    <t>Selected papers, newest first.</t>
   </si>
   <si>
     <t>Text at the top of the Publications page.</t>
@@ -1136,7 +841,7 @@
     <t>Max Delbrück Center</t>
   </si>
   <si>
-    <t>Berlin Institute for Medical Systems Biology (BIMSB)
+    <t xml:space="preserve">Berlin Institute for Medical Systems Biology (BIMSB)
 Hannoversche Straße 28, 10115 Berlin</t>
   </si>
   <si>
@@ -1233,6 +938,15 @@
     <t>apark55@jhmi.edu</t>
   </si>
   <si>
+    <t>Brady Bock</t>
+  </si>
+  <si>
+    <t>Undergraduate</t>
+  </si>
+  <si>
+    <t>bbock4@jh.edu</t>
+  </si>
+  <si>
     <t>Li Wang</t>
   </si>
   <si>
@@ -3049,71 +2763,41 @@
   </si>
   <si>
     <t>Granted</t>
-  </si>
-  <si>
-    <t>Brady Bock</t>
-  </si>
-  <si>
-    <t>Undergraduate</t>
-  </si>
-  <si>
-    <t>bbock4@jh.edu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="11"/>
       <color rgb="FF666666"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -3143,11 +2827,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3174,12 +2857,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3516,33 +3195,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF003366"/>
   </sheetPr>
   <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="3"/>
+    </row>
+    <row r="5" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -3550,7 +3232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -3558,7 +3240,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -3566,7 +3248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -3574,7 +3256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -3582,12 +3264,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
@@ -3595,7 +3278,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -3603,7 +3286,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
@@ -3611,7 +3294,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -3619,7 +3302,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -3627,7 +3310,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
@@ -3635,12 +3318,13 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="3"/>
+    </row>
+    <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -3648,7 +3332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
@@ -3656,7 +3340,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>31</v>
       </c>
@@ -3664,7 +3348,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
@@ -3672,7 +3356,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>35</v>
       </c>
@@ -3680,7 +3364,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>37</v>
       </c>
@@ -3688,7 +3372,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>39</v>
       </c>
@@ -3696,7 +3380,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>41</v>
       </c>
@@ -3704,7 +3388,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:2" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>43</v>
       </c>
@@ -3714,14 +3398,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -3732,12 +3416,12 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>422</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>786</v>
@@ -3752,13 +3436,13 @@
         <v>789</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2026</v>
       </c>
@@ -3777,11 +3461,12 @@
       <c r="F2" s="2" t="s">
         <v>794</v>
       </c>
+      <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2025</v>
       </c>
@@ -3800,37 +3485,38 @@
       <c r="F3" s="2" t="s">
         <v>794</v>
       </c>
+      <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
+  <autoFilter ref="A1:H1"/>
   <dataValidations count="2">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Status" error="Choose a value from the list." sqref="E2:E1000" xr:uid="{00000000-0002-0000-0900-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Status" error="Choose a value from the list." sqref="E2:E1000">
       <formula1>"Filed,Published,Granted"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="H2:H1000" xr:uid="{00000000-0002-0000-0900-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="H2:H1000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>45</v>
       </c>
@@ -3841,7 +3527,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>48</v>
       </c>
@@ -3852,7 +3538,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>51</v>
       </c>
@@ -3863,7 +3549,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>54</v>
       </c>
@@ -3874,7 +3560,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>57</v>
       </c>
@@ -3885,7 +3571,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>60</v>
       </c>
@@ -3896,7 +3582,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>62</v>
       </c>
@@ -3907,7 +3593,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>64</v>
       </c>
@@ -3918,7 +3604,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>67</v>
       </c>
@@ -3929,7 +3615,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="2" customFormat="1" ht="224" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>70</v>
       </c>
@@ -3940,7 +3626,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="2" customFormat="1" ht="395" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>73</v>
       </c>
@@ -3951,7 +3637,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>76</v>
       </c>
@@ -3962,7 +3648,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>79</v>
       </c>
@@ -3973,7 +3659,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>82</v>
       </c>
@@ -3984,7 +3670,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>85</v>
       </c>
@@ -3995,34 +3681,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>45</v>
       </c>
@@ -4033,423 +3708,446 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="1:3" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="C7" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" s="2" customFormat="1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="B2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>65</v>
       </c>
+      <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>101</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B19" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="C23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:D1"/>
   <dataValidations count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="D2:D1000" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="D2:D1000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4460,109 +4158,111 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="B2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:G1"/>
   <dataValidations count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Current site" error="&quot;yes&quot; for an active site, &quot;no&quot; for a past one." sqref="G2:G1000" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Current site" error="&quot;yes&quot; for an active site, &quot;no&quot; for a past one." sqref="G2:G1000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -4573,210 +4273,231 @@
     <col min="8" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="I1" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="B2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="2" customFormat="1" ht="96" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="64" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" ht="112" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>798</v>
-      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>190</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>180</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
         <v>191</v>
       </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>192</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
         <v>194</v>
       </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>196</v>
@@ -4784,39 +4505,45 @@
       <c r="D10" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
         <v>197</v>
       </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>198</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
         <v>199</v>
       </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>200</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>201</v>
@@ -4824,82 +4551,93 @@
       <c r="D12" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>202</v>
       </c>
+      <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
         <v>203</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>204</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>205</v>
       </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>206</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>207</v>
       </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>208</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
         <v>209</v>
       </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" ht="80" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>211</v>
@@ -4913,19 +4651,20 @@
       <c r="F16" s="2" t="s">
         <v>213</v>
       </c>
+      <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
         <v>214</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>215</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>216</v>
@@ -4933,33 +4672,41 @@
       <c r="D17" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>218</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>219</v>
@@ -4967,19 +4714,22 @@
       <c r="D19" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
         <v>220</v>
       </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>221</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>219</v>
@@ -4987,19 +4737,22 @@
       <c r="D20" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
         <v>222</v>
       </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>224</v>
@@ -5007,19 +4760,22 @@
       <c r="D21" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
         <v>225</v>
       </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>226</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>227</v>
@@ -5027,45 +4783,36 @@
       <c r="D22" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
         <v>228</v>
       </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
-  <dataValidations count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="I2:I1001" xr:uid="{00000000-0002-0000-0500-000001000000}">
+  <autoFilter ref="A1:I1"/>
+  <dataValidations count="2">
+    <dataValidation type="list" showErrorMessage="1" errorStyle="warning" errorTitle="Site" error="A code from the Sites tab." sqref="B2:B1000">
+      <formula1>Sites!$A$2:$A$50</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="I2:I1000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="F7" r:id="rId1" xr:uid="{72576DDF-177A-9843-88DF-1B21D72EA54A}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" errorStyle="warning" showErrorMessage="1" errorTitle="Site" error="A code from the Sites tab." xr:uid="{00000000-0002-0000-0500-000000000000}">
-          <x14:formula1>
-            <xm:f>Sites!$A$2:$A$50</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B1001</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -5074,18 +4821,18 @@
     <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>229</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>230</v>
@@ -5094,10 +4841,10 @@
         <v>231</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>232</v>
       </c>
@@ -5105,16 +4852,18 @@
         <v>233</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>234</v>
       </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>235</v>
       </c>
@@ -5122,7 +4871,7 @@
         <v>236</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>237</v>
@@ -5130,11 +4879,12 @@
       <c r="E3" s="2" t="s">
         <v>238</v>
       </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>239</v>
       </c>
@@ -5142,7 +4892,7 @@
         <v>236</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>237</v>
@@ -5150,11 +4900,12 @@
       <c r="E4" s="2" t="s">
         <v>240</v>
       </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>241</v>
       </c>
@@ -5162,7 +4913,7 @@
         <v>236</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>242</v>
@@ -5170,11 +4921,12 @@
       <c r="E5" s="2" t="s">
         <v>243</v>
       </c>
+      <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>244</v>
       </c>
@@ -5182,7 +4934,7 @@
         <v>245</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>246</v>
@@ -5190,11 +4942,12 @@
       <c r="E6" s="2" t="s">
         <v>247</v>
       </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>248</v>
       </c>
@@ -5202,7 +4955,7 @@
         <v>249</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>237</v>
@@ -5210,11 +4963,12 @@
       <c r="E7" s="2" t="s">
         <v>250</v>
       </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>251</v>
       </c>
@@ -5222,7 +4976,7 @@
         <v>249</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>242</v>
@@ -5230,11 +4984,12 @@
       <c r="E8" s="2" t="s">
         <v>252</v>
       </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>253</v>
       </c>
@@ -5242,16 +4997,18 @@
         <v>249</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>234</v>
       </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>254</v>
       </c>
@@ -5259,7 +5016,7 @@
         <v>255</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>237</v>
@@ -5267,11 +5024,12 @@
       <c r="E10" s="2" t="s">
         <v>256</v>
       </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>257</v>
       </c>
@@ -5279,7 +5037,7 @@
         <v>258</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>237</v>
@@ -5287,11 +5045,12 @@
       <c r="E11" s="2" t="s">
         <v>259</v>
       </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>260</v>
       </c>
@@ -5299,7 +5058,7 @@
         <v>261</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>262</v>
@@ -5307,11 +5066,12 @@
       <c r="E12" s="2" t="s">
         <v>263</v>
       </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>264</v>
       </c>
@@ -5319,7 +5079,7 @@
         <v>265</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>242</v>
@@ -5327,11 +5087,12 @@
       <c r="E13" s="2" t="s">
         <v>266</v>
       </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>267</v>
       </c>
@@ -5339,7 +5100,7 @@
         <v>268</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>262</v>
@@ -5347,11 +5108,12 @@
       <c r="E14" s="2" t="s">
         <v>269</v>
       </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>270</v>
       </c>
@@ -5359,7 +5121,7 @@
         <v>268</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>262</v>
@@ -5367,11 +5129,12 @@
       <c r="E15" s="2" t="s">
         <v>271</v>
       </c>
+      <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>272</v>
       </c>
@@ -5379,7 +5142,7 @@
         <v>273</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>242</v>
@@ -5387,11 +5150,12 @@
       <c r="E16" s="2" t="s">
         <v>274</v>
       </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>275</v>
       </c>
@@ -5399,7 +5163,7 @@
         <v>273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>242</v>
@@ -5407,11 +5171,12 @@
       <c r="E17" s="2" t="s">
         <v>276</v>
       </c>
+      <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>277</v>
       </c>
@@ -5419,7 +5184,7 @@
         <v>278</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>237</v>
@@ -5427,11 +5192,12 @@
       <c r="E18" s="2" t="s">
         <v>279</v>
       </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>280</v>
       </c>
@@ -5447,11 +5213,12 @@
       <c r="E19" s="2" t="s">
         <v>283</v>
       </c>
+      <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>284</v>
       </c>
@@ -5459,7 +5226,7 @@
         <v>285</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>246</v>
@@ -5467,11 +5234,12 @@
       <c r="E20" s="2" t="s">
         <v>286</v>
       </c>
+      <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>287</v>
       </c>
@@ -5479,7 +5247,7 @@
         <v>285</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>237</v>
@@ -5487,11 +5255,12 @@
       <c r="E21" s="2" t="s">
         <v>288</v>
       </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>289</v>
       </c>
@@ -5499,7 +5268,7 @@
         <v>290</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>246</v>
@@ -5507,11 +5276,12 @@
       <c r="E22" s="2" t="s">
         <v>291</v>
       </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>292</v>
       </c>
@@ -5519,7 +5289,7 @@
         <v>293</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>242</v>
@@ -5527,11 +5297,12 @@
       <c r="E23" s="2" t="s">
         <v>294</v>
       </c>
+      <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>295</v>
       </c>
@@ -5539,16 +5310,18 @@
         <v>293</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>234</v>
       </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>296</v>
       </c>
@@ -5556,7 +5329,7 @@
         <v>297</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>237</v>
@@ -5564,11 +5337,12 @@
       <c r="E25" s="2" t="s">
         <v>298</v>
       </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>299</v>
       </c>
@@ -5584,11 +5358,12 @@
       <c r="E26" s="2" t="s">
         <v>301</v>
       </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>302</v>
       </c>
@@ -5604,11 +5379,12 @@
       <c r="E27" s="2" t="s">
         <v>304</v>
       </c>
+      <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>305</v>
       </c>
@@ -5616,7 +5392,7 @@
         <v>306</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>242</v>
@@ -5624,11 +5400,12 @@
       <c r="E28" s="2" t="s">
         <v>307</v>
       </c>
+      <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>308</v>
       </c>
@@ -5636,7 +5413,7 @@
         <v>306</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>242</v>
@@ -5644,11 +5421,12 @@
       <c r="E29" s="2" t="s">
         <v>309</v>
       </c>
+      <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>310</v>
       </c>
@@ -5656,7 +5434,7 @@
         <v>311</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>237</v>
@@ -5664,11 +5442,12 @@
       <c r="E30" s="2" t="s">
         <v>312</v>
       </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>313</v>
       </c>
@@ -5676,7 +5455,7 @@
         <v>311</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>237</v>
@@ -5684,11 +5463,12 @@
       <c r="E31" s="2" t="s">
         <v>314</v>
       </c>
+      <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>315</v>
       </c>
@@ -5704,11 +5484,12 @@
       <c r="E32" s="2" t="s">
         <v>317</v>
       </c>
+      <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>318</v>
       </c>
@@ -5716,7 +5497,7 @@
         <v>319</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>242</v>
@@ -5724,11 +5505,12 @@
       <c r="E33" s="2" t="s">
         <v>320</v>
       </c>
+      <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>321</v>
       </c>
@@ -5744,11 +5526,12 @@
       <c r="E34" s="2" t="s">
         <v>324</v>
       </c>
+      <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>325</v>
       </c>
@@ -5764,11 +5547,12 @@
       <c r="E35" s="2" t="s">
         <v>327</v>
       </c>
+      <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>328</v>
       </c>
@@ -5784,11 +5568,12 @@
       <c r="E36" s="2" t="s">
         <v>330</v>
       </c>
+      <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>331</v>
       </c>
@@ -5804,11 +5589,12 @@
       <c r="E37" s="2" t="s">
         <v>333</v>
       </c>
+      <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>334</v>
       </c>
@@ -5824,11 +5610,12 @@
       <c r="E38" s="2" t="s">
         <v>335</v>
       </c>
+      <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>336</v>
       </c>
@@ -5844,11 +5631,12 @@
       <c r="E39" s="2" t="s">
         <v>338</v>
       </c>
+      <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>339</v>
       </c>
@@ -5856,7 +5644,7 @@
         <v>340</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>237</v>
@@ -5864,11 +5652,12 @@
       <c r="E40" s="2" t="s">
         <v>341</v>
       </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>342</v>
       </c>
@@ -5876,7 +5665,7 @@
         <v>343</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>262</v>
@@ -5884,11 +5673,12 @@
       <c r="E41" s="2" t="s">
         <v>344</v>
       </c>
+      <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>345</v>
       </c>
@@ -5896,7 +5686,7 @@
         <v>346</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>323</v>
@@ -5904,11 +5694,12 @@
       <c r="E42" s="2" t="s">
         <v>347</v>
       </c>
+      <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>348</v>
       </c>
@@ -5916,7 +5707,7 @@
         <v>349</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>237</v>
@@ -5924,11 +5715,12 @@
       <c r="E43" s="2" t="s">
         <v>350</v>
       </c>
+      <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>351</v>
       </c>
@@ -5936,7 +5728,7 @@
         <v>352</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>242</v>
@@ -5944,11 +5736,12 @@
       <c r="E44" s="2" t="s">
         <v>353</v>
       </c>
+      <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>354</v>
       </c>
@@ -5956,7 +5749,7 @@
         <v>355</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>262</v>
@@ -5964,11 +5757,12 @@
       <c r="E45" s="2" t="s">
         <v>356</v>
       </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>357</v>
       </c>
@@ -5976,16 +5770,18 @@
         <v>358</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>359</v>
       </c>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>360</v>
       </c>
@@ -5993,16 +5789,18 @@
         <v>358</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>359</v>
       </c>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>361</v>
       </c>
@@ -6010,7 +5808,7 @@
         <v>362</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>323</v>
@@ -6018,11 +5816,12 @@
       <c r="E48" s="2" t="s">
         <v>363</v>
       </c>
+      <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>364</v>
       </c>
@@ -6030,16 +5829,18 @@
         <v>365</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>359</v>
       </c>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>366</v>
       </c>
@@ -6047,16 +5848,18 @@
         <v>367</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>359</v>
       </c>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>368</v>
       </c>
@@ -6064,16 +5867,18 @@
         <v>367</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>359</v>
       </c>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>369</v>
       </c>
@@ -6081,7 +5886,7 @@
         <v>370</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>237</v>
@@ -6089,11 +5894,12 @@
       <c r="E52" s="2" t="s">
         <v>371</v>
       </c>
+      <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>372</v>
       </c>
@@ -6101,7 +5907,7 @@
         <v>373</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>246</v>
@@ -6109,11 +5915,12 @@
       <c r="E53" s="2" t="s">
         <v>374</v>
       </c>
+      <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>375</v>
       </c>
@@ -6121,76 +5928,94 @@
         <v>376</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>359</v>
       </c>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>377</v>
       </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
         <v>246</v>
       </c>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>378</v>
       </c>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
         <v>246</v>
       </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>379</v>
       </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
         <v>237</v>
       </c>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>380</v>
       </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
         <v>237</v>
       </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <autoFilter ref="A1:G1"/>
   <dataValidations count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="G2:G1000" xr:uid="{00000000-0002-0000-0600-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="G2:G1000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" style="7" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6199,7 +6024,7 @@
     <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>381</v>
       </c>
@@ -6207,19 +6032,19 @@
         <v>382</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>383</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>46212</v>
       </c>
@@ -6236,10 +6061,10 @@
         <v>387</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>46175</v>
       </c>
@@ -6252,11 +6077,12 @@
       <c r="D3" s="2" t="s">
         <v>390</v>
       </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <v>45938</v>
       </c>
@@ -6273,10 +6099,10 @@
         <v>394</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>45799</v>
       </c>
@@ -6293,10 +6119,10 @@
         <v>398</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>45637</v>
       </c>
@@ -6313,10 +6139,10 @@
         <v>402</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>45333</v>
       </c>
@@ -6333,10 +6159,10 @@
         <v>405</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>45096</v>
       </c>
@@ -6353,10 +6179,10 @@
         <v>409</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>44980</v>
       </c>
@@ -6373,10 +6199,10 @@
         <v>412</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" ht="64" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>44517</v>
       </c>
@@ -6393,10 +6219,10 @@
         <v>415</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>44120</v>
       </c>
@@ -6413,10 +6239,10 @@
         <v>418</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>43766</v>
       </c>
@@ -6433,26 +6259,26 @@
         <v>421</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <autoFilter ref="A1:F1"/>
   <dataValidations count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="F2:F1000" xr:uid="{00000000-0002-0000-0700-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="F2:F1000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L99"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
@@ -6464,12 +6290,12 @@
     <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>422</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>423</v>
@@ -6487,7 +6313,7 @@
         <v>427</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>428</v>
@@ -6499,10 +6325,10 @@
         <v>430</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2026</v>
       </c>
@@ -6521,14 +6347,18 @@
       <c r="F2" s="2" t="s">
         <v>435</v>
       </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2026</v>
       </c>
@@ -6541,17 +6371,22 @@
       <c r="D3" s="2" t="s">
         <v>438</v>
       </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
         <v>439</v>
       </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2026</v>
       </c>
@@ -6564,17 +6399,22 @@
       <c r="D4" s="2" t="s">
         <v>442</v>
       </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
         <v>443</v>
       </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2026</v>
       </c>
@@ -6587,17 +6427,22 @@
       <c r="D5" s="2" t="s">
         <v>438</v>
       </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2025</v>
       </c>
@@ -6610,17 +6455,22 @@
       <c r="D6" s="2" t="s">
         <v>438</v>
       </c>
+      <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
         <v>449</v>
       </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2025</v>
       </c>
@@ -6639,14 +6489,18 @@
       <c r="F7" s="2" t="s">
         <v>454</v>
       </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>2025</v>
       </c>
@@ -6665,14 +6519,18 @@
       <c r="F8" s="2" t="s">
         <v>459</v>
       </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>2025</v>
       </c>
@@ -6685,17 +6543,22 @@
       <c r="D9" s="2" t="s">
         <v>462</v>
       </c>
+      <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
         <v>463</v>
       </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" ht="96" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2024</v>
       </c>
@@ -6711,17 +6574,21 @@
       <c r="E10" s="2" t="s">
         <v>467</v>
       </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
         <v>468</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>2024</v>
       </c>
@@ -6737,14 +6604,19 @@
       <c r="E11" s="2" t="s">
         <v>472</v>
       </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" s="2" customFormat="1" ht="64" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>2024</v>
       </c>
@@ -6757,17 +6629,22 @@
       <c r="D12" s="2" t="s">
         <v>438</v>
       </c>
+      <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
         <v>475</v>
       </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>2024</v>
       </c>
@@ -6780,17 +6657,22 @@
       <c r="D13" s="2" t="s">
         <v>478</v>
       </c>
+      <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
         <v>479</v>
       </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>2024</v>
       </c>
@@ -6803,17 +6685,22 @@
       <c r="D14" s="2" t="s">
         <v>482</v>
       </c>
+      <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
         <v>483</v>
       </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>2023</v>
       </c>
@@ -6829,14 +6716,19 @@
       <c r="E15" s="2" t="s">
         <v>487</v>
       </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>2023</v>
       </c>
@@ -6855,14 +6747,18 @@
       <c r="F16" s="2" t="s">
         <v>491</v>
       </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>2023</v>
       </c>
@@ -6878,14 +6774,19 @@
       <c r="E17" s="2" t="s">
         <v>495</v>
       </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2022</v>
       </c>
@@ -6901,14 +6802,19 @@
       <c r="E18" s="2" t="s">
         <v>499</v>
       </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>2022</v>
       </c>
@@ -6924,14 +6830,19 @@
       <c r="E19" s="2" t="s">
         <v>503</v>
       </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>2022</v>
       </c>
@@ -6947,14 +6858,19 @@
       <c r="E20" s="2" t="s">
         <v>507</v>
       </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>2021</v>
       </c>
@@ -6970,14 +6886,19 @@
       <c r="E21" s="2" t="s">
         <v>511</v>
       </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>2021</v>
       </c>
@@ -6996,14 +6917,18 @@
       <c r="F22" s="2" t="s">
         <v>515</v>
       </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>2021</v>
       </c>
@@ -7019,14 +6944,19 @@
       <c r="E23" s="2" t="s">
         <v>518</v>
       </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>2021</v>
       </c>
@@ -7042,14 +6972,19 @@
       <c r="E24" s="2" t="s">
         <v>522</v>
       </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>2020</v>
       </c>
@@ -7065,14 +7000,19 @@
       <c r="E25" s="2" t="s">
         <v>525</v>
       </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>2020</v>
       </c>
@@ -7088,14 +7028,19 @@
       <c r="E26" s="2" t="s">
         <v>529</v>
       </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>2020</v>
       </c>
@@ -7111,14 +7056,19 @@
       <c r="E27" s="2" t="s">
         <v>533</v>
       </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2020</v>
       </c>
@@ -7134,14 +7084,19 @@
       <c r="E28" s="2" t="s">
         <v>537</v>
       </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2019</v>
       </c>
@@ -7157,14 +7112,19 @@
       <c r="E29" s="2" t="s">
         <v>541</v>
       </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2019</v>
       </c>
@@ -7180,14 +7140,19 @@
       <c r="E30" s="2" t="s">
         <v>544</v>
       </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2018</v>
       </c>
@@ -7203,14 +7168,19 @@
       <c r="E31" s="2" t="s">
         <v>548</v>
       </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>2018</v>
       </c>
@@ -7226,14 +7196,19 @@
       <c r="E32" s="2" t="s">
         <v>551</v>
       </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>2017</v>
       </c>
@@ -7249,14 +7224,19 @@
       <c r="E33" s="2" t="s">
         <v>554</v>
       </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>2017</v>
       </c>
@@ -7272,14 +7252,19 @@
       <c r="E34" s="2" t="s">
         <v>558</v>
       </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>2017</v>
       </c>
@@ -7295,14 +7280,19 @@
       <c r="E35" s="2" t="s">
         <v>561</v>
       </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>2017</v>
       </c>
@@ -7318,14 +7308,19 @@
       <c r="E36" s="2" t="s">
         <v>564</v>
       </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>2017</v>
       </c>
@@ -7341,14 +7336,19 @@
       <c r="E37" s="2" t="s">
         <v>568</v>
       </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>2017</v>
       </c>
@@ -7364,14 +7364,19 @@
       <c r="E38" s="2" t="s">
         <v>572</v>
       </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>2017</v>
       </c>
@@ -7387,14 +7392,19 @@
       <c r="E39" s="2" t="s">
         <v>576</v>
       </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>2017</v>
       </c>
@@ -7410,14 +7420,19 @@
       <c r="E40" s="2" t="s">
         <v>579</v>
       </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2017</v>
       </c>
@@ -7433,14 +7448,19 @@
       <c r="E41" s="2" t="s">
         <v>582</v>
       </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>2016</v>
       </c>
@@ -7456,14 +7476,19 @@
       <c r="E42" s="2" t="s">
         <v>585</v>
       </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>2016</v>
       </c>
@@ -7479,14 +7504,19 @@
       <c r="E43" s="2" t="s">
         <v>588</v>
       </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>2016</v>
       </c>
@@ -7502,14 +7532,19 @@
       <c r="E44" s="2" t="s">
         <v>591</v>
       </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>2016</v>
       </c>
@@ -7525,14 +7560,19 @@
       <c r="E45" s="2" t="s">
         <v>595</v>
       </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>2015</v>
       </c>
@@ -7548,14 +7588,19 @@
       <c r="E46" s="2" t="s">
         <v>599</v>
       </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>2015</v>
       </c>
@@ -7571,14 +7616,19 @@
       <c r="E47" s="2" t="s">
         <v>602</v>
       </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>2015</v>
       </c>
@@ -7594,14 +7644,19 @@
       <c r="E48" s="2" t="s">
         <v>606</v>
       </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>2015</v>
       </c>
@@ -7617,14 +7672,19 @@
       <c r="E49" s="2" t="s">
         <v>610</v>
       </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>2015</v>
       </c>
@@ -7640,14 +7700,19 @@
       <c r="E50" s="2" t="s">
         <v>613</v>
       </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>2014</v>
       </c>
@@ -7663,14 +7728,19 @@
       <c r="E51" s="2" t="s">
         <v>616</v>
       </c>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>2014</v>
       </c>
@@ -7686,14 +7756,19 @@
       <c r="E52" s="2" t="s">
         <v>619</v>
       </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>2014</v>
       </c>
@@ -7709,14 +7784,19 @@
       <c r="E53" s="2" t="s">
         <v>623</v>
       </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>2014</v>
       </c>
@@ -7732,14 +7812,19 @@
       <c r="E54" s="2" t="s">
         <v>627</v>
       </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>2013</v>
       </c>
@@ -7755,14 +7840,19 @@
       <c r="E55" s="2" t="s">
         <v>631</v>
       </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>2013</v>
       </c>
@@ -7778,14 +7868,19 @@
       <c r="E56" s="2" t="s">
         <v>635</v>
       </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>2013</v>
       </c>
@@ -7801,14 +7896,19 @@
       <c r="E57" s="2" t="s">
         <v>639</v>
       </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>2013</v>
       </c>
@@ -7824,14 +7924,19 @@
       <c r="E58" s="2" t="s">
         <v>643</v>
       </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>2012</v>
       </c>
@@ -7847,14 +7952,19 @@
       <c r="E59" s="2" t="s">
         <v>647</v>
       </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>2012</v>
       </c>
@@ -7870,14 +7980,19 @@
       <c r="E60" s="2" t="s">
         <v>649</v>
       </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>2012</v>
       </c>
@@ -7893,14 +8008,19 @@
       <c r="E61" s="2" t="s">
         <v>653</v>
       </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>2012</v>
       </c>
@@ -7916,14 +8036,19 @@
       <c r="E62" s="2" t="s">
         <v>657</v>
       </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>2012</v>
       </c>
@@ -7939,14 +8064,19 @@
       <c r="E63" s="2" t="s">
         <v>660</v>
       </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>2011</v>
       </c>
@@ -7962,14 +8092,19 @@
       <c r="E64" s="2" t="s">
         <v>664</v>
       </c>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>2011</v>
       </c>
@@ -7985,14 +8120,19 @@
       <c r="E65" s="2" t="s">
         <v>667</v>
       </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>2010</v>
       </c>
@@ -8008,14 +8148,19 @@
       <c r="E66" s="2" t="s">
         <v>671</v>
       </c>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>2010</v>
       </c>
@@ -8031,14 +8176,19 @@
       <c r="E67" s="2" t="s">
         <v>674</v>
       </c>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>2010</v>
       </c>
@@ -8054,14 +8204,19 @@
       <c r="E68" s="2" t="s">
         <v>678</v>
       </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>2010</v>
       </c>
@@ -8077,14 +8232,19 @@
       <c r="E69" s="2" t="s">
         <v>681</v>
       </c>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>2010</v>
       </c>
@@ -8100,14 +8260,19 @@
       <c r="E70" s="2" t="s">
         <v>684</v>
       </c>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>2010</v>
       </c>
@@ -8123,14 +8288,19 @@
       <c r="E71" s="2" t="s">
         <v>688</v>
       </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>2010</v>
       </c>
@@ -8146,14 +8316,19 @@
       <c r="E72" s="2" t="s">
         <v>692</v>
       </c>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>2010</v>
       </c>
@@ -8169,14 +8344,19 @@
       <c r="E73" s="2" t="s">
         <v>696</v>
       </c>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>2009</v>
       </c>
@@ -8192,14 +8372,19 @@
       <c r="E74" s="2" t="s">
         <v>700</v>
       </c>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>2009</v>
       </c>
@@ -8215,14 +8400,19 @@
       <c r="E75" s="2" t="s">
         <v>703</v>
       </c>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>2009</v>
       </c>
@@ -8238,14 +8428,19 @@
       <c r="E76" s="2" t="s">
         <v>706</v>
       </c>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>2009</v>
       </c>
@@ -8261,14 +8456,19 @@
       <c r="E77" s="2" t="s">
         <v>710</v>
       </c>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>2008</v>
       </c>
@@ -8284,14 +8484,19 @@
       <c r="E78" s="2" t="s">
         <v>713</v>
       </c>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>2008</v>
       </c>
@@ -8307,14 +8512,19 @@
       <c r="E79" s="2" t="s">
         <v>717</v>
       </c>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>2008</v>
       </c>
@@ -8330,14 +8540,19 @@
       <c r="E80" s="2" t="s">
         <v>720</v>
       </c>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>2007</v>
       </c>
@@ -8353,14 +8568,19 @@
       <c r="E81" s="2" t="s">
         <v>723</v>
       </c>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>2007</v>
       </c>
@@ -8376,14 +8596,19 @@
       <c r="E82" s="2" t="s">
         <v>726</v>
       </c>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>2007</v>
       </c>
@@ -8399,14 +8624,19 @@
       <c r="E83" s="2" t="s">
         <v>730</v>
       </c>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>2007</v>
       </c>
@@ -8422,14 +8652,19 @@
       <c r="E84" s="2" t="s">
         <v>734</v>
       </c>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>2007</v>
       </c>
@@ -8445,14 +8680,19 @@
       <c r="E85" s="2" t="s">
         <v>738</v>
       </c>
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>2006</v>
       </c>
@@ -8468,14 +8708,19 @@
       <c r="E86" s="2" t="s">
         <v>740</v>
       </c>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>2006</v>
       </c>
@@ -8491,14 +8736,19 @@
       <c r="E87" s="2" t="s">
         <v>743</v>
       </c>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>2006</v>
       </c>
@@ -8514,14 +8764,19 @@
       <c r="E88" s="2" t="s">
         <v>746</v>
       </c>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>2005</v>
       </c>
@@ -8537,14 +8792,19 @@
       <c r="E89" s="2" t="s">
         <v>749</v>
       </c>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>2005</v>
       </c>
@@ -8560,14 +8820,19 @@
       <c r="E90" s="2" t="s">
         <v>753</v>
       </c>
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>2004</v>
       </c>
@@ -8583,14 +8848,19 @@
       <c r="E91" s="2" t="s">
         <v>757</v>
       </c>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>2004</v>
       </c>
@@ -8606,14 +8876,19 @@
       <c r="E92" s="2" t="s">
         <v>761</v>
       </c>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>2004</v>
       </c>
@@ -8629,14 +8904,19 @@
       <c r="E93" s="2" t="s">
         <v>764</v>
       </c>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
       <c r="K93" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>2003</v>
       </c>
@@ -8652,14 +8932,19 @@
       <c r="E94" s="2" t="s">
         <v>768</v>
       </c>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>2003</v>
       </c>
@@ -8675,14 +8960,19 @@
       <c r="E95" s="2" t="s">
         <v>771</v>
       </c>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" s="2" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>2003</v>
       </c>
@@ -8698,14 +8988,19 @@
       <c r="E96" s="2" t="s">
         <v>775</v>
       </c>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>2003</v>
       </c>
@@ -8721,14 +9016,19 @@
       <c r="E97" s="2" t="s">
         <v>779</v>
       </c>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>2003</v>
       </c>
@@ -8744,14 +9044,19 @@
       <c r="E98" s="2" t="s">
         <v>782</v>
       </c>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>2003</v>
       </c>
@@ -8767,25 +9072,30 @@
       <c r="E99" s="2" t="s">
         <v>785</v>
       </c>
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="A1:L1"/>
   <dataValidations count="2">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Featured" error="&quot;yes&quot; to show it on the homepage and mark it as featured." sqref="K2:K1000" xr:uid="{00000000-0002-0000-0800-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Featured" error="&quot;yes&quot; to show it on the homepage and mark it as featured." sqref="K2:K1000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="L2:L1000" xr:uid="{00000000-0002-0000-0800-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Show" error="Set to &quot;no&quot; to hide this row on the website without deleting it." sqref="L2:L1000">
       <formula1>"yes,no"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1377" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1462" uniqueCount="881">
   <si>
     <t>Lab website content</t>
   </si>
@@ -1781,6 +1781,9 @@
     <t>13(4), bio060415</t>
   </si>
   <si>
+    <t>10.1242/bio.060415</t>
+  </si>
+  <si>
     <t>https://journals.biologists.com/bio/article/13/4/bio060415/347005/SRRM2-splicing-factor-modulates-cell-fate-in-early</t>
   </si>
   <si>
@@ -1796,6 +1799,9 @@
     <t>84(3), 415–428</t>
   </si>
   <si>
+    <t>10.1016/j.molcel.2023.12.032</t>
+  </si>
+  <si>
     <t>A single dose of cocaine rewires the 3D genome structure of midbrain dopamine neurons</t>
   </si>
   <si>
@@ -1841,6 +1847,9 @@
     <t>20, 993–994</t>
   </si>
   <si>
+    <t>10.1038/s41592-023-01905-z</t>
+  </si>
+  <si>
     <t>Multiplex-GAM: genome-wide identification of chromatin contacts yields insights overlooked by Hi-C</t>
   </si>
   <si>
@@ -1865,6 +1874,9 @@
     <t>32, 100443</t>
   </si>
   <si>
+    <t>10.1016/j.coisb.2022.100443</t>
+  </si>
+  <si>
     <t>A noncoding single-nucleotide polymorphism at 8q24 drives IDH1-mutant glioma formation</t>
   </si>
   <si>
@@ -1877,6 +1889,9 @@
     <t>378(6615), 68–78</t>
   </si>
   <si>
+    <t>10.1126/science.abj2890</t>
+  </si>
+  <si>
     <t>Single-cell-resolved dynamics of chromatin architecture delineate cell and regulatory states in zebrafish embryos</t>
   </si>
   <si>
@@ -1889,6 +1904,9 @@
     <t>2(1)</t>
   </si>
   <si>
+    <t>10.1016/j.xgen.2021.100083</t>
+  </si>
+  <si>
     <t>Altered nuclear architecture in blood cells from Huntington’s disease patients</t>
   </si>
   <si>
@@ -1901,6 +1919,9 @@
     <t>43(1), 379–385</t>
   </si>
   <si>
+    <t>10.1007/s10072-021-05289-w</t>
+  </si>
+  <si>
     <t>GAMIBHEAR: whole-genome haplotype reconstruction from Genome Architecture Mapping data</t>
   </si>
   <si>
@@ -1913,6 +1934,9 @@
     <t>37(19), 3128–3135</t>
   </si>
   <si>
+    <t>10.1093/bioinformatics/btab238</t>
+  </si>
+  <si>
     <t>Cell-type specialization is encoded by specific chromatin topologies</t>
   </si>
   <si>
@@ -1934,6 +1958,9 @@
     <t>18(5), 482–490</t>
   </si>
   <si>
+    <t>10.1038/s41592-021-01135-1</t>
+  </si>
+  <si>
     <t>The dynamics of chromatin architecture in brain development and function</t>
   </si>
   <si>
@@ -1946,6 +1973,9 @@
     <t>67, 84–93</t>
   </si>
   <si>
+    <t>10.1016/j.gde.2020.12.008</t>
+  </si>
+  <si>
     <t>LifeTime and improving European healthcare through cell-based interceptive medicine</t>
   </si>
   <si>
@@ -1955,6 +1985,9 @@
     <t>587(7834), 377–386</t>
   </si>
   <si>
+    <t>10.1038/s41586-020-2715-9</t>
+  </si>
+  <si>
     <t>Inference of chromosome 3D structures from GAM data by a physics computational approach</t>
   </si>
   <si>
@@ -1967,6 +2000,9 @@
     <t>181, 70–79</t>
   </si>
   <si>
+    <t>10.1016/j.ymeth.2019.09.018</t>
+  </si>
+  <si>
     <t>Evolving methodologies and concepts in 4D nucleome research</t>
   </si>
   <si>
@@ -1979,6 +2015,9 @@
     <t>64, 105–111</t>
   </si>
   <si>
+    <t>10.1016/j.ceb.2020.04.005</t>
+  </si>
+  <si>
     <t>Methods for mapping 3D chromosome architecture</t>
   </si>
   <si>
@@ -1991,6 +2030,9 @@
     <t>21(4), 207–226</t>
   </si>
   <si>
+    <t>10.1038/s41576-019-0195-2</t>
+  </si>
+  <si>
     <t>Editorial overview: Genome architecture and expression</t>
   </si>
   <si>
@@ -2003,6 +2045,9 @@
     <t>55, iii–iv</t>
   </si>
   <si>
+    <t>10.1016/j.gde.2019.09.001</t>
+  </si>
+  <si>
     <t>R-loops enhance polycomb repression at a subset of developmental regulator genes</t>
   </si>
   <si>
@@ -2012,6 +2057,9 @@
     <t>73(5), 930–945.e4</t>
   </si>
   <si>
+    <t>10.1016/j.molcel.2018.12.016</t>
+  </si>
+  <si>
     <t>Challenges and guidelines toward 4D nucleome data and model standards</t>
   </si>
   <si>
@@ -2024,6 +2072,9 @@
     <t>50(10), 1352–1358</t>
   </si>
   <si>
+    <t>10.1038/s41588-018-0236-3</t>
+  </si>
+  <si>
     <t>Polymer physics predicts the effects of structural variants on chromatin architecture</t>
   </si>
   <si>
@@ -2033,6 +2084,9 @@
     <t>50(5), 662–667</t>
   </si>
   <si>
+    <t>10.1038/s41588-018-0098-8</t>
+  </si>
+  <si>
     <t>RNA polymerase II primes Polycomb-repressed developmental genes throughout terminal neuronal differentiation</t>
   </si>
   <si>
@@ -2042,6 +2096,9 @@
     <t>13(10), MSB177754</t>
   </si>
   <si>
+    <t>10.15252/msb.20177754</t>
+  </si>
+  <si>
     <t>FANTOM5 CAGE profiles of human and mouse samples</t>
   </si>
   <si>
@@ -2054,6 +2111,9 @@
     <t>4(1), 170112</t>
   </si>
   <si>
+    <t>10.1038/sdata.2017.112</t>
+  </si>
+  <si>
     <t>Cell cycle: Continuous chromatin changes</t>
   </si>
   <si>
@@ -2063,6 +2123,9 @@
     <t>547(7661), 34</t>
   </si>
   <si>
+    <t>10.1038/547034a</t>
+  </si>
+  <si>
     <t>Flipping between Polycomb repressed and active transcriptional states introduces noise in gene expression</t>
   </si>
   <si>
@@ -2072,6 +2135,9 @@
     <t>8(1), 36</t>
   </si>
   <si>
+    <t>10.1038/s41467-017-00052-2</t>
+  </si>
+  <si>
     <t>Active and poised promoter states drive folding of the extended HoxB locus in mouse embryonic stem cells</t>
   </si>
   <si>
@@ -2084,6 +2150,9 @@
     <t>24(6), 515–524</t>
   </si>
   <si>
+    <t>10.1038/nsmb.3402</t>
+  </si>
+  <si>
     <t>Keep them close: PRC2 poises enhancer-promoter interactions at anterior neuronal genes</t>
   </si>
   <si>
@@ -2096,6 +2165,9 @@
     <t>20(5), 573–575</t>
   </si>
   <si>
+    <t>10.1016/j.stem.2017.04.006</t>
+  </si>
+  <si>
     <t>Maternal immune activation results in complex microglial transcriptome signature in the adult offspring that is reversed by minocycline treatment</t>
   </si>
   <si>
@@ -2108,6 +2180,9 @@
     <t>7(5), e1120</t>
   </si>
   <si>
+    <t>10.1038/tp.2017.80</t>
+  </si>
+  <si>
     <t>Complex multi-enhancer contacts captured by genome architecture mapping</t>
   </si>
   <si>
@@ -2117,6 +2192,9 @@
     <t>543(7646), 519–524</t>
   </si>
   <si>
+    <t>10.1038/nature21411</t>
+  </si>
+  <si>
     <t>A finer print than TADs: PRC1-mediated domains</t>
   </si>
   <si>
@@ -2126,6 +2204,9 @@
     <t>65(3), 373–375</t>
   </si>
   <si>
+    <t>10.1016/j.molcel.2017.01.028</t>
+  </si>
+  <si>
     <t>Examining topological domain influence on enhancer function</t>
   </si>
   <si>
@@ -2135,6 +2216,9 @@
     <t>39(5), 523–524</t>
   </si>
   <si>
+    <t>10.1016/j.devcel.2016.11.011</t>
+  </si>
+  <si>
     <t>Formation of new chromatin domains determines pathogenicity of genomic duplications</t>
   </si>
   <si>
@@ -2144,6 +2228,9 @@
     <t>538(7624), 265–269</t>
   </si>
   <si>
+    <t>10.1038/nature19800</t>
+  </si>
+  <si>
     <t>Gene activation by metazoan enhancers: diverse mechanisms stimulate distinct steps of transcription</t>
   </si>
   <si>
@@ -2153,6 +2240,9 @@
     <t>38(9), 881–893</t>
   </si>
   <si>
+    <t>10.1002/bies.201600032</t>
+  </si>
+  <si>
     <t>Mechanical regulation of transcription controls Polycomb-mediated gene silencing during lineage commitment</t>
   </si>
   <si>
@@ -2165,6 +2255,9 @@
     <t>18(8), 864–875</t>
   </si>
   <si>
+    <t>10.1038/ncb3387</t>
+  </si>
+  <si>
     <t>Methylation of RNA polymerase II non-consensus Lysine residues marks early transcription in mammalian cells</t>
   </si>
   <si>
@@ -2177,6 +2270,9 @@
     <t>4, e11215</t>
   </si>
   <si>
+    <t>10.7554/elife.11215</t>
+  </si>
+  <si>
     <t>Hierarchical folding and reorganization of chromosomes are linked to transcriptional changes in cellular differentiation</t>
   </si>
   <si>
@@ -2186,6 +2282,9 @@
     <t>11(12), MSB156492</t>
   </si>
   <si>
+    <t>10.15252/msb.20156492</t>
+  </si>
+  <si>
     <t>Polymer models of the organization of chromosomes in the nucleus of cells</t>
   </si>
   <si>
@@ -2198,6 +2297,9 @@
     <t>29(09), 1530003</t>
   </si>
   <si>
+    <t>10.1142/s0217984915300033</t>
+  </si>
+  <si>
     <t>Three-dimensional genome architecture: players and mechanisms</t>
   </si>
   <si>
@@ -2210,6 +2312,9 @@
     <t>16(4), 245–257</t>
   </si>
   <si>
+    <t>10.1038/nrm3965</t>
+  </si>
+  <si>
     <t>Transcribed enhancers lead waves of coordinated transcription in transitioning mammalian cells</t>
   </si>
   <si>
@@ -2219,6 +2324,9 @@
     <t>347(6225), 1010–1014</t>
   </si>
   <si>
+    <t>10.1126/science.1259418</t>
+  </si>
+  <si>
     <t>Stem cell epigenetics: looking forward</t>
   </si>
   <si>
@@ -2228,6 +2336,9 @@
     <t>14(6), 706–709</t>
   </si>
   <si>
+    <t>10.1016/j.stem.2014.05.011</t>
+  </si>
+  <si>
     <t>Models of chromosome structure</t>
   </si>
   <si>
@@ -2237,6 +2348,9 @@
     <t>28, 90–95</t>
   </si>
   <si>
+    <t>10.1016/j.ceb.2014.04.004</t>
+  </si>
+  <si>
     <t>Physical mechanisms behind the large scale features of chromatin organization</t>
   </si>
   <si>
@@ -2249,6 +2363,9 @@
     <t>5(2), e28447</t>
   </si>
   <si>
+    <t>10.4161/trns.28447</t>
+  </si>
+  <si>
     <t>An H3K9/S10 methyl-phospho switch modulates Polycomb and Pol II binding at repressed genes during differentiation</t>
   </si>
   <si>
@@ -2261,6 +2378,9 @@
     <t>25(6), 904–915</t>
   </si>
   <si>
+    <t>10.1091/mbc.e13-10-0628</t>
+  </si>
+  <si>
     <t>Polymer physics, scaling and heterogeneity in the spatial organisation of chromosomes in the cell nucleus</t>
   </si>
   <si>
@@ -2273,6 +2393,9 @@
     <t>9(36), 8631–8635</t>
   </si>
   <si>
+    <t>10.1039/c3sm51436f</t>
+  </si>
+  <si>
     <t>A polymer model explains the complexity of large-scale chromatin folding</t>
   </si>
   <si>
@@ -2285,6 +2408,9 @@
     <t>4(4), 267–273</t>
   </si>
   <si>
+    <t>10.4161/nucl.25432</t>
+  </si>
+  <si>
     <t>Polymer models of chromatin organization</t>
   </si>
   <si>
@@ -2297,6 +2423,9 @@
     <t>4, 113</t>
   </si>
   <si>
+    <t>10.3389/fgene.2013.00113</t>
+  </si>
+  <si>
     <t>A model of the large-scale organization of chromatin</t>
   </si>
   <si>
@@ -2309,6 +2438,9 @@
     <t>41(2), 508–512</t>
   </si>
   <si>
+    <t>10.1042/bst20120238</t>
+  </si>
+  <si>
     <t>Mean expression of the X-chromosome is associated with neuronal density</t>
   </si>
   <si>
@@ -2321,12 +2453,18 @@
     <t>6, 161</t>
   </si>
   <si>
+    <t>10.3389/fnins.2012.00161</t>
+  </si>
+  <si>
     <t>Complexity of chromatin folding is captured by the strings and binders switch model</t>
   </si>
   <si>
     <t>109(40), 16173–16178</t>
   </si>
   <si>
+    <t>10.1073/pnas.1204799109</t>
+  </si>
+  <si>
     <t>Proteomic analysis of mitotic RNA polymerase II reveals novel interactors and association with proteins dysfunctional in disease</t>
   </si>
   <si>
@@ -2339,6 +2477,9 @@
     <t>11(6)</t>
   </si>
   <si>
+    <t>10.1074/mcp.M111.011767</t>
+  </si>
+  <si>
     <t>Code breaking: the RNAPII modification code in pluripotency</t>
   </si>
   <si>
@@ -2351,6 +2492,9 @@
     <t>11(7), 1267–1268</t>
   </si>
   <si>
+    <t>10.4161/cc.19990</t>
+  </si>
+  <si>
     <t>Polycomb associates genome-wide with a specific RNA polymerase II variant, and regulates metabolic genes in ESCs</t>
   </si>
   <si>
@@ -2360,6 +2504,9 @@
     <t>10(2), 157–170</t>
   </si>
   <si>
+    <t>10.1016/j.stem.2011.12.017</t>
+  </si>
+  <si>
     <t>Polycomb targets seek closest neighbours</t>
   </si>
   <si>
@@ -2372,6 +2519,9 @@
     <t>7(3), e1002031</t>
   </si>
   <si>
+    <t>10.1371/journal.pgen.1002031</t>
+  </si>
+  <si>
     <t>Nuclear cell biology</t>
   </si>
   <si>
@@ -2381,6 +2531,9 @@
     <t>22(6), 722–722</t>
   </si>
   <si>
+    <t>10.1091/mbc.e10-12-0966</t>
+  </si>
+  <si>
     <t>Ring1B and Suv39h1 delineate distinct chromatin states at bivalent genes during early mouse lineage commitment</t>
   </si>
   <si>
@@ -2393,6 +2546,9 @@
     <t>137(15), 2483–2492</t>
   </si>
   <si>
+    <t>10.1242/dev.048363</t>
+  </si>
+  <si>
     <t>Short RNAs are transcribed from repressed polycomb target genes and interact with polycomb repressive complex-2</t>
   </si>
   <si>
@@ -2402,6 +2558,9 @@
     <t>38(5), 675–688</t>
   </si>
   <si>
+    <t>10.1016/j.molcel.2010.03.019</t>
+  </si>
+  <si>
     <t>Gene positioning</t>
   </si>
   <si>
@@ -2414,6 +2573,9 @@
     <t>2(6), a000588</t>
   </si>
   <si>
+    <t>10.1101/cshperspect.a000588</t>
+  </si>
+  <si>
     <t>Jarid2 is a PRC2 component in embryonic stem cells required for multi-lineage differentiation and recruitment of PRC1 and RNA Polymerase II to developmental regulators</t>
   </si>
   <si>
@@ -2423,6 +2585,9 @@
     <t>12(6), 618–624</t>
   </si>
   <si>
+    <t>10.1038/ncb2065</t>
+  </si>
+  <si>
     <t>Nucleus and gene expression: the structure and function conundrum</t>
   </si>
   <si>
@@ -2432,6 +2597,9 @@
     <t>22(3), 269–270</t>
   </si>
   <si>
+    <t>10.1016/j.ceb.2010.04.010</t>
+  </si>
+  <si>
     <t>Poised transcription factories prime silent uPA gene prior to activation</t>
   </si>
   <si>
@@ -2444,6 +2612,9 @@
     <t>8(1), e1000270</t>
   </si>
   <si>
+    <t>10.1371/journal.pbio.1000270</t>
+  </si>
+  <si>
     <t>Nuclear architecture in stem cells</t>
   </si>
   <si>
@@ -2456,6 +2627,9 @@
     <t>695, 14–25</t>
   </si>
   <si>
+    <t>10.1007/978-1-4419-7037-4_2</t>
+  </si>
+  <si>
     <t>Measurement of replication structures at the nanometer scale using super-resolution light microscopy</t>
   </si>
   <si>
@@ -2468,6 +2642,9 @@
     <t>38(2), e8</t>
   </si>
   <si>
+    <t>10.1093/nar/gkp901</t>
+  </si>
+  <si>
     <t>The molecular basis for stability of heterochromatin-mediated silencing in mammals</t>
   </si>
   <si>
@@ -2480,6 +2657,9 @@
     <t>2(1), 14</t>
   </si>
   <si>
+    <t>10.1186/1756-8935-2-14</t>
+  </si>
+  <si>
     <t>Modifications of RNA polymerase II are pivotal in regulating gene expression states</t>
   </si>
   <si>
@@ -2489,6 +2669,9 @@
     <t>10(11), 1213</t>
   </si>
   <si>
+    <t>10.1038/embor.2009.221</t>
+  </si>
+  <si>
     <t>3D chromatin regulation of Sonic hedgehog in the limb buds</t>
   </si>
   <si>
@@ -2498,6 +2681,9 @@
     <t>16(1), 9–11</t>
   </si>
   <si>
+    <t>10.1016/j.devcel.2008.12.010</t>
+  </si>
+  <si>
     <t>Mechanisms regulating S phase progression in mammalian cells</t>
   </si>
   <si>
@@ -2510,6 +2696,9 @@
     <t>14(11), 4199–4213</t>
   </si>
   <si>
+    <t>10.2741/3523</t>
+  </si>
+  <si>
     <t>Eukaryotic gene regulation in three dimensions and its impact on genome evolution</t>
   </si>
   <si>
@@ -2519,6 +2708,9 @@
     <t>18(6), 571–582</t>
   </si>
   <si>
+    <t>10.1016/j.gde.2008.10.002</t>
+  </si>
+  <si>
     <t>Changes in chromosome organization during PHA-activation of resting human lymphocytes measured by cryo-FISH</t>
   </si>
   <si>
@@ -2531,6 +2723,9 @@
     <t>16(3), 413–426</t>
   </si>
   <si>
+    <t>10.1007/s10577-008-1230-x</t>
+  </si>
+  <si>
     <t>Transcription and chromatin organization of a housekeeping gene cluster containing an integrated β-globin locus control region</t>
   </si>
   <si>
@@ -2540,6 +2735,9 @@
     <t>4(3), e1000016</t>
   </si>
   <si>
+    <t>10.1371/journal.pgen.1000016</t>
+  </si>
+  <si>
     <t>Ring1-mediated ubiquitination of H2A restrains poised RNA polymerase II at bivalent genes in mouse ES cells</t>
   </si>
   <si>
@@ -2549,6 +2747,9 @@
     <t>9(12), 1428–1435</t>
   </si>
   <si>
+    <t>10.1038/ncb1663</t>
+  </si>
+  <si>
     <t>Functional organisation of the genome during interphase</t>
   </si>
   <si>
@@ -2558,6 +2759,9 @@
     <t>17(5), 451–455</t>
   </si>
   <si>
+    <t>10.1016/j.gde.2007.08.008</t>
+  </si>
+  <si>
     <t>Advances in imaging the interphase nucleus using thin cryosections</t>
   </si>
   <si>
@@ -2570,6 +2774,9 @@
     <t>128(2), 97–104</t>
   </si>
   <si>
+    <t>10.1007/s00418-007-0310-x</t>
+  </si>
+  <si>
     <t>Desmin immunolocalisation in autosomal dominant Emery-Dreifuss muscular dystrophy</t>
   </si>
   <si>
@@ -2582,6 +2789,9 @@
     <t>17(4), 297–305</t>
   </si>
   <si>
+    <t>10.1016/j.nmd.2007.01.003</t>
+  </si>
+  <si>
     <t>Chromosome organization: new facts, new models</t>
   </si>
   <si>
@@ -2594,12 +2804,18 @@
     <t>17(3), 127–134</t>
   </si>
   <si>
+    <t>10.1016/j.tcb.2006.12.006</t>
+  </si>
+  <si>
     <t>Intermingling of chromosome territories in interphase suggests role in translocations and transcription-dependent associations</t>
   </si>
   <si>
     <t>4(5), e138</t>
   </si>
   <si>
+    <t>10.1371/journal.pbio.0040138</t>
+  </si>
+  <si>
     <t>Splicing speckles are not reservoirs of RNA polymerase II, but contain an inactive form, phosphorylated on Serine2 residues of the C-terminal domain</t>
   </si>
   <si>
@@ -2609,6 +2825,9 @@
     <t>17(4), 1723–1733</t>
   </si>
   <si>
+    <t>10.1091/mbc.e05-08-0726</t>
+  </si>
+  <si>
     <t>Distribution of different phosphorylated forms of RNA polymerase II in relation to Cajal and PML bodies in human cells: an ultrastructural study</t>
   </si>
   <si>
@@ -2618,6 +2837,9 @@
     <t>125(1), 21–31</t>
   </si>
   <si>
+    <t>10.1007/s00418-005-0064-2</t>
+  </si>
+  <si>
     <t>Variant histone H3.3 marks promoters of transcriptionally active genes during mammalian cell division</t>
   </si>
   <si>
@@ -2627,6 +2849,9 @@
     <t>6(4), 354</t>
   </si>
   <si>
+    <t>10.1038/sj.embor.7400366</t>
+  </si>
+  <si>
     <t>Functional analysis of Vif protein shows less restriction of human immunodeficiency virus type 2 by APOBEC3G</t>
   </si>
   <si>
@@ -2639,6 +2864,9 @@
     <t>79(2), 823–833</t>
   </si>
   <si>
+    <t>10.1128/jvi.79.2.823-833.2005</t>
+  </si>
+  <si>
     <t>CD8α is an activation marker for a subset of peripheral CD4 T cells</t>
   </si>
   <si>
@@ -2651,6 +2879,9 @@
     <t>34(5), 1262–1271</t>
   </si>
   <si>
+    <t>10.1002/eji.200324363</t>
+  </si>
+  <si>
     <t>Fixation-induced redistribution of hyperphosphorylated RNA polymerase II in the nucleus of human cells</t>
   </si>
   <si>
@@ -2663,6 +2894,9 @@
     <t>295(2), 460–468</t>
   </si>
   <si>
+    <t>10.1016/j.yexcr.2004.01.020</t>
+  </si>
+  <si>
     <t>Measuring the size of biological nanostructures with spatially modulated illumination microscopy</t>
   </si>
   <si>
@@ -2672,6 +2906,9 @@
     <t>15(5), 2449–2455</t>
   </si>
   <si>
+    <t>10.1091/mbc.e04-01-0045</t>
+  </si>
+  <si>
     <t>Interaction of proteins with promoter elements of the human U2 snRNA genes in vivo</t>
   </si>
   <si>
@@ -2684,6 +2921,9 @@
     <t>315, 103–112</t>
   </si>
   <si>
+    <t>10.1016/s0378-1119(03)00717-0</t>
+  </si>
+  <si>
     <t>Transcription factories: quantitative studies of nanostructures in the mammalian nucleus</t>
   </si>
   <si>
@@ -2693,6 +2933,9 @@
     <t>11(5), 461–470</t>
   </si>
   <si>
+    <t>10.1023/a:1024926710797</t>
+  </si>
+  <si>
     <t>Genome function and nuclear architecture: from gene expression to nanoscience</t>
   </si>
   <si>
@@ -2705,6 +2948,9 @@
     <t>13(6a), 1029–1041</t>
   </si>
   <si>
+    <t>10.1101/gr.946403</t>
+  </si>
+  <si>
     <t>From linear genome sequence to three-dimensional organization of the cell nucleus</t>
   </si>
   <si>
@@ -2717,6 +2963,9 @@
     <t>4(3), 310</t>
   </si>
   <si>
+    <t>10.1186/gb-2003-4-3-310</t>
+  </si>
+  <si>
     <t>Cellular genomics: which genes are transcribed, when and where?</t>
   </si>
   <si>
@@ -2726,6 +2975,9 @@
     <t>28(1), 6–9</t>
   </si>
   <si>
+    <t>10.1016/s0968-0004(02)00011-7</t>
+  </si>
+  <si>
     <t>Genomics meets nanoscience: probing genes and the cell nucleus at 10−9 meters</t>
   </si>
   <si>
@@ -2733,6 +2985,9 @@
   </si>
   <si>
     <t>3(3), reports4007.1</t>
+  </si>
+  <si>
+    <t>10.1186/gb-2002-3-3-reports4007</t>
   </si>
   <si>
     <t>Inventors</t>
@@ -3424,16 +3679,16 @@
         <v>90</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>786</v>
+        <v>871</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>787</v>
+        <v>872</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>788</v>
+        <v>873</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>789</v>
+        <v>874</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>105</v>
@@ -3447,19 +3702,19 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>790</v>
+        <v>875</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>791</v>
+        <v>876</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>792</v>
+        <v>877</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>793</v>
+        <v>878</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>794</v>
+        <v>879</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
@@ -3471,19 +3726,19 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>790</v>
+        <v>875</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>791</v>
+        <v>876</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>792</v>
+        <v>877</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>795</v>
+        <v>880</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>794</v>
+        <v>879</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
@@ -6574,12 +6829,14 @@
       <c r="E10" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>468</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>131</v>
@@ -6593,18 +6850,20 @@
         <v>2024</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F11" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>474</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -6621,17 +6880,17 @@
         <v>2024</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>438</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -6649,17 +6908,17 @@
         <v>2024</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -6677,17 +6936,17 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -6705,18 +6964,20 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F15" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>490</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -6733,19 +6994,19 @@
         <v>2023</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>486</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -6763,18 +7024,20 @@
         <v>2023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="F17" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>499</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -6791,18 +7054,20 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F18" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>504</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -6819,18 +7084,20 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F19" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>509</v>
+      </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -6847,18 +7114,20 @@
         <v>2022</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F20" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>514</v>
+      </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -6875,18 +7144,20 @@
         <v>2021</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F21" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>519</v>
+      </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -6903,19 +7174,19 @@
         <v>2021</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>433</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -6933,18 +7204,20 @@
         <v>2021</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="F23" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>527</v>
+      </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -6961,18 +7234,20 @@
         <v>2021</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="F24" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>532</v>
+      </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -6989,18 +7264,20 @@
         <v>2020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>433</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F25" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>536</v>
+      </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -7017,18 +7294,20 @@
         <v>2020</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F26" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>541</v>
+      </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -7045,18 +7324,20 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F27" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>546</v>
+      </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -7073,18 +7354,20 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="F28" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>551</v>
+      </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -7101,18 +7384,20 @@
         <v>2019</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F29" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>556</v>
+      </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -7129,18 +7414,20 @@
         <v>2019</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F30" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>560</v>
+      </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -7157,18 +7444,20 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="F31" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>565</v>
+      </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -7185,18 +7474,20 @@
         <v>2018</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="F32" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>569</v>
+      </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -7213,18 +7504,20 @@
         <v>2017</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>457</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="F33" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>573</v>
+      </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -7241,18 +7534,20 @@
         <v>2017</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="F34" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>578</v>
+      </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -7269,18 +7564,20 @@
         <v>2017</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>433</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="F35" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>582</v>
+      </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -7297,18 +7594,20 @@
         <v>2017</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="F36" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>586</v>
+      </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -7325,18 +7624,20 @@
         <v>2017</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>566</v>
+        <v>588</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>567</v>
+        <v>589</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F37" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>591</v>
+      </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -7353,18 +7654,20 @@
         <v>2017</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="F38" s="2"/>
+        <v>595</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>596</v>
+      </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -7381,18 +7684,20 @@
         <v>2017</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>573</v>
+        <v>597</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="F39" s="2"/>
+        <v>600</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>601</v>
+      </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -7409,18 +7714,20 @@
         <v>2017</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>578</v>
+        <v>603</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>433</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F40" s="2"/>
+        <v>604</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>605</v>
+      </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -7437,18 +7744,20 @@
         <v>2017</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="F41" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>609</v>
+      </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -7465,18 +7774,20 @@
         <v>2016</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>584</v>
+        <v>611</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F42" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>613</v>
+      </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
@@ -7493,18 +7804,20 @@
         <v>2016</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>587</v>
+        <v>615</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>433</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="F43" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>617</v>
+      </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -7521,18 +7834,20 @@
         <v>2016</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>589</v>
+        <v>618</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>560</v>
+        <v>580</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>590</v>
+        <v>619</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="F44" s="2"/>
+        <v>620</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>621</v>
+      </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
@@ -7549,18 +7864,20 @@
         <v>2016</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>592</v>
+        <v>622</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>593</v>
+        <v>623</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>594</v>
+        <v>624</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="F45" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>626</v>
+      </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -7577,18 +7894,20 @@
         <v>2015</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>596</v>
+        <v>627</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>597</v>
+        <v>628</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>598</v>
+        <v>629</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="F46" s="2"/>
+        <v>630</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>631</v>
+      </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -7605,18 +7924,20 @@
         <v>2015</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>601</v>
+        <v>633</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>457</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="F47" s="2"/>
+        <v>634</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>635</v>
+      </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
@@ -7633,18 +7954,20 @@
         <v>2015</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>603</v>
+        <v>636</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>604</v>
+        <v>637</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>605</v>
+        <v>638</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="F48" s="2"/>
+        <v>639</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>640</v>
+      </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -7661,18 +7984,20 @@
         <v>2015</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>607</v>
+        <v>641</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>608</v>
+        <v>642</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>609</v>
+        <v>643</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="F49" s="2"/>
+        <v>644</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>645</v>
+      </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
@@ -7689,18 +8014,20 @@
         <v>2015</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>611</v>
+        <v>646</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>612</v>
+        <v>647</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F50" s="2"/>
+        <v>648</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>649</v>
+      </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -7717,18 +8044,20 @@
         <v>2014</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>614</v>
+        <v>650</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>615</v>
+        <v>651</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="F51" s="2"/>
+        <v>652</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>653</v>
+      </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -7745,18 +8074,20 @@
         <v>2014</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>617</v>
+        <v>654</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>618</v>
+        <v>655</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F52" s="2"/>
+        <v>656</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>657</v>
+      </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -7773,18 +8104,20 @@
         <v>2014</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>620</v>
+        <v>658</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>621</v>
+        <v>659</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>622</v>
+        <v>660</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="F53" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>662</v>
+      </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -7801,18 +8134,20 @@
         <v>2014</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>624</v>
+        <v>663</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>625</v>
+        <v>664</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>626</v>
+        <v>665</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F54" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>667</v>
+      </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -7829,18 +8164,20 @@
         <v>2013</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>628</v>
+        <v>668</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>629</v>
+        <v>669</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F55" s="2"/>
+        <v>671</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>672</v>
+      </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -7857,18 +8194,20 @@
         <v>2013</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>632</v>
+        <v>673</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>633</v>
+        <v>674</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>634</v>
+        <v>675</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F56" s="2"/>
+        <v>676</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>677</v>
+      </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
@@ -7885,18 +8224,20 @@
         <v>2013</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>636</v>
+        <v>678</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>637</v>
+        <v>679</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>638</v>
+        <v>680</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F57" s="2"/>
+        <v>681</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>682</v>
+      </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -7913,18 +8254,20 @@
         <v>2013</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>640</v>
+        <v>683</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>641</v>
+        <v>684</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>642</v>
+        <v>685</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="F58" s="2"/>
+        <v>686</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>687</v>
+      </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
@@ -7941,18 +8284,20 @@
         <v>2012</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>644</v>
+        <v>688</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>645</v>
+        <v>689</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>646</v>
+        <v>690</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="F59" s="2"/>
+        <v>691</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>692</v>
+      </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
@@ -7969,18 +8314,20 @@
         <v>2012</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>648</v>
+        <v>693</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>641</v>
+        <v>684</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>452</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="F60" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>695</v>
+      </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -7997,18 +8344,20 @@
         <v>2012</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>650</v>
+        <v>696</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>651</v>
+        <v>697</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>652</v>
+        <v>698</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="F61" s="2"/>
+        <v>699</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>700</v>
+      </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -8025,18 +8374,20 @@
         <v>2012</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>654</v>
+        <v>701</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>656</v>
+        <v>703</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="F62" s="2"/>
+        <v>704</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>705</v>
+      </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
@@ -8053,18 +8404,20 @@
         <v>2012</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>658</v>
+        <v>706</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>659</v>
+        <v>707</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="F63" s="2"/>
+        <v>708</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>709</v>
+      </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -8081,18 +8434,20 @@
         <v>2011</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>661</v>
+        <v>710</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>662</v>
+        <v>711</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>663</v>
+        <v>712</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="F64" s="2"/>
+        <v>713</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>714</v>
+      </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
@@ -8109,18 +8464,20 @@
         <v>2011</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>626</v>
-      </c>
       <c r="E65" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="F65" s="2"/>
+        <v>717</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>718</v>
+      </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
@@ -8137,18 +8494,20 @@
         <v>2010</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>668</v>
+        <v>719</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>669</v>
+        <v>720</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>670</v>
+        <v>721</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="F66" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>723</v>
+      </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
@@ -8165,18 +8524,20 @@
         <v>2010</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>672</v>
+        <v>724</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>673</v>
+        <v>725</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="F67" s="2"/>
+        <v>726</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>727</v>
+      </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -8193,18 +8554,20 @@
         <v>2010</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>675</v>
+        <v>728</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>676</v>
+        <v>729</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>677</v>
+        <v>730</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F68" s="2"/>
+        <v>731</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>732</v>
+      </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -8221,18 +8584,20 @@
         <v>2010</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>679</v>
+        <v>733</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>680</v>
+        <v>734</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>594</v>
+        <v>624</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="F69" s="2"/>
+        <v>735</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>736</v>
+      </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -8249,18 +8614,20 @@
         <v>2010</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>682</v>
+        <v>737</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>683</v>
+        <v>738</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="F70" s="2"/>
+        <v>739</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>740</v>
+      </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -8277,18 +8644,20 @@
         <v>2010</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>685</v>
+        <v>741</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>686</v>
+        <v>742</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>687</v>
+        <v>743</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="F71" s="2"/>
+        <v>744</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>745</v>
+      </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -8305,18 +8674,20 @@
         <v>2010</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>689</v>
+        <v>746</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>690</v>
+        <v>747</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>691</v>
+        <v>748</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F72" s="2"/>
+        <v>749</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>750</v>
+      </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -8333,18 +8704,20 @@
         <v>2010</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>693</v>
+        <v>751</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>694</v>
+        <v>752</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>695</v>
+        <v>753</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="F73" s="2"/>
+        <v>754</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>755</v>
+      </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
@@ -8361,18 +8734,20 @@
         <v>2009</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>697</v>
+        <v>756</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>698</v>
+        <v>757</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>699</v>
+        <v>758</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="F74" s="2"/>
+        <v>759</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>760</v>
+      </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -8389,18 +8764,20 @@
         <v>2009</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>701</v>
+        <v>761</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>702</v>
+        <v>762</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="F75" s="2"/>
+        <v>763</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>764</v>
+      </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -8417,18 +8794,20 @@
         <v>2009</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>704</v>
+        <v>765</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>705</v>
+        <v>766</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>584</v>
+        <v>611</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="F76" s="2"/>
+        <v>767</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>768</v>
+      </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
@@ -8445,18 +8824,20 @@
         <v>2009</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>707</v>
+        <v>769</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>708</v>
+        <v>770</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>709</v>
+        <v>771</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="F77" s="2"/>
+        <v>772</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>773</v>
+      </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
@@ -8473,18 +8854,20 @@
         <v>2008</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>711</v>
+        <v>774</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>712</v>
+        <v>775</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="F78" s="2"/>
+        <v>776</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>777</v>
+      </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
@@ -8501,18 +8884,20 @@
         <v>2008</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>714</v>
+        <v>778</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>715</v>
+        <v>779</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>716</v>
+        <v>780</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="F79" s="2"/>
+        <v>781</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>782</v>
+      </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
@@ -8529,18 +8914,20 @@
         <v>2008</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>718</v>
+        <v>783</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>719</v>
+        <v>784</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>663</v>
+        <v>712</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="F80" s="2"/>
+        <v>785</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>786</v>
+      </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
@@ -8557,18 +8944,20 @@
         <v>2007</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>721</v>
+        <v>787</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>722</v>
+        <v>788</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>594</v>
+        <v>624</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="F81" s="2"/>
+        <v>789</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>790</v>
+      </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
@@ -8585,18 +8974,20 @@
         <v>2007</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>724</v>
+        <v>791</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>725</v>
+        <v>792</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="F82" s="2"/>
+        <v>793</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>794</v>
+      </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
@@ -8613,18 +9004,20 @@
         <v>2007</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>727</v>
+        <v>795</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>728</v>
+        <v>796</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>729</v>
+        <v>797</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F83" s="2"/>
+        <v>798</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>799</v>
+      </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
@@ -8641,18 +9034,20 @@
         <v>2007</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>731</v>
+        <v>800</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>732</v>
+        <v>801</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>733</v>
+        <v>802</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="F84" s="2"/>
+        <v>803</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>804</v>
+      </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
@@ -8669,18 +9064,20 @@
         <v>2007</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>735</v>
+        <v>805</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>736</v>
+        <v>806</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>737</v>
+        <v>807</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="F85" s="2"/>
+        <v>808</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>809</v>
+      </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
@@ -8697,18 +9094,20 @@
         <v>2006</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>739</v>
+        <v>810</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>736</v>
+        <v>806</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>687</v>
+        <v>743</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="F86" s="2"/>
+        <v>811</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>812</v>
+      </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
@@ -8725,18 +9124,20 @@
         <v>2006</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>741</v>
+        <v>813</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>742</v>
+        <v>814</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>626</v>
+        <v>665</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="F87" s="2"/>
+        <v>815</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>816</v>
+      </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
@@ -8753,18 +9154,20 @@
         <v>2006</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>744</v>
+        <v>817</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>745</v>
+        <v>818</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>729</v>
+        <v>797</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="F88" s="2"/>
+        <v>819</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>820</v>
+      </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
@@ -8781,18 +9184,20 @@
         <v>2005</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>747</v>
+        <v>821</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>748</v>
+        <v>822</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>702</v>
+        <v>762</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="F89" s="2"/>
+        <v>823</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>824</v>
+      </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
@@ -8809,18 +9214,20 @@
         <v>2005</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>750</v>
+        <v>825</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>751</v>
+        <v>826</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>752</v>
+        <v>827</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="F90" s="2"/>
+        <v>828</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>829</v>
+      </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
@@ -8837,18 +9244,20 @@
         <v>2004</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>754</v>
+        <v>830</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>755</v>
+        <v>831</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>756</v>
+        <v>832</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="F91" s="2"/>
+        <v>833</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>834</v>
+      </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
@@ -8865,18 +9274,20 @@
         <v>2004</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>758</v>
+        <v>835</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>759</v>
+        <v>836</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>760</v>
+        <v>837</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="F92" s="2"/>
+        <v>838</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>839</v>
+      </c>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
@@ -8893,18 +9304,20 @@
         <v>2004</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>762</v>
+        <v>840</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>763</v>
+        <v>841</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>626</v>
+        <v>665</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="F93" s="2"/>
+        <v>842</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>843</v>
+      </c>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
@@ -8921,18 +9334,20 @@
         <v>2003</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>765</v>
+        <v>844</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>766</v>
+        <v>845</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>767</v>
+        <v>846</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="F94" s="2"/>
+        <v>847</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>848</v>
+      </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
@@ -8949,18 +9364,20 @@
         <v>2003</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>769</v>
+        <v>849</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>770</v>
+        <v>850</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>716</v>
+        <v>780</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="F95" s="2"/>
+        <v>851</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>852</v>
+      </c>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
@@ -8977,18 +9394,20 @@
         <v>2003</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>772</v>
+        <v>853</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>773</v>
+        <v>854</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>774</v>
+        <v>855</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="F96" s="2"/>
+        <v>856</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>857</v>
+      </c>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
@@ -9005,18 +9424,20 @@
         <v>2003</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>776</v>
+        <v>858</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>777</v>
+        <v>859</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>778</v>
+        <v>860</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="F97" s="2"/>
+        <v>861</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>862</v>
+      </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
@@ -9033,18 +9454,20 @@
         <v>2003</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>780</v>
+        <v>863</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>728</v>
+        <v>796</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>781</v>
+        <v>864</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="F98" s="2"/>
+        <v>865</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>866</v>
+      </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
@@ -9061,18 +9484,20 @@
         <v>2003</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>783</v>
+        <v>867</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>784</v>
+        <v>868</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>778</v>
+        <v>860</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="F99" s="2"/>
+        <v>869</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>870</v>
+      </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>

--- a/content/lab-content.xlsx
+++ b/content/lab-content.xlsx
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="884">
   <si>
     <t>Lab website content</t>
   </si>
@@ -546,10 +546,19 @@
     <t>Homepage headline</t>
   </si>
   <si>
+    <t>Genome Biology</t>
+  </si>
+  <si>
+    <t>The large sentence at the top of the homepage.</t>
+  </si>
+  <si>
+    <t>Homepage subheading</t>
+  </si>
+  <si>
     <t>Epigenetic regulation and chromatin architecture</t>
   </si>
   <si>
-    <t>The large sentence at the top of the homepage.</t>
+    <t>Smaller line directly under the homepage headline. Leave blank for none.</t>
   </si>
   <si>
     <t>Homepage introduction</t>
@@ -938,6 +947,12 @@
     <t>apark55@jhmi.edu</t>
   </si>
   <si>
+    <t>Li Wang</t>
+  </si>
+  <si>
+    <t>lwang258@jh.edu</t>
+  </si>
+  <si>
     <t>Brady Bock</t>
   </si>
   <si>
@@ -947,12 +962,6 @@
     <t>bbock4@jh.edu</t>
   </si>
   <si>
-    <t>Li Wang</t>
-  </si>
-  <si>
-    <t>lwang258@jh.edu</t>
-  </si>
-  <si>
     <t>Luiz Gustavo dos Anjos Borges</t>
   </si>
   <si>
@@ -2958,9 +2967,6 @@
   </si>
   <si>
     <t>Politz, J., van Driel, R., Sauer, M., Pombo, A.</t>
-  </si>
-  <si>
-    <t>Genome Biology</t>
   </si>
   <si>
     <t>4(3), 310</t>
@@ -3676,28 +3682,28 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3705,23 +3711,23 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3729,23 +3735,23 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3766,7 +3772,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -3834,29 +3840,29 @@
         <v>60</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>66</v>
@@ -3937,6 +3943,17 @@
       </c>
       <c r="C15" s="6" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3968,77 +3985,77 @@
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4059,334 +4076,334 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -4418,90 +4435,90 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -4533,524 +4550,524 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="H1" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -5083,1180 +5100,1180 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -6286,22 +6303,22 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6309,19 +6326,19 @@
         <v>46212</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6329,17 +6346,17 @@
         <v>46175</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6347,19 +6364,19 @@
         <v>45938</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6367,19 +6384,19 @@
         <v>45799</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6387,19 +6404,19 @@
         <v>45637</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6407,19 +6424,19 @@
         <v>45333</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6427,19 +6444,19 @@
         <v>45096</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6447,19 +6464,19 @@
         <v>44980</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6467,19 +6484,19 @@
         <v>44517</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6487,19 +6504,19 @@
         <v>44120</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6507,19 +6524,19 @@
         <v>43766</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -6552,40 +6569,40 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6593,29 +6610,29 @@
         <v>2026</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6623,27 +6640,27 @@
         <v>2026</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6651,27 +6668,27 @@
         <v>2026</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6679,27 +6696,27 @@
         <v>2026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6707,27 +6724,27 @@
         <v>2025</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6735,29 +6752,29 @@
         <v>2025</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6765,29 +6782,29 @@
         <v>2025</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6795,27 +6812,27 @@
         <v>2025</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6823,31 +6840,31 @@
         <v>2024</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6855,29 +6872,29 @@
         <v>2024</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6885,27 +6902,27 @@
         <v>2024</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6913,27 +6930,27 @@
         <v>2024</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6941,27 +6958,27 @@
         <v>2024</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6969,29 +6986,29 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6999,29 +7016,29 @@
         <v>2023</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7029,29 +7046,29 @@
         <v>2023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7059,29 +7076,29 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7089,29 +7106,29 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7119,29 +7136,29 @@
         <v>2022</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7149,29 +7166,29 @@
         <v>2021</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7179,29 +7196,29 @@
         <v>2021</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7209,29 +7226,29 @@
         <v>2021</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7239,29 +7256,29 @@
         <v>2021</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7269,29 +7286,29 @@
         <v>2020</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7299,29 +7316,29 @@
         <v>2020</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7329,29 +7346,29 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7359,29 +7376,29 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7389,29 +7406,29 @@
         <v>2019</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7419,29 +7436,29 @@
         <v>2019</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7449,29 +7466,29 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7479,29 +7496,29 @@
         <v>2018</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>564</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7509,29 +7526,29 @@
         <v>2017</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7539,29 +7556,29 @@
         <v>2017</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7569,29 +7586,29 @@
         <v>2017</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7599,29 +7616,29 @@
         <v>2017</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7629,29 +7646,29 @@
         <v>2017</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7659,29 +7676,29 @@
         <v>2017</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7689,29 +7706,29 @@
         <v>2017</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7719,29 +7736,29 @@
         <v>2017</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7749,29 +7766,29 @@
         <v>2017</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7779,29 +7796,29 @@
         <v>2016</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7809,29 +7826,29 @@
         <v>2016</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L43" s="2" t="s">
-